--- a/latest.xlsx
+++ b/latest.xlsx
@@ -467,7 +467,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>90492.804</v>
+        <v>90477.326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G2" t="n">
-        <v>90.48999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>79650.151</v>
+        <v>80005.679</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G3" t="n">
-        <v>79.65000000000001</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>37724.857</v>
+        <v>37956.677</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G4" t="n">
-        <v>37.72</v>
+        <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>29028.823</v>
+        <v>29189.813</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G5" t="n">
-        <v>29.03</v>
+        <v>29.19</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         <v>91</v>
       </c>
       <c r="B6" t="n">
-        <v>26646.445</v>
+        <v>26648.069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G6" t="n">
         <v>26.65</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +627,7 @@
         <v>92</v>
       </c>
       <c r="B7" t="n">
-        <v>26491.751</v>
+        <v>26521.296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G7" t="n">
-        <v>26.49</v>
+        <v>26.52</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="8">
@@ -659,7 +659,7 @@
         <v>103</v>
       </c>
       <c r="B8" t="n">
-        <v>25287.073</v>
+        <v>25322.371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G8" t="n">
-        <v>25.29</v>
+        <v>25.32</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="9">
@@ -691,7 +691,7 @@
         <v>127</v>
       </c>
       <c r="B9" t="n">
-        <v>21315.126</v>
+        <v>21394.307</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,21 +709,21 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779090002216</v>
+        <v>1779090602161</v>
       </c>
       <c r="G9" t="n">
-        <v>21.32</v>
+        <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46160.54863675926</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" t="n">
-        <v>16488.03</v>
+        <v>16508.292</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G10" t="n">
-        <v>16.49</v>
+        <v>16.51</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>212</v>
       </c>
       <c r="B11" t="n">
-        <v>14116.083</v>
+        <v>14130.808</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G11" t="n">
-        <v>14.12</v>
+        <v>14.13</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="12">
@@ -787,7 +787,7 @@
         <v>235</v>
       </c>
       <c r="B12" t="n">
-        <v>12975.388</v>
+        <v>13046.133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G12" t="n">
-        <v>12.98</v>
+        <v>13.05</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="13">
@@ -819,7 +819,7 @@
         <v>250</v>
       </c>
       <c r="B13" t="n">
-        <v>12363.982</v>
+        <v>12384.432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -837,21 +837,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G13" t="n">
-        <v>12.36</v>
+        <v>12.38</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" t="n">
-        <v>11210.941</v>
+        <v>11285.461</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G14" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="15">
@@ -883,7 +883,7 @@
         <v>315</v>
       </c>
       <c r="B15" t="n">
-        <v>10425.266</v>
+        <v>10431.436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G15" t="n">
         <v>10.43</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B16" t="n">
-        <v>10018.194</v>
+        <v>10076.324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G16" t="n">
-        <v>10.02</v>
+        <v>10.08</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B17" t="n">
-        <v>9236.787</v>
+        <v>9246.704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G17" t="n">
-        <v>9.24</v>
+        <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B18" t="n">
-        <v>9213.691999999999</v>
+        <v>9223.608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G18" t="n">
-        <v>9.210000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B19" t="n">
-        <v>8364.214</v>
+        <v>8400.114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G19" t="n">
-        <v>8.359999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="20">
@@ -1043,7 +1043,7 @@
         <v>429</v>
       </c>
       <c r="B20" t="n">
-        <v>8250.134</v>
+        <v>8252.09</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="21">
@@ -1075,7 +1075,7 @@
         <v>469</v>
       </c>
       <c r="B21" t="n">
-        <v>7829.914</v>
+        <v>7845.496</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G21" t="n">
-        <v>7.83</v>
+        <v>7.85</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B22" t="n">
-        <v>7702.825</v>
+        <v>7698.846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G22" t="n">
         <v>7.7</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B23" t="n">
-        <v>7702.685</v>
+        <v>7698.706</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G23" t="n">
         <v>7.7</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="24">
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B25" t="n">
-        <v>7264.225</v>
+        <v>7296.476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G25" t="n">
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B26" t="n">
-        <v>6467.865</v>
+        <v>6475.728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G26" t="n">
-        <v>6.47</v>
+        <v>6.48</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B27" t="n">
-        <v>6130.665</v>
+        <v>6147.498</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G27" t="n">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="28">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G28" t="n">
         <v>5.88</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="30">
@@ -1363,7 +1363,7 @@
         <v>772</v>
       </c>
       <c r="B30" t="n">
-        <v>5451.656</v>
+        <v>5453.086</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B31" t="n">
-        <v>5146.324</v>
+        <v>5154.958</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G31" t="n">
         <v>5.15</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B32" t="n">
-        <v>5146.324</v>
+        <v>5154.958</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G32" t="n">
         <v>5.15</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="33">
@@ -1459,7 +1459,7 @@
         <v>824</v>
       </c>
       <c r="B33" t="n">
-        <v>5133.839</v>
+        <v>5133.936</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G33" t="n">
         <v>5.13</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G34" t="n">
         <v>5.07</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="35">
@@ -1523,16 +1523,16 @@
         <v>836</v>
       </c>
       <c r="B35" t="n">
-        <v>5048.198</v>
+        <v>5050.003</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Venu Srinivasan</t>
+          <t>Mangal Prabhat Lodha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Two-wheelers</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G35" t="n">
         <v>5.05</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="36">
@@ -1555,7 +1555,7 @@
         <v>837</v>
       </c>
       <c r="B36" t="n">
-        <v>5047.662</v>
+        <v>5048.433</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="37">
@@ -1587,7 +1587,7 @@
         <v>838</v>
       </c>
       <c r="B37" t="n">
-        <v>5047.657</v>
+        <v>5048.428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1605,30 +1605,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B38" t="n">
-        <v>5024.231</v>
+        <v>5032.425</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mangal Prabhat Lodha</t>
+          <t>Venu Srinivasan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Two-wheelers</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1637,30 +1637,30 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G38" t="n">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B39" t="n">
-        <v>4973.227</v>
+        <v>4990.785</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chandru Raheja</t>
+          <t>Kailashchandra Nuwal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Industrial explosives</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1669,30 +1669,30 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G39" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B40" t="n">
-        <v>4968.726</v>
+        <v>4973.835</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kailashchandra Nuwal</t>
+          <t>Chandru Raheja</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Industrial explosives</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G40" t="n">
         <v>4.97</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="41">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G41" t="n">
         <v>4.96</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="42">
@@ -1765,21 +1765,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B43" t="n">
-        <v>4615.363</v>
+        <v>4642.004</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G43" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B44" t="n">
-        <v>4571.528</v>
+        <v>4589.998</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G44" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B45" t="n">
         <v>4394.112</v>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="B46" t="n">
-        <v>4364.853</v>
+        <v>4373.556</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1893,18 +1893,18 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G46" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B47" t="n">
         <v>4286.386</v>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G47" t="n">
         <v>4.29</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B48" t="n">
-        <v>4247.147</v>
+        <v>4271.237</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B49" t="n">
-        <v>4110.868</v>
+        <v>4107.405</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G49" t="n">
         <v>4.11</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="51">
@@ -2035,7 +2035,7 @@
         <v>1092</v>
       </c>
       <c r="B51" t="n">
-        <v>3903.891</v>
+        <v>3910.26</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G51" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="52">
@@ -2067,7 +2067,7 @@
         <v>1097</v>
       </c>
       <c r="B52" t="n">
-        <v>3887.541</v>
+        <v>3896.349</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G52" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B53" t="n">
-        <v>3820.525</v>
+        <v>3826.894</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G53" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B54" t="n">
-        <v>3718.966</v>
+        <v>3725.447</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G54" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B55" t="n">
-        <v>3718.929</v>
+        <v>3725.41</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G55" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B56" t="n">
-        <v>3718.929</v>
+        <v>3725.41</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G56" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="57">
@@ -2227,7 +2227,7 @@
         <v>1162</v>
       </c>
       <c r="B57" t="n">
-        <v>3688.192</v>
+        <v>3686.541</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B58" t="n">
-        <v>3674.213</v>
+        <v>3684.607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G58" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B59" t="n">
-        <v>3558.149</v>
+        <v>3565.925</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G59" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B60" t="n">
-        <v>3538.797</v>
+        <v>3550.464</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G60" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="B61" t="n">
-        <v>3497.412</v>
+        <v>3513.031</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G61" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B62" t="n">
-        <v>3494.24</v>
+        <v>3503.706</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G62" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="B63" t="n">
-        <v>3473.737</v>
+        <v>3479.264</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G63" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B64" t="n">
-        <v>3462.495</v>
+        <v>3471.711</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2469,21 +2469,21 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G64" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B65" t="n">
-        <v>3452.156</v>
+        <v>3453.607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G65" t="n">
         <v>3.45</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B66" t="n">
-        <v>3414.626</v>
+        <v>3417.551</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G66" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="B67" t="n">
-        <v>3399.222</v>
+        <v>3403.577</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G67" t="n">
         <v>3.4</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="68">
@@ -2579,7 +2579,7 @@
         <v>1274</v>
       </c>
       <c r="B68" t="n">
-        <v>3357.3</v>
+        <v>3361.341</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="70">
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B71" t="n">
-        <v>3192.375</v>
+        <v>3189.698</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2693,21 +2693,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G71" t="n">
         <v>3.19</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B72" t="n">
-        <v>3142.957</v>
+        <v>3151.052</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G72" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="74">
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B75" t="n">
-        <v>3073.909</v>
+        <v>3077.258</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G75" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B76" t="n">
-        <v>3071.51</v>
+        <v>3073.774</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G76" t="n">
         <v>3.07</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="77">
@@ -2885,18 +2885,18 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G77" t="n">
         <v>3.06</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B78" t="n">
         <v>3011.155</v>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B79" t="n">
-        <v>3001.011</v>
+        <v>3004.303</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="80">
@@ -2963,16 +2963,16 @@
         <v>1415</v>
       </c>
       <c r="B80" t="n">
-        <v>2991.225</v>
+        <v>2994.858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leena Tewari</t>
+          <t>Rajan Raheja &amp; family</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2981,30 +2981,30 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G80" t="n">
         <v>2.99</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B81" t="n">
-        <v>2986.954</v>
+        <v>2991.225</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rajan Raheja &amp; family</t>
+          <t>Leena Tewari</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="82">
@@ -3027,7 +3027,7 @@
         <v>1429</v>
       </c>
       <c r="B82" t="n">
-        <v>2951.056</v>
+        <v>2954.252</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B83" t="n">
-        <v>2935.311</v>
+        <v>2939.282</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G83" t="n">
         <v>2.94</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B85" t="n">
-        <v>2831.948</v>
+        <v>2830.394</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G85" t="n">
         <v>2.83</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B86" t="n">
-        <v>2810.175</v>
+        <v>2811.5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G86" t="n">
         <v>2.81</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="88">
@@ -3219,7 +3219,7 @@
         <v>1536</v>
       </c>
       <c r="B88" t="n">
-        <v>2746.009</v>
+        <v>2746.154</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="B89" t="n">
-        <v>2740.806</v>
+        <v>2738.756</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3269,21 +3269,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G89" t="n">
         <v>2.74</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="B90" t="n">
-        <v>2740.806</v>
+        <v>2738.756</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="91">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="92">
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B93" t="n">
-        <v>2644.596</v>
+        <v>2642.879</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G93" t="n">
         <v>2.64</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="B94" t="n">
-        <v>2602.298</v>
+        <v>2615.953</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G94" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="B95" t="n">
-        <v>2602.298</v>
+        <v>2615.953</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G95" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="B96" t="n">
-        <v>2602.298</v>
+        <v>2615.953</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G96" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="B97" t="n">
-        <v>2602.298</v>
+        <v>2615.953</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G97" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="B98" t="n">
-        <v>2597.669</v>
+        <v>2601.617</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G98" t="n">
         <v>2.6</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="B99" t="n">
-        <v>2540.295</v>
+        <v>2551.289</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="100">
@@ -3603,7 +3603,7 @@
         <v>1651</v>
       </c>
       <c r="B100" t="n">
-        <v>2525.691</v>
+        <v>2527.26</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G100" t="n">
         <v>2.53</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B101" t="n">
-        <v>2506.256</v>
+        <v>2510.433</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G101" t="n">
         <v>2.51</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B102" t="n">
-        <v>2491.362</v>
+        <v>2490.262</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B103" t="n">
-        <v>2477.774</v>
+        <v>2484.027</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3717,21 +3717,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G103" t="n">
         <v>2.48</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="B104" t="n">
-        <v>2455.251</v>
+        <v>2465.701</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G104" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1703</v>
+        <v>1693</v>
       </c>
       <c r="B105" t="n">
-        <v>2447.452</v>
+        <v>2457.753</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G105" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="106">
@@ -3795,7 +3795,7 @@
         <v>1718</v>
       </c>
       <c r="B106" t="n">
-        <v>2436.419</v>
+        <v>2438.423</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3813,30 +3813,30 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779090002217</v>
+        <v>1779090602161</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55558056713</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="B107" t="n">
-        <v>2380.303</v>
+        <v>2385.558</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Anand Deshpande</t>
+          <t>Sandeep Engineer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Plastic pipes</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3845,30 +3845,30 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G107" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="B108" t="n">
-        <v>2379.292</v>
+        <v>2382.005</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sandeep Engineer</t>
+          <t>Anand Deshpande</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Plastic pipes</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G108" t="n">
         <v>2.38</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="109">
@@ -3891,16 +3891,16 @@
         <v>1773</v>
       </c>
       <c r="B109" t="n">
-        <v>2355.703</v>
+        <v>2355.746</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salil Singhal</t>
+          <t>Bhadresh Shah</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Agrochemicals</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3909,30 +3909,30 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1780</v>
+        <v>1774</v>
       </c>
       <c r="B110" t="n">
-        <v>2345.99</v>
+        <v>2355.74</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bhadresh Shah</t>
+          <t>Salil Singhal</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Agrochemicals</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G110" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="B111" t="n">
-        <v>2336.34</v>
+        <v>2338.878</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G111" t="n">
         <v>2.34</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="112">
@@ -4005,30 +4005,30 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="B113" t="n">
-        <v>2250.673</v>
+        <v>2256.716</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Acharya Balkrishna</t>
+          <t>Sunil Vachani</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4037,30 +4037,30 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G113" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="B114" t="n">
-        <v>2248.757</v>
+        <v>2250.673</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sunil Vachani</t>
+          <t>Acharya Balkrishna</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4069,21 +4069,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="B115" t="n">
-        <v>2238.599</v>
+        <v>2237.983</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="116">
@@ -4115,7 +4115,7 @@
         <v>1872</v>
       </c>
       <c r="B116" t="n">
-        <v>2230.236</v>
+        <v>2233.495</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G116" t="n">
         <v>2.23</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="B117" t="n">
         <v>2189.241</v>
@@ -4165,21 +4165,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G117" t="n">
         <v>2.19</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B118" t="n">
-        <v>2187.406</v>
+        <v>2187.807</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="B119" t="n">
-        <v>2175.665</v>
+        <v>2184.233</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B121" t="n">
-        <v>2143.253</v>
+        <v>2144.847</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="B122" t="n">
-        <v>2108.924</v>
+        <v>2111.088</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="123">
@@ -4339,7 +4339,7 @@
         <v>1971</v>
       </c>
       <c r="B123" t="n">
-        <v>2104.785</v>
+        <v>2106.816</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G123" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="125">
@@ -4421,21 +4421,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B126" t="n">
-        <v>2091.244</v>
+        <v>2091.138</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -4453,13 +4453,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="127">
@@ -4467,7 +4467,7 @@
         <v>2015</v>
       </c>
       <c r="B127" t="n">
-        <v>2055.787</v>
+        <v>2057.94</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G127" t="n">
         <v>2.06</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B128" t="n">
-        <v>2045.561</v>
+        <v>2054.162</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B129" t="n">
         <v>2017.058</v>
@@ -4549,21 +4549,21 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B130" t="n">
-        <v>2014.01</v>
+        <v>2013.065</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G130" t="n">
         <v>2.01</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2092</v>
+        <v>2086</v>
       </c>
       <c r="B131" t="n">
-        <v>1991.97</v>
+        <v>1997.884</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G131" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="132">
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="133">
@@ -4677,30 +4677,30 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B134" t="n">
-        <v>1943.862</v>
+        <v>1944.772</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>P.V. Krishna Reddy</t>
+          <t>Lalit Khaitan</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4709,30 +4709,30 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G134" t="n">
         <v>1.94</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="B135" t="n">
-        <v>1942.191</v>
+        <v>1943.862</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lalit Khaitan</t>
+          <t>P.V. Krishna Reddy</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4741,21 +4741,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2181</v>
+        <v>2175</v>
       </c>
       <c r="B136" t="n">
-        <v>1908.52</v>
+        <v>1916.917</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G136" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B137" t="n">
-        <v>1890.537</v>
+        <v>1893.939</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="138">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="139">
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2240</v>
+        <v>2246</v>
       </c>
       <c r="B140" t="n">
-        <v>1846.016</v>
+        <v>1841.699</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G140" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="B141" t="n">
-        <v>1834.013</v>
+        <v>1835.829</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G141" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="142">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="143">
@@ -4979,7 +4979,7 @@
         <v>2280</v>
       </c>
       <c r="B143" t="n">
-        <v>1805.028</v>
+        <v>1806.911</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="B144" t="n">
-        <v>1763.658</v>
+        <v>1768.507</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G144" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="145">
@@ -5043,16 +5043,16 @@
         <v>2327</v>
       </c>
       <c r="B145" t="n">
-        <v>1760.675</v>
+        <v>1761.696</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Banwari Lal Bawri</t>
+          <t>Pawan Munjal</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5061,30 +5061,30 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="B146" t="n">
-        <v>1757.812</v>
+        <v>1760.675</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pawan Munjal</t>
+          <t>Banwari Lal Bawri</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="B148" t="n">
-        <v>1703.798</v>
+        <v>1706.459</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -5157,21 +5157,21 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G148" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="B149" t="n">
-        <v>1686.164</v>
+        <v>1689.841</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G149" t="n">
         <v>1.69</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2420</v>
+        <v>2417</v>
       </c>
       <c r="B150" t="n">
-        <v>1679.399</v>
+        <v>1683.057</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="B151" t="n">
-        <v>1674.745</v>
+        <v>1680.313</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -5253,21 +5253,21 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G151" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="B152" t="n">
-        <v>1669.898</v>
+        <v>1673.323</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="B153" t="n">
-        <v>1665.715</v>
+        <v>1667.389</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="154">
@@ -5331,7 +5331,7 @@
         <v>2433</v>
       </c>
       <c r="B154" t="n">
-        <v>1661.723</v>
+        <v>1663.379</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G154" t="n">
         <v>1.66</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2442</v>
+        <v>2434</v>
       </c>
       <c r="B155" t="n">
-        <v>1652.505</v>
+        <v>1659.779</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -5381,21 +5381,21 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G155" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2448</v>
+        <v>2437</v>
       </c>
       <c r="B156" t="n">
-        <v>1650.821</v>
+        <v>1658.87</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G156" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="B157" t="n">
-        <v>1641.536</v>
+        <v>1644.184</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G157" t="n">
         <v>1.64</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B158" t="n">
-        <v>1638.789</v>
+        <v>1638.595</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="159">
@@ -5491,7 +5491,7 @@
         <v>2464</v>
       </c>
       <c r="B159" t="n">
-        <v>1634.41</v>
+        <v>1635.093</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G159" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="160">
@@ -5523,16 +5523,16 @@
         <v>2488</v>
       </c>
       <c r="B160" t="n">
-        <v>1610.731</v>
+        <v>1607.901</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>R.G. Chandramogan</t>
+          <t>Saroj Rani Gupta</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Steel tubes</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5541,30 +5541,30 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2496</v>
+        <v>2490</v>
       </c>
       <c r="B161" t="n">
-        <v>1595.82</v>
+        <v>1606.57</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saroj Rani Gupta</t>
+          <t>R.G. Chandramogan</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Steel tubes</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G161" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="162">
@@ -5587,7 +5587,7 @@
         <v>2535</v>
       </c>
       <c r="B162" t="n">
-        <v>1566.646</v>
+        <v>1565.993</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2547</v>
+        <v>2540</v>
       </c>
       <c r="B163" t="n">
-        <v>1560.001</v>
+        <v>1563.974</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -5637,30 +5637,30 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="B164" t="n">
-        <v>1555.71</v>
+        <v>1560.286</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Satish Reddy</t>
+          <t>Sanjay Agarwal</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5669,30 +5669,30 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G164" t="n">
         <v>1.56</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2563</v>
+        <v>2553</v>
       </c>
       <c r="B165" t="n">
-        <v>1550.646</v>
+        <v>1559.846</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sanjay Agarwal</t>
+          <t>Satish Reddy</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G165" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="B166" t="n">
-        <v>1536.257</v>
+        <v>1534.67</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -5733,13 +5733,13 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G166" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="167">
@@ -5747,7 +5747,7 @@
         <v>2597</v>
       </c>
       <c r="B167" t="n">
-        <v>1528.778</v>
+        <v>1528.57</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -5765,21 +5765,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B168" t="n">
-        <v>1511.87</v>
+        <v>1508.694</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G168" t="n">
         <v>1.51</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="B169" t="n">
         <v>1500</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="B170" t="n">
         <v>1493.176</v>
@@ -5861,21 +5861,21 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="B171" t="n">
-        <v>1492.61</v>
+        <v>1492.347</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="172">
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G172" t="n">
         <v>1.49</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2678</v>
+        <v>2674</v>
       </c>
       <c r="B173" t="n">
-        <v>1463.717</v>
+        <v>1469.671</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2678</v>
+        <v>2674</v>
       </c>
       <c r="B174" t="n">
-        <v>1463.717</v>
+        <v>1469.671</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G174" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="B175" t="n">
-        <v>1453.36</v>
+        <v>1456.345</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -6021,21 +6021,21 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G175" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="B176" t="n">
-        <v>1451.682</v>
+        <v>1454.675</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -6053,21 +6053,21 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="B177" t="n">
-        <v>1439.499</v>
+        <v>1440.731</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G177" t="n">
         <v>1.44</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="B178" t="n">
         <v>1414.525</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="B179" t="n">
         <v>1409.921</v>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="B180" t="n">
-        <v>1406.831</v>
+        <v>1407.631</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779090002217</v>
+        <v>1779090602162</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.5555805787</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2782</v>
+        <v>2779</v>
       </c>
       <c r="B181" t="n">
-        <v>1385.609</v>
+        <v>1387.938</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G181" t="n">
         <v>1.39</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2794</v>
+        <v>2789</v>
       </c>
       <c r="B182" t="n">
-        <v>1378.602</v>
+        <v>1382.324</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G182" t="n">
         <v>1.38</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2800</v>
+        <v>2795</v>
       </c>
       <c r="B183" t="n">
-        <v>1374.327</v>
+        <v>1378.199</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G183" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="B184" t="n">
-        <v>1372.732</v>
+        <v>1376.21</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -6309,21 +6309,21 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G184" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="B185" t="n">
-        <v>1370.49</v>
+        <v>1371.724</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2824</v>
+        <v>2822</v>
       </c>
       <c r="B187" t="n">
-        <v>1354.689</v>
+        <v>1358.151</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -6405,21 +6405,21 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G187" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2845</v>
+        <v>2839</v>
       </c>
       <c r="B188" t="n">
-        <v>1336.735</v>
+        <v>1340.91</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="B189" t="n">
-        <v>1335.695</v>
+        <v>1338.049</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G189" t="n">
         <v>1.34</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="190">
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="191">
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2928</v>
+        <v>2925</v>
       </c>
       <c r="B192" t="n">
-        <v>1284.324</v>
+        <v>1287.787</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -6565,21 +6565,21 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G192" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2943</v>
+        <v>2939</v>
       </c>
       <c r="B193" t="n">
-        <v>1278.721</v>
+        <v>1281.52</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -6597,21 +6597,21 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2949</v>
+        <v>2945</v>
       </c>
       <c r="B194" t="n">
-        <v>1273.562</v>
+        <v>1275.441</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G194" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="195">
@@ -6643,7 +6643,7 @@
         <v>2961</v>
       </c>
       <c r="B195" t="n">
-        <v>1263.669</v>
+        <v>1264.516</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G195" t="n">
         <v>1.26</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="B196" t="n">
-        <v>1252.817</v>
+        <v>1255.644</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G196" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="B197" t="n">
-        <v>1252.804</v>
+        <v>1255.63</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="B198" t="n">
-        <v>1252.804</v>
+        <v>1255.63</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="199">
@@ -6771,7 +6771,7 @@
         <v>2986</v>
       </c>
       <c r="B199" t="n">
-        <v>1245.353</v>
+        <v>1246.287</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2998</v>
+        <v>3001</v>
       </c>
       <c r="B200" t="n">
-        <v>1235.721</v>
+        <v>1234.428</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -6821,30 +6821,30 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3014</v>
+        <v>3004</v>
       </c>
       <c r="B201" t="n">
-        <v>1226.41</v>
+        <v>1232.452</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Deepak Mehta</t>
+          <t>Subbamma Jasti</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6853,30 +6853,30 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3019</v>
+        <v>3006</v>
       </c>
       <c r="B202" t="n">
-        <v>1223.695</v>
+        <v>1229.49</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Alakh Pandey</t>
+          <t>Deepak Mehta</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6885,25 +6885,25 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="B203" t="n">
-        <v>1223.695</v>
+        <v>1222.617</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prateek Boob</t>
+          <t>Alakh Pandey</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6917,30 +6917,30 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3023</v>
+        <v>3020</v>
       </c>
       <c r="B204" t="n">
-        <v>1220.205</v>
+        <v>1222.617</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Subbamma Jasti</t>
+          <t>Prateek Boob</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Edtech</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="B205" t="n">
-        <v>1213.334</v>
+        <v>1214.058</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -6981,21 +6981,21 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="B206" t="n">
-        <v>1175.221</v>
+        <v>1175.807</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G206" t="n">
         <v>1.18</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,21 +7045,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="B208" t="n">
-        <v>1146.998</v>
+        <v>1150.269</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="B209" t="n">
-        <v>1143.138</v>
+        <v>1142.121</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G209" t="n">
         <v>1.14</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3177</v>
+        <v>3179</v>
       </c>
       <c r="B210" t="n">
         <v>1132.544</v>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3179</v>
+        <v>3183</v>
       </c>
       <c r="B211" t="n">
-        <v>1131.107</v>
+        <v>1129.678</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -7173,21 +7173,21 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G211" t="n">
         <v>1.13</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="B212" t="n">
-        <v>1116.784</v>
+        <v>1117.064</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G212" t="n">
         <v>1.12</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="B213" t="n">
-        <v>1111.514</v>
+        <v>1113.057</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3238</v>
+        <v>3234</v>
       </c>
       <c r="B214" t="n">
-        <v>1098.843</v>
+        <v>1099.956</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="215">
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G215" t="n">
         <v>1.08</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="216">
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="B217" t="n">
-        <v>1077.903</v>
+        <v>1081.42</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -7365,30 +7365,30 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3291</v>
+        <v>3288</v>
       </c>
       <c r="B218" t="n">
-        <v>1065.578</v>
+        <v>1067.125</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sachin Agarwal</t>
+          <t>Lalit Keshre</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Metal castings</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7397,30 +7397,30 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="B219" t="n">
-        <v>1064.794</v>
+        <v>1065.578</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Lalit Keshre</t>
+          <t>Sachin Agarwal</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metal castings</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G219" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="B220" t="n">
-        <v>1050.914</v>
+        <v>1050.313</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G220" t="n">
         <v>1.05</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="222">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="223">
@@ -7539,7 +7539,7 @@
         <v>3356</v>
       </c>
       <c r="B223" t="n">
-        <v>1012.217</v>
+        <v>1012.107</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
     <row r="224">
@@ -7571,7 +7571,7 @@
         <v>3391</v>
       </c>
       <c r="B224" t="n">
-        <v>978.676</v>
+        <v>979.436</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779090002217</v>
+        <v>1779090302155</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46160.54863677084</v>
+        <v>46160.55210827546</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -467,7 +467,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>90477.326</v>
+        <v>90360.864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779090602161</v>
+        <v>1779104102168</v>
       </c>
       <c r="G2" t="n">
-        <v>90.48</v>
+        <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183064815</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>80005.679</v>
+        <v>80845.08199999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779090602161</v>
+        <v>1779104102168</v>
       </c>
       <c r="G3" t="n">
-        <v>80.01000000000001</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183064815</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>37956.677</v>
+        <v>37956.283</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779090602161</v>
+        <v>1779104102168</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183064815</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>29189.813</v>
+        <v>29151.569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779090602161</v>
+        <v>1779104102168</v>
       </c>
       <c r="G5" t="n">
-        <v>29.19</v>
+        <v>29.15</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183064815</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         <v>91</v>
       </c>
       <c r="B6" t="n">
-        <v>26648.069</v>
+        <v>26668.92</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G6" t="n">
-        <v>26.65</v>
+        <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +627,7 @@
         <v>92</v>
       </c>
       <c r="B7" t="n">
-        <v>26521.296</v>
+        <v>26624.834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G7" t="n">
-        <v>26.52</v>
+        <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="8">
@@ -659,7 +659,7 @@
         <v>103</v>
       </c>
       <c r="B8" t="n">
-        <v>25322.371</v>
+        <v>25354.315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G8" t="n">
-        <v>25.32</v>
+        <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="9">
@@ -691,7 +691,7 @@
         <v>127</v>
       </c>
       <c r="B9" t="n">
-        <v>21394.307</v>
+        <v>21391.106</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         <v>176</v>
       </c>
       <c r="B10" t="n">
-        <v>16508.292</v>
+        <v>16501.504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G10" t="n">
-        <v>16.51</v>
+        <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>212</v>
       </c>
       <c r="B11" t="n">
-        <v>14130.808</v>
+        <v>14095.831</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G11" t="n">
-        <v>14.13</v>
+        <v>14.1</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="12">
@@ -787,7 +787,7 @@
         <v>235</v>
       </c>
       <c r="B12" t="n">
-        <v>13046.133</v>
+        <v>13062.151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G12" t="n">
-        <v>13.05</v>
+        <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B13" t="n">
-        <v>12384.432</v>
+        <v>12471.668</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -837,21 +837,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G13" t="n">
-        <v>12.38</v>
+        <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B14" t="n">
-        <v>11285.461</v>
+        <v>11445.012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -869,21 +869,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G14" t="n">
-        <v>11.29</v>
+        <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B15" t="n">
-        <v>10431.436</v>
+        <v>10376.047</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G15" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B16" t="n">
-        <v>10076.324</v>
+        <v>10139.4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G16" t="n">
-        <v>10.08</v>
+        <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B17" t="n">
-        <v>9246.704</v>
+        <v>9223.575999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G17" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B18" t="n">
-        <v>9223.608</v>
+        <v>9200.481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G18" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="19">
@@ -1011,7 +1011,7 @@
         <v>421</v>
       </c>
       <c r="B19" t="n">
-        <v>8400.114</v>
+        <v>8387.036</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G19" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B20" t="n">
         <v>8252.09</v>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B21" t="n">
-        <v>7845.496</v>
+        <v>7877.188</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G21" t="n">
-        <v>7.85</v>
+        <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B22" t="n">
-        <v>7698.846</v>
+        <v>7731.099</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B23" t="n">
-        <v>7698.706</v>
+        <v>7730.956</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="25">
@@ -1203,7 +1203,7 @@
         <v>523</v>
       </c>
       <c r="B25" t="n">
-        <v>7296.476</v>
+        <v>7289.86</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B26" t="n">
-        <v>6475.728</v>
+        <v>6473.386</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G26" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="27">
@@ -1267,7 +1267,7 @@
         <v>666</v>
       </c>
       <c r="B27" t="n">
-        <v>6147.498</v>
+        <v>6149.447</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1285,21 +1285,21 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B28" t="n">
-        <v>5881.297</v>
+        <v>5899.196</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G28" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="29">
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B30" t="n">
-        <v>5453.086</v>
+        <v>5453.212</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B31" t="n">
-        <v>5154.958</v>
+        <v>5177.898</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G31" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B32" t="n">
-        <v>5154.958</v>
+        <v>5177.898</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G32" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B33" t="n">
-        <v>5133.936</v>
+        <v>5150.844</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1477,30 +1477,30 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G33" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B34" t="n">
-        <v>5071.275</v>
+        <v>5084.179</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lachhman Das Mittal</t>
+          <t>Mangal Prabhat Lodha</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tractors</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1509,30 +1509,30 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G34" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B35" t="n">
-        <v>5050.003</v>
+        <v>5071.275</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mangal Prabhat Lodha</t>
+          <t>Lachhman Das Mittal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Tractors</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G35" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="36">
@@ -1555,7 +1555,7 @@
         <v>837</v>
       </c>
       <c r="B36" t="n">
-        <v>5048.433</v>
+        <v>5050.542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="37">
@@ -1587,7 +1587,7 @@
         <v>838</v>
       </c>
       <c r="B37" t="n">
-        <v>5048.428</v>
+        <v>5050.537</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1605,30 +1605,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B38" t="n">
-        <v>5032.425</v>
+        <v>4996.846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Venu Srinivasan</t>
+          <t>Chandru Raheja</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Two-wheelers</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1637,21 +1637,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G38" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B39" t="n">
-        <v>4990.785</v>
+        <v>4986.26</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1669,30 +1669,30 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B40" t="n">
-        <v>4973.835</v>
+        <v>4961.495</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chandru Raheja</t>
+          <t>Joy Alukkas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Jewelry</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1701,30 +1701,30 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G40" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B41" t="n">
-        <v>4961.495</v>
+        <v>4953.328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Joy Alukkas</t>
+          <t>Venu Srinivasan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jewelry</t>
+          <t>Two-wheelers</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G41" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="42">
@@ -1765,21 +1765,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B43" t="n">
-        <v>4642.004</v>
+        <v>4651.997</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G43" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B44" t="n">
-        <v>4589.998</v>
+        <v>4599.875</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G44" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="45">
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B46" t="n">
-        <v>4373.556</v>
+        <v>4371.578</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1893,30 +1893,30 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="B47" t="n">
-        <v>4286.386</v>
+        <v>4311.644</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ravi Pillai</t>
+          <t>Falguni Nayar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1925,30 +1925,30 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G47" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B48" t="n">
-        <v>4271.237</v>
+        <v>4287.14</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Falguni Nayar</t>
+          <t>Ravi Pillai</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G48" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="B49" t="n">
-        <v>4107.405</v>
+        <v>4091.609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G49" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B51" t="n">
-        <v>3910.26</v>
+        <v>3920.534</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2053,30 +2053,30 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G51" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1097</v>
+        <v>1120</v>
       </c>
       <c r="B52" t="n">
-        <v>3896.349</v>
+        <v>3837.168</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nirmal Minda</t>
+          <t>Adi Godrej</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Auto parts</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2085,30 +2085,30 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G52" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="B53" t="n">
-        <v>3826.894</v>
+        <v>3812.24</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Adi Godrej</t>
+          <t>Nirmal Minda</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Auto parts</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G53" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="54">
@@ -2131,7 +2131,7 @@
         <v>1144</v>
       </c>
       <c r="B54" t="n">
-        <v>3725.447</v>
+        <v>3742.953</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G54" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="55">
@@ -2163,7 +2163,7 @@
         <v>1145</v>
       </c>
       <c r="B55" t="n">
-        <v>3725.41</v>
+        <v>3742.915</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G55" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="56">
@@ -2195,7 +2195,7 @@
         <v>1145</v>
       </c>
       <c r="B56" t="n">
-        <v>3725.41</v>
+        <v>3742.915</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G56" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="57">
@@ -2227,7 +2227,7 @@
         <v>1162</v>
       </c>
       <c r="B57" t="n">
-        <v>3686.541</v>
+        <v>3692.361</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B58" t="n">
-        <v>3684.607</v>
+        <v>3680.841</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G58" t="n">
         <v>3.68</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="B59" t="n">
-        <v>3565.925</v>
+        <v>3542.882</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G59" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="B60" t="n">
-        <v>3550.464</v>
+        <v>3531.797</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G60" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="61">
@@ -2355,16 +2355,16 @@
         <v>1211</v>
       </c>
       <c r="B61" t="n">
-        <v>3513.031</v>
+        <v>3517.715</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>P.V. Ramprasad Reddy</t>
+          <t>G. M. Rao</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2373,30 +2373,30 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G61" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B62" t="n">
-        <v>3503.706</v>
+        <v>3494.663</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>G. M. Rao</t>
+          <t>P.V. Ramprasad Reddy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2405,30 +2405,30 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G62" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="B63" t="n">
-        <v>3479.264</v>
+        <v>3463.696</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prathap Reddy</t>
+          <t>Sanjiv Goenka</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2437,30 +2437,30 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G63" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B64" t="n">
-        <v>3471.711</v>
+        <v>3461.525</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sanjiv Goenka</t>
+          <t>Vinod Rai Gupta</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Electrical equipment</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2469,30 +2469,30 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G64" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B65" t="n">
-        <v>3453.607</v>
+        <v>3457.731</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vinod Rai Gupta</t>
+          <t>Prathap Reddy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Electrical equipment</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G65" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="B66" t="n">
-        <v>3417.551</v>
+        <v>3437.408</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G66" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="B67" t="n">
-        <v>3403.577</v>
+        <v>3426.048</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G67" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="68">
@@ -2579,7 +2579,7 @@
         <v>1274</v>
       </c>
       <c r="B68" t="n">
-        <v>3361.341</v>
+        <v>3358.115</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="69">
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B70" t="n">
         <v>3221.232</v>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1330</v>
+        <v>1321</v>
       </c>
       <c r="B71" t="n">
-        <v>3189.698</v>
+        <v>3212.603</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2693,21 +2693,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G71" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="B72" t="n">
-        <v>3151.052</v>
+        <v>3152.624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="74">
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="B75" t="n">
-        <v>3077.258</v>
+        <v>3068.446</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2821,30 +2821,30 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G75" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B76" t="n">
-        <v>3073.774</v>
+        <v>3063.21</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Surender Saluja</t>
+          <t>Arvind Tiku</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Solar energy</t>
+          <t>Renewable energy, real estate</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2853,30 +2853,30 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G76" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="B77" t="n">
-        <v>3063.21</v>
+        <v>3047.215</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arvind Tiku</t>
+          <t>Surender Saluja</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Renewable energy, real estate</t>
+          <t>Solar energy</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G77" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="78">
@@ -2917,30 +2917,30 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="B79" t="n">
-        <v>3004.303</v>
+        <v>3011.141</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ramesh Juneja</t>
+          <t>Rajan Raheja &amp; family</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2949,30 +2949,30 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="B80" t="n">
-        <v>2994.858</v>
+        <v>3003.735</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rajan Raheja &amp; family</t>
+          <t>Ramesh Juneja</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G80" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="81">
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B82" t="n">
-        <v>2954.252</v>
+        <v>2953.701</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="83">
@@ -3059,7 +3059,7 @@
         <v>1433</v>
       </c>
       <c r="B83" t="n">
-        <v>2939.282</v>
+        <v>2946.291</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G83" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="B85" t="n">
-        <v>2830.394</v>
+        <v>2835.87</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G85" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="B86" t="n">
-        <v>2811.5</v>
+        <v>2819.016</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G86" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="87">
@@ -3205,30 +3205,30 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B88" t="n">
-        <v>2746.154</v>
+        <v>2749.231</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Harsh Goenka</t>
+          <t>Gurbachan Singh Dhingra</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Paints</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3237,25 +3237,25 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="B89" t="n">
-        <v>2738.756</v>
+        <v>2749.231</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gurbachan Singh Dhingra</t>
+          <t>Kuldip Singh Dhingra</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3269,30 +3269,30 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G89" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="B90" t="n">
-        <v>2738.756</v>
+        <v>2744.293</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kuldip Singh Dhingra</t>
+          <t>Harsh Goenka</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paints</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B91" t="n">
         <v>2717.279</v>
@@ -3333,18 +3333,18 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B92" t="n">
         <v>2707.811</v>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="B93" t="n">
-        <v>2642.879</v>
+        <v>2627.533</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G93" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B94" t="n">
-        <v>2615.953</v>
+        <v>2622.743</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B95" t="n">
-        <v>2615.953</v>
+        <v>2622.743</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B96" t="n">
-        <v>2615.953</v>
+        <v>2622.743</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B97" t="n">
-        <v>2615.953</v>
+        <v>2622.743</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1603</v>
+        <v>1615</v>
       </c>
       <c r="B98" t="n">
-        <v>2601.617</v>
+        <v>2587.632</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3557,30 +3557,30 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G98" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="B99" t="n">
-        <v>2551.289</v>
+        <v>2552.876</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Inder Jaisinghani</t>
+          <t>Devi Shetty</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3589,30 +3589,30 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1651</v>
+        <v>1640</v>
       </c>
       <c r="B100" t="n">
-        <v>2527.26</v>
+        <v>2551.171</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Yusuf Hamied</t>
+          <t>Inder Jaisinghani</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3621,30 +3621,30 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B101" t="n">
-        <v>2510.433</v>
+        <v>2515.184</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Devi Shetty</t>
+          <t>Yusuf Hamied</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G101" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B102" t="n">
-        <v>2490.262</v>
+        <v>2494.136</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="B103" t="n">
-        <v>2484.027</v>
+        <v>2490.279</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3717,21 +3717,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G103" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B104" t="n">
-        <v>2465.701</v>
+        <v>2465.589</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B105" t="n">
-        <v>2457.753</v>
+        <v>2457.642</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B106" t="n">
-        <v>2438.423</v>
+        <v>2435.956</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3813,30 +3813,30 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779090602161</v>
+        <v>1779104102169</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46160.55558056713</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1754</v>
+        <v>1733</v>
       </c>
       <c r="B107" t="n">
-        <v>2385.558</v>
+        <v>2410.942</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sandeep Engineer</t>
+          <t>Anand Deshpande</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Plastic pipes</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3845,30 +3845,30 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G107" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="B108" t="n">
-        <v>2382.005</v>
+        <v>2366.47</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Anand Deshpande</t>
+          <t>Sandeep Engineer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Plastic pipes</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="109">
@@ -3891,7 +3891,7 @@
         <v>1773</v>
       </c>
       <c r="B109" t="n">
-        <v>2355.746</v>
+        <v>2355.803</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -3909,30 +3909,30 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1774</v>
+        <v>1787</v>
       </c>
       <c r="B110" t="n">
-        <v>2355.74</v>
+        <v>2338.44</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Salil Singhal</t>
+          <t>Prem Kumar Arora</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Agrochemicals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3941,30 +3941,30 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G110" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="B111" t="n">
-        <v>2338.878</v>
+        <v>2328.854</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prem Kumar Arora</t>
+          <t>Salil Singhal</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Agrochemicals</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G111" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1843</v>
+        <v>1846</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,30 +4005,30 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1853</v>
+        <v>1847</v>
       </c>
       <c r="B113" t="n">
-        <v>2256.716</v>
+        <v>2270.559</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sunil Vachani</t>
+          <t>Rafique Malik</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4037,18 +4037,18 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G113" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B114" t="n">
         <v>2250.673</v>
@@ -4069,30 +4069,30 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="B115" t="n">
-        <v>2237.983</v>
+        <v>2243.02</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kalanithi Maran</t>
+          <t>Sunil Vachani</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4101,30 +4101,30 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B116" t="n">
-        <v>2233.495</v>
+        <v>2237.983</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rafique Malik</t>
+          <t>Kalanithi Maran</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4133,30 +4133,30 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G116" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1908</v>
+        <v>1892</v>
       </c>
       <c r="B117" t="n">
-        <v>2189.241</v>
+        <v>2203.177</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jupally Rameshwar Rao</t>
+          <t>Basudeo Singh</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4165,30 +4165,30 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G117" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B118" t="n">
-        <v>2187.807</v>
+        <v>2189.241</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Basudeo Singh</t>
+          <t>Jupally Rameshwar Rao</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="B119" t="n">
-        <v>2184.233</v>
+        <v>2182.036</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1940</v>
+        <v>1944</v>
       </c>
       <c r="B121" t="n">
-        <v>2144.847</v>
+        <v>2142.349</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="B122" t="n">
-        <v>2111.088</v>
+        <v>2105.407</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4325,21 +4325,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1971</v>
+        <v>1975</v>
       </c>
       <c r="B123" t="n">
-        <v>2106.816</v>
+        <v>2101.476</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G123" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="125">
@@ -4421,21 +4421,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B126" t="n">
-        <v>2091.138</v>
+        <v>2091.564</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B127" t="n">
-        <v>2057.94</v>
+        <v>2054.429</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G127" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B128" t="n">
-        <v>2054.162</v>
+        <v>2054.069</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -4517,30 +4517,30 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="B129" t="n">
-        <v>2017.058</v>
+        <v>2023.611</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Radha Vembu</t>
+          <t>T.S. Kalyanaraman</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Business software</t>
+          <t>Jewelry</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4549,30 +4549,30 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B130" t="n">
-        <v>2013.065</v>
+        <v>2017.058</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>K. Dinesh</t>
+          <t>Radha Vembu</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Business software</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4581,30 +4581,30 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G130" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2086</v>
+        <v>2059</v>
       </c>
       <c r="B131" t="n">
-        <v>1997.884</v>
+        <v>2016.395</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T.S. Kalyanaraman</t>
+          <t>K. Dinesh</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Jewelry</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779090602162</v>
+        <v>1779104102169</v>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183065973</v>
       </c>
     </row>
     <row r="132">
@@ -4645,30 +4645,30 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="B133" t="n">
-        <v>1950.98</v>
+        <v>1952.485</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hemendra Kothari</t>
+          <t>Lalit Khaitan</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4677,30 +4677,30 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2151</v>
+        <v>2142</v>
       </c>
       <c r="B134" t="n">
-        <v>1944.772</v>
+        <v>1950.98</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lalit Khaitan</t>
+          <t>Hemendra Kothari</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G134" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="135">
@@ -4741,21 +4741,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B136" t="n">
-        <v>1916.917</v>
+        <v>1920.8</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B137" t="n">
-        <v>1893.939</v>
+        <v>1888.225</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="138">
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B139" t="n">
         <v>1853.32</v>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B140" t="n">
-        <v>1841.699</v>
+        <v>1843.48</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779090602162</v>
+        <v>1779104102170</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.71183067129</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2251</v>
+        <v>2258</v>
       </c>
       <c r="B141" t="n">
-        <v>1835.829</v>
+        <v>1831.051</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G141" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="B142" t="n">
         <v>1813.92</v>
@@ -4965,21 +4965,21 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B143" t="n">
-        <v>1806.911</v>
+        <v>1809.194</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -4997,13 +4997,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="144">
@@ -5011,7 +5011,7 @@
         <v>2320</v>
       </c>
       <c r="B144" t="n">
-        <v>1768.507</v>
+        <v>1766.869</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="145">
@@ -5043,16 +5043,16 @@
         <v>2327</v>
       </c>
       <c r="B145" t="n">
-        <v>1761.696</v>
+        <v>1760.675</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pawan Munjal</t>
+          <t>Banwari Lal Bawri</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5061,30 +5061,30 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2328</v>
+        <v>2333</v>
       </c>
       <c r="B146" t="n">
-        <v>1760.675</v>
+        <v>1755.532</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Banwari Lal Bawri</t>
+          <t>Pawan Munjal</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779090602162</v>
+        <v>1779103802108</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835773148</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2388</v>
+        <v>2396</v>
       </c>
       <c r="B148" t="n">
-        <v>1706.459</v>
+        <v>1699.828</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -5157,21 +5157,21 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G148" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2410</v>
+        <v>2415</v>
       </c>
       <c r="B149" t="n">
-        <v>1689.841</v>
+        <v>1684.006</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G149" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="B150" t="n">
-        <v>1683.057</v>
+        <v>1677.252</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5221,30 +5221,30 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B151" t="n">
-        <v>1680.313</v>
+        <v>1676.783</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Aloke Lohia</t>
+          <t>Shyam Bhartia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Petrochemicals</t>
+          <t>Pharmaceuticals, food</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5253,30 +5253,30 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="B152" t="n">
-        <v>1673.323</v>
+        <v>1674.745</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Viren Doshi</t>
+          <t>Aloke Lohia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Petrochemicals</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5285,30 +5285,30 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2430</v>
+        <v>2425</v>
       </c>
       <c r="B153" t="n">
-        <v>1667.389</v>
+        <v>1672.564</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Shyam Bhartia</t>
+          <t>Hari Bhartia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, food</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5317,30 +5317,30 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2433</v>
+        <v>2427</v>
       </c>
       <c r="B154" t="n">
-        <v>1663.379</v>
+        <v>1671.06</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hari Bhartia</t>
+          <t>Viren Doshi</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G154" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="155">
@@ -5363,16 +5363,16 @@
         <v>2434</v>
       </c>
       <c r="B155" t="n">
-        <v>1659.779</v>
+        <v>1664.253</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Motilal Oswal</t>
+          <t>Arvind Lal</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Medical diagnostics</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5381,30 +5381,30 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="B156" t="n">
-        <v>1658.87</v>
+        <v>1663.143</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Anand Burman</t>
+          <t>Motilal Oswal</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5413,30 +5413,30 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2457</v>
+        <v>2440</v>
       </c>
       <c r="B157" t="n">
-        <v>1644.184</v>
+        <v>1657.112</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Arvind Lal</t>
+          <t>Anand Burman</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Medical diagnostics</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G157" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="158">
@@ -5459,16 +5459,16 @@
         <v>2463</v>
       </c>
       <c r="B158" t="n">
-        <v>1638.595</v>
+        <v>1638.82</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Premchand Godha</t>
+          <t>Surjit Kumar Gupta</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Electrical equipment</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5477,30 +5477,30 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="B159" t="n">
-        <v>1635.093</v>
+        <v>1633.314</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Surjit Kumar Gupta</t>
+          <t>Premchand Godha</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Electrical equipment</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5509,30 +5509,30 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G159" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="B160" t="n">
-        <v>1607.901</v>
+        <v>1607.589</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Saroj Rani Gupta</t>
+          <t>R.G. Chandramogan</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Steel tubes</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5541,30 +5541,30 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2490</v>
+        <v>2495</v>
       </c>
       <c r="B161" t="n">
-        <v>1606.57</v>
+        <v>1602.739</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>R.G. Chandramogan</t>
+          <t>Saroj Rani Gupta</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Steel tubes</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5573,21 +5573,21 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G161" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="B162" t="n">
-        <v>1565.993</v>
+        <v>1568.294</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2540</v>
+        <v>2552</v>
       </c>
       <c r="B163" t="n">
-        <v>1563.974</v>
+        <v>1558.753</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -5637,30 +5637,30 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2551</v>
+        <v>2558</v>
       </c>
       <c r="B164" t="n">
-        <v>1560.286</v>
+        <v>1554.411</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sanjay Agarwal</t>
+          <t>Satish Reddy</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5669,30 +5669,30 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G164" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2553</v>
+        <v>2559</v>
       </c>
       <c r="B165" t="n">
-        <v>1559.846</v>
+        <v>1553.807</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Satish Reddy</t>
+          <t>Sanjay Agarwal</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5701,30 +5701,30 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G165" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="B166" t="n">
-        <v>1534.67</v>
+        <v>1534.485</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kamlesh Jain</t>
+          <t>Ronnie Screwvala</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Recycling</t>
+          <t>edtech, entertainment</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5733,30 +5733,30 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2597</v>
+        <v>2593</v>
       </c>
       <c r="B167" t="n">
-        <v>1528.57</v>
+        <v>1532.656</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ronnie Screwvala</t>
+          <t>D.V. Manjunatha</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>edtech, entertainment</t>
+          <t>Solar panels</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5765,30 +5765,30 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2622</v>
+        <v>2627</v>
       </c>
       <c r="B168" t="n">
-        <v>1508.694</v>
+        <v>1500</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>D.V. Manjunatha</t>
+          <t>Prasanna Sankar</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Solar panels</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5797,30 +5797,30 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G168" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2628</v>
+        <v>2638</v>
       </c>
       <c r="B169" t="n">
-        <v>1500</v>
+        <v>1499.185</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Prasanna Sankar</t>
+          <t>Manoj Upadhyay</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>solar energy</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="B170" t="n">
-        <v>1493.176</v>
+        <v>1494.058</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -5861,30 +5861,30 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2649</v>
+        <v>2656</v>
       </c>
       <c r="B171" t="n">
-        <v>1492.347</v>
+        <v>1485.365</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Manoj Upadhyay</t>
+          <t>Sekar Vembu</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>solar energy</t>
+          <t>Business software</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5893,30 +5893,30 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2657</v>
+        <v>2663</v>
       </c>
       <c r="B172" t="n">
-        <v>1485.365</v>
+        <v>1480.068</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sekar Vembu</t>
+          <t>Chaitanya Desai</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Business software</t>
+          <t>Electric cables</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5925,30 +5925,30 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G172" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2674</v>
+        <v>2663</v>
       </c>
       <c r="B173" t="n">
-        <v>1469.671</v>
+        <v>1480.068</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chaitanya Desai</t>
+          <t>Kushal Desai</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Electric cables</t>
+          <t>Electrical cables</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5957,30 +5957,30 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G173" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2674</v>
+        <v>2690</v>
       </c>
       <c r="B174" t="n">
-        <v>1469.671</v>
+        <v>1454.351</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Kushal Desai</t>
+          <t>Hitesh Doshi</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Electrical cables</t>
+          <t>Solar panels</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5989,25 +5989,25 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G174" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2689</v>
+        <v>2691</v>
       </c>
       <c r="B175" t="n">
-        <v>1456.345</v>
+        <v>1452.72</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hitesh Doshi</t>
+          <t>Pankaj Doshi</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6021,30 +6021,30 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G175" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2691</v>
+        <v>2696</v>
       </c>
       <c r="B176" t="n">
-        <v>1454.675</v>
+        <v>1448.537</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Pankaj Doshi</t>
+          <t>Chirayu Amin</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Solar panels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6053,30 +6053,30 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2704</v>
+        <v>2730</v>
       </c>
       <c r="B177" t="n">
-        <v>1440.731</v>
+        <v>1414.525</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chirayu Amin</t>
+          <t>Rajeev Gulati</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6085,30 +6085,30 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G177" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2730</v>
+        <v>2737</v>
       </c>
       <c r="B178" t="n">
-        <v>1414.525</v>
+        <v>1410.982</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Rajeev Gulati</t>
+          <t>Aditya Khemka</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Security solutions</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6117,30 +6117,30 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="B179" t="n">
-        <v>1409.921</v>
+        <v>1409.964</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Binny Bansal</t>
+          <t>Mofatraj Munot</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6149,30 +6149,30 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="B180" t="n">
-        <v>1407.631</v>
+        <v>1409.921</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Mofatraj Munot</t>
+          <t>Binny Bansal</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6181,30 +6181,30 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779090602162</v>
+        <v>1779103802109</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46160.5555805787</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2779</v>
+        <v>2765</v>
       </c>
       <c r="B181" t="n">
-        <v>1387.938</v>
+        <v>1397.551</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Kapil Bhatia</t>
+          <t>Shrikant Badve</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Aviation</t>
+          <t>auto parts</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6213,30 +6213,30 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G181" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2789</v>
+        <v>2770</v>
       </c>
       <c r="B182" t="n">
-        <v>1382.324</v>
+        <v>1393.31</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Shrikant Badve</t>
+          <t>Rajju Shroff</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>auto parts</t>
+          <t>Agrochemicals</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6245,30 +6245,30 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G182" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2795</v>
+        <v>2776</v>
       </c>
       <c r="B183" t="n">
-        <v>1378.199</v>
+        <v>1389.701</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Rajju Shroff</t>
+          <t>Kapil Bhatia</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Agrochemicals</t>
+          <t>Aviation</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6277,30 +6277,30 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G183" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2800</v>
+        <v>2804</v>
       </c>
       <c r="B184" t="n">
-        <v>1376.21</v>
+        <v>1372.472</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Habil Khorakiwala</t>
+          <t>Naresh Jain</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>pharmaceuticals</t>
+          <t>Auto components</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6309,30 +6309,30 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G184" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2807</v>
+        <v>2809</v>
       </c>
       <c r="B185" t="n">
-        <v>1371.724</v>
+        <v>1369.934</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Naresh Jain</t>
+          <t>Habil Khorakiwala</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Auto components</t>
+          <t>pharmaceuticals</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="186">
@@ -6373,30 +6373,30 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2822</v>
+        <v>2820</v>
       </c>
       <c r="B187" t="n">
-        <v>1358.151</v>
+        <v>1361.194</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Aditya Khemka</t>
+          <t>Vinod Saraf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Security solutions</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6405,21 +6405,21 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2839</v>
+        <v>2835</v>
       </c>
       <c r="B188" t="n">
-        <v>1340.91</v>
+        <v>1344.894</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -6437,30 +6437,30 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2845</v>
+        <v>2874</v>
       </c>
       <c r="B189" t="n">
-        <v>1338.049</v>
+        <v>1316.638</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Vinod Saraf</t>
+          <t>Deepinder Goyal</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Food delivery service</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G189" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="190">
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="191">
@@ -6533,30 +6533,30 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2925</v>
+        <v>2913</v>
       </c>
       <c r="B192" t="n">
-        <v>1287.787</v>
+        <v>1293.862</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deepinder Goyal</t>
+          <t>Kamlesh Jain</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Food delivery service</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6565,30 +6565,30 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2939</v>
+        <v>2943</v>
       </c>
       <c r="B193" t="n">
-        <v>1281.52</v>
+        <v>1276.294</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Onkar Kanwar</t>
+          <t>Aluru Jagadish Prasad</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Tires</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6597,30 +6597,30 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2945</v>
+        <v>2954</v>
       </c>
       <c r="B194" t="n">
-        <v>1275.441</v>
+        <v>1270.546</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Aluru Jagadish Prasad</t>
+          <t>Onkar Kanwar</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Tires</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6629,30 +6629,30 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G194" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2961</v>
+        <v>2955</v>
       </c>
       <c r="B195" t="n">
-        <v>1264.516</v>
+        <v>1270.507</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kirit Doshi</t>
+          <t>Irfan Razack</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6661,25 +6661,25 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G195" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2968</v>
+        <v>2956</v>
       </c>
       <c r="B196" t="n">
-        <v>1255.644</v>
+        <v>1270.493</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Irfan Razack</t>
+          <t>Noaman Razack</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6693,25 +6693,25 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2969</v>
+        <v>2956</v>
       </c>
       <c r="B197" t="n">
-        <v>1255.63</v>
+        <v>1270.493</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Noaman Razack</t>
+          <t>Rezwan Razack</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6725,30 +6725,30 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G197" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2969</v>
+        <v>2963</v>
       </c>
       <c r="B198" t="n">
-        <v>1255.63</v>
+        <v>1264.62</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Rezwan Razack</t>
+          <t>Kirit Doshi</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="199">
@@ -6771,16 +6771,16 @@
         <v>2986</v>
       </c>
       <c r="B199" t="n">
-        <v>1246.287</v>
+        <v>1246.285</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ramesh Kunhikannan</t>
+          <t>Subbamma Jasti</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronics </t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>3001</v>
+        <v>2994</v>
       </c>
       <c r="B200" t="n">
-        <v>1234.428</v>
+        <v>1237.687</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -6821,30 +6821,30 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G200" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3004</v>
+        <v>3015</v>
       </c>
       <c r="B201" t="n">
-        <v>1232.452</v>
+        <v>1226.325</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Subbamma Jasti</t>
+          <t>Ramesh Kunhikannan</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t xml:space="preserve">Electronics </t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6853,30 +6853,30 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3006</v>
+        <v>3020</v>
       </c>
       <c r="B202" t="n">
-        <v>1229.49</v>
+        <v>1222.617</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Deepak Mehta</t>
+          <t>Alakh Pandey</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Edtech</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6885,13 +6885,13 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G202" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="203">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Alakh Pandey</t>
+          <t>Prateek Boob</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6917,30 +6917,30 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3020</v>
+        <v>3028</v>
       </c>
       <c r="B204" t="n">
-        <v>1222.617</v>
+        <v>1219.798</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Prateek Boob</t>
+          <t>Deepak Mehta</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3035</v>
+        <v>3054</v>
       </c>
       <c r="B205" t="n">
-        <v>1214.058</v>
+        <v>1207.273</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -6981,21 +6981,21 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3099</v>
+        <v>3105</v>
       </c>
       <c r="B206" t="n">
-        <v>1175.807</v>
+        <v>1172.514</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G206" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,30 +7045,30 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3144</v>
+        <v>3148</v>
       </c>
       <c r="B208" t="n">
-        <v>1150.269</v>
+        <v>1146.05</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bhaskara Rao Bollineni</t>
+          <t>Naresh Trehan</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Hospitals</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7077,30 +7077,30 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3158</v>
+        <v>3176</v>
       </c>
       <c r="B209" t="n">
-        <v>1142.121</v>
+        <v>1132.544</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Naresh Trehan</t>
+          <t>Sachin Bansal</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Hospitals</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7109,30 +7109,30 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G209" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3179</v>
+        <v>3188</v>
       </c>
       <c r="B210" t="n">
-        <v>1132.544</v>
+        <v>1126.872</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sachin Bansal</t>
+          <t>Bhaskara Rao Bollineni</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3183</v>
+        <v>3194</v>
       </c>
       <c r="B211" t="n">
-        <v>1129.678</v>
+        <v>1122.12</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -7173,21 +7173,21 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G211" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3203</v>
+        <v>3209</v>
       </c>
       <c r="B212" t="n">
-        <v>1117.064</v>
+        <v>1111.893</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G212" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="213">
@@ -7219,7 +7219,7 @@
         <v>3211</v>
       </c>
       <c r="B213" t="n">
-        <v>1113.057</v>
+        <v>1111.63</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="B214" t="n">
-        <v>1099.956</v>
+        <v>1102.434</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -7269,30 +7269,30 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3267</v>
+        <v>3244</v>
       </c>
       <c r="B215" t="n">
-        <v>1081.614</v>
+        <v>1093.128</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Chandubhai Virani</t>
+          <t>Vijay Shekhar Sharma</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>financial technology</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7301,25 +7301,25 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G215" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3267</v>
+        <v>3265</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Kanjibhai Virani</t>
+          <t>Chandubhai Virani</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -7333,30 +7333,30 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3269</v>
+        <v>3265</v>
       </c>
       <c r="B217" t="n">
-        <v>1081.42</v>
+        <v>1081.614</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Vijay Shekhar Sharma</t>
+          <t>Kanjibhai Virani</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>financial technology</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7365,21 +7365,21 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3288</v>
+        <v>3282</v>
       </c>
       <c r="B218" t="n">
-        <v>1067.125</v>
+        <v>1070.911</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3293</v>
+        <v>3286</v>
       </c>
       <c r="B219" t="n">
-        <v>1065.578</v>
+        <v>1069.408</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3309</v>
+        <v>3301</v>
       </c>
       <c r="B220" t="n">
-        <v>1050.313</v>
+        <v>1059.625</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G220" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="222">
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3356</v>
+        <v>3365</v>
       </c>
       <c r="B223" t="n">
-        <v>1012.107</v>
+        <v>1006.935</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
     <row r="224">
@@ -7571,7 +7571,7 @@
         <v>3391</v>
       </c>
       <c r="B224" t="n">
-        <v>979.436</v>
+        <v>984.373</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779090302155</v>
+        <v>1779103802109</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46160.55210827546</v>
+        <v>46160.70835774305</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779104102168</v>
+        <v>1779115802229</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46160.71183064815</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779104102168</v>
+        <v>1779115802229</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46160.71183064815</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="4">
@@ -549,21 +549,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779104102168</v>
+        <v>1779115802229</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46160.71183064815</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="n">
-        <v>29151.569</v>
+        <v>29457.932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779104102168</v>
+        <v>1779115802229</v>
       </c>
       <c r="G5" t="n">
-        <v>29.15</v>
+        <v>29.46</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46160.71183064815</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="7">
@@ -645,18 +645,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" t="n">
         <v>25354.315</v>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>212</v>
       </c>
       <c r="B11" t="n">
-        <v>14095.831</v>
+        <v>14135.523</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G11" t="n">
-        <v>14.1</v>
+        <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="12">
@@ -805,18 +805,18 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B13" t="n">
         <v>12471.668</v>
@@ -837,18 +837,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B14" t="n">
         <v>11445.012</v>
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B15" t="n">
         <v>10376.047</v>
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="16">
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B17" t="n">
-        <v>9223.575999999999</v>
+        <v>9249.528</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B18" t="n">
-        <v>9200.481</v>
+        <v>9226.433000000001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,18 +997,18 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B19" t="n">
         <v>8387.036</v>
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B20" t="n">
         <v>8252.09</v>
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B21" t="n">
         <v>7877.188</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="23">
@@ -1157,18 +1157,18 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B24" t="n">
         <v>7608.8</v>
@@ -1189,18 +1189,18 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B25" t="n">
         <v>7289.86</v>
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B26" t="n">
         <v>6473.386</v>
@@ -1253,18 +1253,18 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B27" t="n">
         <v>6149.447</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="28">
@@ -1317,18 +1317,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1349,18 +1349,18 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B30" t="n">
         <v>5453.212</v>
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B31" t="n">
         <v>5177.898</v>
@@ -1413,18 +1413,18 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B32" t="n">
         <v>5177.898</v>
@@ -1445,18 +1445,18 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B33" t="n">
         <v>5150.844</v>
@@ -1477,18 +1477,18 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B34" t="n">
         <v>5084.179</v>
@@ -1509,18 +1509,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B35" t="n">
         <v>5071.275</v>
@@ -1541,18 +1541,18 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B36" t="n">
         <v>5050.542</v>
@@ -1573,18 +1573,18 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B37" t="n">
         <v>5050.537</v>
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B38" t="n">
         <v>4996.846</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="39">
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B40" t="n">
         <v>4961.495</v>
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B41" t="n">
         <v>4953.328</v>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="42">
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B43" t="n">
         <v>4651.997</v>
@@ -1797,18 +1797,18 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B44" t="n">
         <v>4599.875</v>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B45" t="n">
         <v>4394.112</v>
@@ -1861,18 +1861,18 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B46" t="n">
         <v>4371.578</v>
@@ -1893,18 +1893,18 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B47" t="n">
         <v>4311.644</v>
@@ -1925,18 +1925,18 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B48" t="n">
         <v>4287.14</v>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B49" t="n">
         <v>4091.609</v>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="B51" t="n">
         <v>3920.534</v>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B52" t="n">
         <v>3837.168</v>
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B53" t="n">
         <v>3812.24</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779104102169</v>
+        <v>1779115802229</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724802084</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="56">
@@ -2213,18 +2213,18 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B57" t="n">
         <v>3692.361</v>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B58" t="n">
-        <v>3680.841</v>
+        <v>3679.037</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,18 +2277,18 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G58" t="n">
         <v>3.68</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="B59" t="n">
         <v>3542.882</v>
@@ -2309,18 +2309,18 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="B60" t="n">
         <v>3531.797</v>
@@ -2341,18 +2341,18 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="B61" t="n">
         <v>3517.715</v>
@@ -2373,18 +2373,18 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="B62" t="n">
         <v>3494.663</v>
@@ -2405,18 +2405,18 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B63" t="n">
         <v>3463.696</v>
@@ -2437,18 +2437,18 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="B64" t="n">
         <v>3461.525</v>
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="B65" t="n">
         <v>3457.731</v>
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B66" t="n">
         <v>3437.408</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="67">
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="B68" t="n">
         <v>3358.115</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="B70" t="n">
         <v>3221.232</v>
@@ -2661,18 +2661,18 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="B71" t="n">
         <v>3212.603</v>
@@ -2693,18 +2693,18 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B72" t="n">
         <v>3152.624</v>
@@ -2725,18 +2725,18 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B73" t="n">
         <v>3113.024</v>
@@ -2757,18 +2757,18 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B74" t="n">
         <v>3085.258</v>
@@ -2789,18 +2789,18 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B75" t="n">
         <v>3068.446</v>
@@ -2821,18 +2821,18 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -2853,18 +2853,18 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B77" t="n">
         <v>3047.215</v>
@@ -2885,18 +2885,18 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B78" t="n">
         <v>3011.155</v>
@@ -2917,18 +2917,18 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B79" t="n">
         <v>3011.141</v>
@@ -2949,18 +2949,18 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B80" t="n">
         <v>3003.735</v>
@@ -2981,18 +2981,18 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B81" t="n">
         <v>2991.225</v>
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B82" t="n">
         <v>2953.701</v>
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="B83" t="n">
         <v>2946.291</v>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="B85" t="n">
         <v>2835.87</v>
@@ -3141,18 +3141,18 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B86" t="n">
         <v>2819.016</v>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,18 +3205,18 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="B88" t="n">
         <v>2749.231</v>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="B89" t="n">
         <v>2749.231</v>
@@ -3269,18 +3269,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1539</v>
+        <v>1544</v>
       </c>
       <c r="B90" t="n">
         <v>2744.293</v>
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="B91" t="n">
         <v>2717.279</v>
@@ -3333,18 +3333,18 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B92" t="n">
         <v>2707.811</v>
@@ -3365,18 +3365,18 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B93" t="n">
         <v>2627.533</v>
@@ -3397,18 +3397,18 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B94" t="n">
         <v>2622.743</v>
@@ -3429,18 +3429,18 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B95" t="n">
         <v>2622.743</v>
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B96" t="n">
         <v>2622.743</v>
@@ -3493,18 +3493,18 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B97" t="n">
         <v>2622.743</v>
@@ -3525,18 +3525,18 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B98" t="n">
         <v>2587.632</v>
@@ -3557,18 +3557,18 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B99" t="n">
         <v>2552.876</v>
@@ -3589,18 +3589,18 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B100" t="n">
         <v>2551.171</v>
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B101" t="n">
         <v>2515.184</v>
@@ -3653,18 +3653,18 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B102" t="n">
         <v>2494.136</v>
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="103">
@@ -3717,18 +3717,18 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="B104" t="n">
         <v>2465.589</v>
@@ -3749,18 +3749,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B105" t="n">
         <v>2457.642</v>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="106">
@@ -3813,18 +3813,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="B107" t="n">
         <v>2410.942</v>
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B108" t="n">
         <v>2366.47</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1773</v>
+        <v>1779</v>
       </c>
       <c r="B109" t="n">
         <v>2355.803</v>
@@ -3909,18 +3909,18 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="B110" t="n">
         <v>2338.44</v>
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B111" t="n">
         <v>2328.854</v>
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B113" t="n">
         <v>2270.559</v>
@@ -4037,18 +4037,18 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="B114" t="n">
         <v>2250.673</v>
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B115" t="n">
         <v>2243.02</v>
@@ -4101,18 +4101,18 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B116" t="n">
         <v>2237.983</v>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="B117" t="n">
         <v>2203.177</v>
@@ -4165,18 +4165,18 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="B118" t="n">
         <v>2189.241</v>
@@ -4197,13 +4197,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="119">
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1929</v>
+        <v>1936</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B121" t="n">
         <v>2142.349</v>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="122">
@@ -4325,18 +4325,18 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B123" t="n">
         <v>2101.476</v>
@@ -4357,18 +4357,18 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B124" t="n">
         <v>2100.998</v>
@@ -4389,18 +4389,18 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="B126" t="n">
         <v>2091.564</v>
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B127" t="n">
         <v>2054.429</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B128" t="n">
         <v>2054.069</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2051</v>
+        <v>2058</v>
       </c>
       <c r="B129" t="n">
         <v>2023.611</v>
@@ -4549,18 +4549,18 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="B130" t="n">
         <v>2017.058</v>
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="B131" t="n">
         <v>2016.395</v>
@@ -4613,18 +4613,18 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779104102169</v>
+        <v>1779115802230</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46160.71183065973</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2115</v>
+        <v>2123</v>
       </c>
       <c r="B132" t="n">
         <v>1971.957</v>
@@ -4645,18 +4645,18 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2138</v>
+        <v>2145</v>
       </c>
       <c r="B133" t="n">
         <v>1952.485</v>
@@ -4677,18 +4677,18 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2142</v>
+        <v>2149</v>
       </c>
       <c r="B134" t="n">
         <v>1950.98</v>
@@ -4709,18 +4709,18 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="B135" t="n">
         <v>1943.862</v>
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="B136" t="n">
         <v>1920.8</v>
@@ -4773,18 +4773,18 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2204</v>
+        <v>2209</v>
       </c>
       <c r="B137" t="n">
         <v>1888.225</v>
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2218</v>
+        <v>2222</v>
       </c>
       <c r="B138" t="n">
         <v>1871.373</v>
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="B139" t="n">
         <v>1853.32</v>
@@ -4869,18 +4869,18 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2243</v>
+        <v>2250</v>
       </c>
       <c r="B140" t="n">
         <v>1843.48</v>
@@ -4901,18 +4901,18 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779104102170</v>
+        <v>1779115802230</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46160.71183067129</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2258</v>
+        <v>2263</v>
       </c>
       <c r="B141" t="n">
         <v>1831.051</v>
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2273</v>
+        <v>2278</v>
       </c>
       <c r="B142" t="n">
         <v>1813.92</v>
@@ -4965,18 +4965,18 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="B143" t="n">
         <v>1809.194</v>
@@ -4997,18 +4997,18 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="B144" t="n">
         <v>1766.869</v>
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="B145" t="n">
         <v>1760.675</v>
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="B146" t="n">
         <v>1755.532</v>
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779103802108</v>
+        <v>1779115802230</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46160.70835773148</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="B148" t="n">
         <v>1699.828</v>
@@ -5157,18 +5157,18 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="B149" t="n">
         <v>1684.006</v>
@@ -5189,18 +5189,18 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="B150" t="n">
         <v>1677.252</v>
@@ -5221,18 +5221,18 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B151" t="n">
         <v>1676.783</v>
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B152" t="n">
         <v>1674.745</v>
@@ -5285,18 +5285,18 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="B153" t="n">
         <v>1672.564</v>
@@ -5317,18 +5317,18 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2427</v>
+        <v>2431</v>
       </c>
       <c r="B154" t="n">
         <v>1671.06</v>
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="B155" t="n">
         <v>1664.253</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="B156" t="n">
         <v>1663.143</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2440</v>
+        <v>2445</v>
       </c>
       <c r="B157" t="n">
         <v>1657.112</v>
@@ -5445,18 +5445,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="B158" t="n">
         <v>1638.82</v>
@@ -5477,18 +5477,18 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B159" t="n">
         <v>1633.314</v>
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="B160" t="n">
         <v>1607.589</v>
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="161">
@@ -5573,18 +5573,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779103802109</v>
+        <v>1779115802230</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84724803241</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="B162" t="n">
         <v>1568.294</v>
@@ -5605,18 +5605,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2552</v>
+        <v>2557</v>
       </c>
       <c r="B163" t="n">
         <v>1558.753</v>
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2558</v>
+        <v>2564</v>
       </c>
       <c r="B164" t="n">
         <v>1554.411</v>
@@ -5669,18 +5669,18 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2559</v>
+        <v>2566</v>
       </c>
       <c r="B165" t="n">
         <v>1553.807</v>
@@ -5701,18 +5701,18 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="B166" t="n">
         <v>1534.485</v>
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="B167" t="n">
         <v>1532.656</v>
@@ -5765,18 +5765,18 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="B168" t="n">
         <v>1500</v>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2638</v>
+        <v>2643</v>
       </c>
       <c r="B169" t="n">
         <v>1499.185</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2644</v>
+        <v>2649</v>
       </c>
       <c r="B170" t="n">
         <v>1494.058</v>
@@ -5861,18 +5861,18 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2656</v>
+        <v>2659</v>
       </c>
       <c r="B171" t="n">
         <v>1485.365</v>
@@ -5893,18 +5893,18 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="B172" t="n">
         <v>1480.068</v>
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="B173" t="n">
         <v>1480.068</v>
@@ -5957,18 +5957,18 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="B174" t="n">
         <v>1454.351</v>
@@ -5989,18 +5989,18 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2691</v>
+        <v>2695</v>
       </c>
       <c r="B175" t="n">
         <v>1452.72</v>
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2696</v>
+        <v>2699</v>
       </c>
       <c r="B176" t="n">
         <v>1448.537</v>
@@ -6053,18 +6053,18 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2730</v>
+        <v>2736</v>
       </c>
       <c r="B177" t="n">
         <v>1414.525</v>
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="B178" t="n">
         <v>1410.982</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2740</v>
+        <v>2743</v>
       </c>
       <c r="B179" t="n">
         <v>1409.964</v>
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2741</v>
+        <v>2744</v>
       </c>
       <c r="B180" t="n">
         <v>1409.921</v>
@@ -6181,18 +6181,18 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2765</v>
+        <v>2771</v>
       </c>
       <c r="B181" t="n">
         <v>1397.551</v>
@@ -6213,18 +6213,18 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2770</v>
+        <v>2776</v>
       </c>
       <c r="B182" t="n">
         <v>1393.31</v>
@@ -6245,18 +6245,18 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2776</v>
+        <v>2781</v>
       </c>
       <c r="B183" t="n">
         <v>1389.701</v>
@@ -6277,18 +6277,18 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2804</v>
+        <v>2809</v>
       </c>
       <c r="B184" t="n">
         <v>1372.472</v>
@@ -6309,18 +6309,18 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2809</v>
+        <v>2814</v>
       </c>
       <c r="B185" t="n">
         <v>1369.934</v>
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2818</v>
+        <v>2821</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,18 +6373,18 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2820</v>
+        <v>2823</v>
       </c>
       <c r="B187" t="n">
         <v>1361.194</v>
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="B188" t="n">
         <v>1344.894</v>
@@ -6437,18 +6437,18 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2874</v>
+        <v>2878</v>
       </c>
       <c r="B189" t="n">
         <v>1316.638</v>
@@ -6469,18 +6469,18 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2892</v>
+        <v>2897</v>
       </c>
       <c r="B190" t="n">
         <v>1304.387</v>
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2907</v>
+        <v>2914</v>
       </c>
       <c r="B191" t="n">
         <v>1297.945</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2913</v>
+        <v>2922</v>
       </c>
       <c r="B192" t="n">
         <v>1293.862</v>
@@ -6565,18 +6565,18 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2943</v>
+        <v>2948</v>
       </c>
       <c r="B193" t="n">
         <v>1276.294</v>
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2954</v>
+        <v>2958</v>
       </c>
       <c r="B194" t="n">
         <v>1270.546</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2955</v>
+        <v>2959</v>
       </c>
       <c r="B195" t="n">
         <v>1270.507</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2956</v>
+        <v>2960</v>
       </c>
       <c r="B196" t="n">
         <v>1270.493</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2956</v>
+        <v>2960</v>
       </c>
       <c r="B197" t="n">
         <v>1270.493</v>
@@ -6725,18 +6725,18 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2963</v>
+        <v>2968</v>
       </c>
       <c r="B198" t="n">
         <v>1264.62</v>
@@ -6757,18 +6757,18 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2986</v>
+        <v>2988</v>
       </c>
       <c r="B199" t="n">
         <v>1246.285</v>
@@ -6789,18 +6789,18 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2994</v>
+        <v>2996</v>
       </c>
       <c r="B200" t="n">
         <v>1237.687</v>
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="B201" t="n">
         <v>1226.325</v>
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3020</v>
+        <v>3022</v>
       </c>
       <c r="B202" t="n">
         <v>1222.617</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3020</v>
+        <v>3022</v>
       </c>
       <c r="B203" t="n">
         <v>1222.617</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3028</v>
+        <v>3030</v>
       </c>
       <c r="B204" t="n">
         <v>1219.798</v>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="205">
@@ -6981,18 +6981,18 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3105</v>
+        <v>3110</v>
       </c>
       <c r="B206" t="n">
         <v>1172.514</v>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3135</v>
+        <v>3141</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3148</v>
+        <v>3152</v>
       </c>
       <c r="B208" t="n">
         <v>1146.05</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B209" t="n">
         <v>1132.544</v>
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="210">
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3194</v>
+        <v>3196</v>
       </c>
       <c r="B211" t="n">
         <v>1122.12</v>
@@ -7173,18 +7173,18 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3209</v>
+        <v>3212</v>
       </c>
       <c r="B212" t="n">
         <v>1111.893</v>
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3211</v>
+        <v>3214</v>
       </c>
       <c r="B213" t="n">
         <v>1111.63</v>
@@ -7237,18 +7237,18 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3226</v>
+        <v>3229</v>
       </c>
       <c r="B214" t="n">
         <v>1102.434</v>
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3244</v>
+        <v>3252</v>
       </c>
       <c r="B215" t="n">
         <v>1093.128</v>
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3265</v>
+        <v>3270</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3265</v>
+        <v>3270</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
@@ -7365,18 +7365,18 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3282</v>
+        <v>3285</v>
       </c>
       <c r="B218" t="n">
         <v>1070.911</v>
@@ -7397,18 +7397,18 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3286</v>
+        <v>3290</v>
       </c>
       <c r="B219" t="n">
         <v>1069.408</v>
@@ -7429,18 +7429,18 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="B220" t="n">
         <v>1059.625</v>
@@ -7461,18 +7461,18 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -7493,18 +7493,18 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -7525,18 +7525,18 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3365</v>
+        <v>3368</v>
       </c>
       <c r="B223" t="n">
         <v>1006.935</v>
@@ -7557,18 +7557,18 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="B224" t="n">
         <v>984.373</v>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779103802109</v>
+        <v>1779115503711</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46160.70835774305</v>
+        <v>46160.84379295139</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="4">
@@ -549,21 +549,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>29457.932</v>
+        <v>29501.632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G5" t="n">
-        <v>29.46</v>
+        <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="10">
@@ -741,21 +741,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B11" t="n">
-        <v>14135.523</v>
+        <v>14139.885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,18 +773,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B12" t="n">
         <v>13062.151</v>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="13">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="14">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="15">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="16">
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B17" t="n">
-        <v>9249.528</v>
+        <v>9252.380999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="18">
@@ -979,7 +979,7 @@
         <v>375</v>
       </c>
       <c r="B18" t="n">
-        <v>9226.433000000001</v>
+        <v>9229.285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="19">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B20" t="n">
         <v>8252.09</v>
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B21" t="n">
         <v>7877.188</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="25">
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B26" t="n">
         <v>6473.386</v>
@@ -1253,18 +1253,18 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B27" t="n">
         <v>6149.447</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="28">
@@ -1317,18 +1317,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="30">
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B31" t="n">
         <v>5177.898</v>
@@ -1413,18 +1413,18 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B32" t="n">
         <v>5177.898</v>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="37">
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B38" t="n">
         <v>4996.846</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="39">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="40">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="41">
@@ -1733,18 +1733,18 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B42" t="n">
         <v>4695.998</v>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="43">
@@ -1797,18 +1797,18 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B44" t="n">
         <v>4599.875</v>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B45" t="n">
         <v>4394.112</v>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="47">
@@ -1925,18 +1925,18 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B48" t="n">
         <v>4287.14</v>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B49" t="n">
         <v>4091.609</v>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B51" t="n">
         <v>3920.534</v>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="52">
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B53" t="n">
         <v>3812.24</v>
@@ -2117,18 +2117,18 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B54" t="n">
         <v>3742.953</v>
@@ -2149,18 +2149,18 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779115802229</v>
+        <v>1779124802267</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46160.84724802084</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B55" t="n">
         <v>3742.915</v>
@@ -2181,18 +2181,18 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B56" t="n">
         <v>3742.915</v>
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="57">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="58">
@@ -2259,7 +2259,7 @@
         <v>1166</v>
       </c>
       <c r="B58" t="n">
-        <v>3679.037</v>
+        <v>3674.76</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,18 +2277,18 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G58" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B59" t="n">
         <v>3542.882</v>
@@ -2309,18 +2309,18 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B60" t="n">
         <v>3531.797</v>
@@ -2341,18 +2341,18 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B61" t="n">
         <v>3517.715</v>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="63">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="64">
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B65" t="n">
         <v>3457.731</v>
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B66" t="n">
         <v>3437.408</v>
@@ -2533,18 +2533,18 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B67" t="n">
         <v>3426.048</v>
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B68" t="n">
         <v>3358.115</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="71">
@@ -2693,18 +2693,18 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B72" t="n">
         <v>3152.624</v>
@@ -2725,18 +2725,18 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B73" t="n">
         <v>3113.024</v>
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="74">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="75">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="76">
@@ -2853,18 +2853,18 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B77" t="n">
         <v>3047.215</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="80">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="81">
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B82" t="n">
         <v>2953.701</v>
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B83" t="n">
         <v>2946.291</v>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="84">
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B85" t="n">
         <v>2835.87</v>
@@ -3141,18 +3141,18 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="B86" t="n">
         <v>2819.016</v>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="87">
@@ -3205,18 +3205,18 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B88" t="n">
         <v>2749.231</v>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B89" t="n">
         <v>2749.231</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="90">
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B91" t="n">
         <v>2717.279</v>
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="92">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="93">
@@ -3397,18 +3397,18 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B94" t="n">
         <v>2622.743</v>
@@ -3429,18 +3429,18 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B95" t="n">
         <v>2622.743</v>
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B96" t="n">
         <v>2622.743</v>
@@ -3493,18 +3493,18 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B97" t="n">
         <v>2622.743</v>
@@ -3525,18 +3525,18 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B98" t="n">
         <v>2587.632</v>
@@ -3557,18 +3557,18 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B99" t="n">
         <v>2552.876</v>
@@ -3589,18 +3589,18 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B100" t="n">
         <v>2551.171</v>
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B101" t="n">
         <v>2515.184</v>
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="102">
@@ -3685,18 +3685,18 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B103" t="n">
         <v>2490.279</v>
@@ -3717,18 +3717,18 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B104" t="n">
         <v>2465.589</v>
@@ -3749,18 +3749,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B105" t="n">
         <v>2457.642</v>
@@ -3781,18 +3781,18 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B106" t="n">
         <v>2435.956</v>
@@ -3813,18 +3813,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="B107" t="n">
         <v>2410.942</v>
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B108" t="n">
         <v>2366.47</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="B109" t="n">
         <v>2355.803</v>
@@ -3909,18 +3909,18 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="B110" t="n">
         <v>2338.44</v>
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1797</v>
+        <v>1793</v>
       </c>
       <c r="B111" t="n">
         <v>2328.854</v>
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B113" t="n">
         <v>2270.559</v>
@@ -4037,18 +4037,18 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="B114" t="n">
         <v>2250.673</v>
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B115" t="n">
         <v>2243.02</v>
@@ -4101,18 +4101,18 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B116" t="n">
         <v>2237.983</v>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B117" t="n">
         <v>2203.177</v>
@@ -4165,18 +4165,18 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="B118" t="n">
         <v>2189.241</v>
@@ -4197,18 +4197,18 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="B119" t="n">
         <v>2182.036</v>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B121" t="n">
         <v>2142.349</v>
@@ -4293,18 +4293,18 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B122" t="n">
         <v>2105.407</v>
@@ -4325,18 +4325,18 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B123" t="n">
         <v>2101.476</v>
@@ -4357,18 +4357,18 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B124" t="n">
         <v>2100.998</v>
@@ -4389,18 +4389,18 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B126" t="n">
         <v>2091.564</v>
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B127" t="n">
         <v>2054.429</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B128" t="n">
         <v>2054.069</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B129" t="n">
         <v>2023.611</v>
@@ -4549,18 +4549,18 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="B130" t="n">
         <v>2017.058</v>
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="B131" t="n">
         <v>2016.395</v>
@@ -4613,18 +4613,18 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="B132" t="n">
         <v>1971.957</v>
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="133">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="134">
@@ -4709,18 +4709,18 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B135" t="n">
         <v>1943.862</v>
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B136" t="n">
         <v>1920.8</v>
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="137">
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B138" t="n">
         <v>1871.373</v>
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B139" t="n">
         <v>1853.32</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="140">
@@ -4901,18 +4901,18 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B141" t="n">
         <v>1831.051</v>
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="B142" t="n">
         <v>1813.92</v>
@@ -4965,18 +4965,18 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B143" t="n">
         <v>1809.194</v>
@@ -4997,18 +4997,18 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="B144" t="n">
         <v>1766.869</v>
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B145" t="n">
         <v>1760.675</v>
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="146">
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="B148" t="n">
         <v>1699.828</v>
@@ -5157,18 +5157,18 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="B149" t="n">
         <v>1684.006</v>
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="150">
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="151">
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="B152" t="n">
         <v>1674.745</v>
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="154">
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="B155" t="n">
         <v>1664.253</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="B156" t="n">
         <v>1663.143</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="B157" t="n">
         <v>1657.112</v>
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="158">
@@ -5477,18 +5477,18 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="B159" t="n">
         <v>1633.314</v>
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="B160" t="n">
         <v>1607.589</v>
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="161">
@@ -5573,18 +5573,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779115802230</v>
+        <v>1779124802267</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46160.84724803241</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B162" t="n">
         <v>1568.294</v>
@@ -5605,18 +5605,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B163" t="n">
         <v>1558.753</v>
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="B164" t="n">
         <v>1554.411</v>
@@ -5669,18 +5669,18 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2566</v>
+        <v>2562</v>
       </c>
       <c r="B165" t="n">
         <v>1553.807</v>
@@ -5701,18 +5701,18 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="B166" t="n">
         <v>1534.485</v>
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="B167" t="n">
         <v>1532.656</v>
@@ -5765,18 +5765,18 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="B168" t="n">
         <v>1500</v>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="B169" t="n">
         <v>1499.185</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B170" t="n">
         <v>1494.058</v>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="171">
@@ -5893,18 +5893,18 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="B172" t="n">
         <v>1480.068</v>
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="B173" t="n">
         <v>1480.068</v>
@@ -5957,18 +5957,18 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="B174" t="n">
         <v>1454.351</v>
@@ -5989,18 +5989,18 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B175" t="n">
         <v>1452.72</v>
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="B176" t="n">
         <v>1448.537</v>
@@ -6053,18 +6053,18 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="B177" t="n">
         <v>1414.525</v>
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B178" t="n">
         <v>1410.982</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="B179" t="n">
         <v>1409.964</v>
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="B180" t="n">
         <v>1409.921</v>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="181">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="182">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="183">
@@ -6277,18 +6277,18 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="B184" t="n">
         <v>1372.472</v>
@@ -6309,18 +6309,18 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2814</v>
+        <v>2811</v>
       </c>
       <c r="B185" t="n">
         <v>1369.934</v>
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,18 +6373,18 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="B187" t="n">
         <v>1361.194</v>
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2841</v>
+        <v>2838</v>
       </c>
       <c r="B188" t="n">
         <v>1344.894</v>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="189">
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="190">
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="B191" t="n">
         <v>1297.945</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2922</v>
+        <v>2919</v>
       </c>
       <c r="B192" t="n">
         <v>1293.862</v>
@@ -6565,18 +6565,18 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2948</v>
+        <v>2944</v>
       </c>
       <c r="B193" t="n">
         <v>1276.294</v>
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2958</v>
+        <v>2955</v>
       </c>
       <c r="B194" t="n">
         <v>1270.546</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="B195" t="n">
         <v>1270.507</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="B196" t="n">
         <v>1270.493</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="B197" t="n">
         <v>1270.493</v>
@@ -6725,18 +6725,18 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2968</v>
+        <v>2963</v>
       </c>
       <c r="B198" t="n">
         <v>1264.62</v>
@@ -6757,18 +6757,18 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="B199" t="n">
         <v>1246.285</v>
@@ -6789,18 +6789,18 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="B200" t="n">
         <v>1237.687</v>
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="B201" t="n">
         <v>1226.325</v>
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="B202" t="n">
         <v>1222.617</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="B203" t="n">
         <v>1222.617</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B204" t="n">
         <v>1219.798</v>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="205">
@@ -6981,18 +6981,18 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3110</v>
+        <v>3107</v>
       </c>
       <c r="B206" t="n">
         <v>1172.514</v>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="B208" t="n">
         <v>1146.05</v>
@@ -7077,13 +7077,13 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="209">
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B210" t="n">
         <v>1126.872</v>
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="B211" t="n">
         <v>1122.12</v>
@@ -7173,18 +7173,18 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="B212" t="n">
         <v>1111.893</v>
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B213" t="n">
         <v>1111.63</v>
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="214">
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3252</v>
+        <v>3249</v>
       </c>
       <c r="B215" t="n">
         <v>1093.128</v>
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="218">
@@ -7397,18 +7397,18 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="B219" t="n">
         <v>1069.408</v>
@@ -7429,13 +7429,13 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="220">
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="222">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="223">
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
     <row r="224">
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779115503711</v>
+        <v>1779124802267</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46160.84379295139</v>
+        <v>46160.95141512732</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779124802267</v>
+        <v>1779131402394</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780548611</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779124802267</v>
+        <v>1779131402394</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780548611</v>
       </c>
     </row>
     <row r="4">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779124802267</v>
+        <v>1779131402394</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780548611</v>
       </c>
     </row>
     <row r="5">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="8">
@@ -677,18 +677,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" t="n">
         <v>21391.106</v>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="11">
@@ -773,18 +773,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B12" t="n">
         <v>13062.151</v>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="13">
@@ -837,18 +837,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B14" t="n">
         <v>11445.012</v>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="15">
@@ -901,18 +901,18 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B16" t="n">
         <v>10139.4</v>
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B17" t="n">
         <v>9252.380999999999</v>
@@ -965,18 +965,18 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B18" t="n">
         <v>9229.285</v>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="19">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B20" t="n">
         <v>8252.09</v>
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B21" t="n">
         <v>7877.188</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="23">
@@ -1157,18 +1157,18 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B24" t="n">
         <v>7608.8</v>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="25">
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B26" t="n">
         <v>6473.386</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="27">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="28">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="30">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="32">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="37">
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B38" t="n">
         <v>4996.846</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="39">
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B40" t="n">
         <v>4961.495</v>
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B41" t="n">
         <v>4953.328</v>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="42">
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B43" t="n">
         <v>4651.997</v>
@@ -1797,18 +1797,18 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B44" t="n">
         <v>4599.875</v>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B45" t="n">
         <v>4394.112</v>
@@ -1861,18 +1861,18 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B46" t="n">
         <v>4371.578</v>
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="48">
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B49" t="n">
         <v>4091.609</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="50">
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B51" t="n">
         <v>3920.534</v>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B52" t="n">
         <v>3837.168</v>
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B53" t="n">
         <v>3812.24</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="56">
@@ -2213,18 +2213,18 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B57" t="n">
         <v>3692.361</v>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B58" t="n">
-        <v>3674.76</v>
+        <v>3673.138</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="59">
@@ -2309,18 +2309,18 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B60" t="n">
         <v>3531.797</v>
@@ -2341,18 +2341,18 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B61" t="n">
         <v>3517.715</v>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="63">
@@ -2437,18 +2437,18 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B64" t="n">
         <v>3461.525</v>
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B65" t="n">
         <v>3457.731</v>
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B66" t="n">
         <v>3437.408</v>
@@ -2533,18 +2533,18 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B67" t="n">
         <v>3426.048</v>
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B68" t="n">
         <v>3358.115</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="72">
@@ -2725,18 +2725,18 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B73" t="n">
         <v>3113.024</v>
@@ -2757,18 +2757,18 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B74" t="n">
         <v>3085.258</v>
@@ -2789,18 +2789,18 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B75" t="n">
         <v>3068.446</v>
@@ -2821,18 +2821,18 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="80">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="81">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="82">
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B83" t="n">
         <v>2946.291</v>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="85">
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="86">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="87">
@@ -3205,18 +3205,18 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B88" t="n">
         <v>2749.231</v>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B89" t="n">
         <v>2749.231</v>
@@ -3269,18 +3269,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B90" t="n">
         <v>2744.293</v>
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B91" t="n">
         <v>2717.279</v>
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="92">
@@ -3365,18 +3365,18 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B93" t="n">
         <v>2627.533</v>
@@ -3397,18 +3397,18 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B94" t="n">
         <v>2622.743</v>
@@ -3429,18 +3429,18 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B95" t="n">
         <v>2622.743</v>
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B96" t="n">
         <v>2622.743</v>
@@ -3493,18 +3493,18 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B97" t="n">
         <v>2622.743</v>
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="98">
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="99">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="100">
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B101" t="n">
         <v>2515.184</v>
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="102">
@@ -3685,18 +3685,18 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B103" t="n">
         <v>2490.279</v>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="104">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="105">
@@ -3781,18 +3781,18 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B106" t="n">
         <v>2435.956</v>
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="107">
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779124802267</v>
+        <v>1779131402395</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02780549769</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B108" t="n">
         <v>2366.47</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B109" t="n">
         <v>2355.803</v>
@@ -3909,18 +3909,18 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B110" t="n">
         <v>2338.44</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="111">
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B113" t="n">
         <v>2270.559</v>
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="114">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="115">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="116">
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B117" t="n">
         <v>2203.177</v>
@@ -4165,18 +4165,18 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B118" t="n">
         <v>2189.241</v>
@@ -4197,18 +4197,18 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B119" t="n">
         <v>2182.036</v>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B121" t="n">
         <v>2142.349</v>
@@ -4293,18 +4293,18 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B122" t="n">
         <v>2105.407</v>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="123">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="125">
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="126">
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B127" t="n">
         <v>2054.429</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B128" t="n">
         <v>2054.069</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="B129" t="n">
         <v>2023.611</v>
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="130">
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="131">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="132">
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="133">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="134">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="135">
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="B136" t="n">
         <v>1920.8</v>
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="137">
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="138">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="139">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="140">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="141">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="142">
@@ -4965,18 +4965,18 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="B143" t="n">
         <v>1809.194</v>
@@ -4997,18 +4997,18 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B144" t="n">
         <v>1766.869</v>
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="B145" t="n">
         <v>1760.675</v>
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="B146" t="n">
         <v>1755.532</v>
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="B148" t="n">
         <v>1699.828</v>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="149">
@@ -5189,18 +5189,18 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="B150" t="n">
         <v>1677.252</v>
@@ -5221,18 +5221,18 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B151" t="n">
         <v>1676.783</v>
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B152" t="n">
         <v>1674.745</v>
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="154">
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="B155" t="n">
         <v>1664.253</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B156" t="n">
         <v>1663.143</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="B157" t="n">
         <v>1657.112</v>
@@ -5445,18 +5445,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B158" t="n">
         <v>1638.82</v>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="159">
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2492</v>
+        <v>2489</v>
       </c>
       <c r="B160" t="n">
         <v>1607.589</v>
@@ -5541,18 +5541,18 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B161" t="n">
         <v>1602.739</v>
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="162">
@@ -5605,18 +5605,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="B163" t="n">
         <v>1558.753</v>
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B164" t="n">
         <v>1554.411</v>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="165">
@@ -5701,18 +5701,18 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="B166" t="n">
         <v>1534.485</v>
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="B167" t="n">
         <v>1532.656</v>
@@ -5765,18 +5765,18 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="B168" t="n">
         <v>1500</v>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="B169" t="n">
         <v>1499.185</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="B170" t="n">
         <v>1494.058</v>
@@ -5861,18 +5861,18 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="B171" t="n">
         <v>1485.365</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="172">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="173">
@@ -5957,18 +5957,18 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="B174" t="n">
         <v>1454.351</v>
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="175">
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="B176" t="n">
         <v>1448.537</v>
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="177">
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="178">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="179">
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="180">
@@ -6181,18 +6181,18 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="B181" t="n">
         <v>1397.551</v>
@@ -6213,18 +6213,18 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="B182" t="n">
         <v>1393.31</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="183">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="184">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="185">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="186">
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="187">
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="B188" t="n">
         <v>1344.894</v>
@@ -6437,18 +6437,18 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="B189" t="n">
         <v>1316.638</v>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="190">
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="B191" t="n">
         <v>1297.945</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="B192" t="n">
         <v>1293.862</v>
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="193">
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="B194" t="n">
         <v>1270.546</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="B195" t="n">
         <v>1270.507</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B196" t="n">
         <v>1270.493</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B197" t="n">
         <v>1270.493</v>
@@ -6725,18 +6725,18 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="B198" t="n">
         <v>1264.62</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="199">
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="200">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="201">
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B202" t="n">
         <v>1222.617</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B203" t="n">
         <v>1222.617</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B204" t="n">
         <v>1219.798</v>
@@ -6949,18 +6949,18 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="B205" t="n">
         <v>1207.273</v>
@@ -6981,18 +6981,18 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="B206" t="n">
         <v>1172.514</v>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="B208" t="n">
         <v>1146.05</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B209" t="n">
         <v>1132.544</v>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="B210" t="n">
         <v>1126.872</v>
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3194</v>
+        <v>3196</v>
       </c>
       <c r="B211" t="n">
         <v>1122.12</v>
@@ -7173,18 +7173,18 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="B212" t="n">
         <v>1111.893</v>
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B213" t="n">
         <v>1111.63</v>
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="214">
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3249</v>
+        <v>3246</v>
       </c>
       <c r="B215" t="n">
         <v>1093.128</v>
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="216">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="217">
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="218">
@@ -7397,13 +7397,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="219">
@@ -7429,18 +7429,18 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3302</v>
+        <v>3300</v>
       </c>
       <c r="B220" t="n">
         <v>1059.625</v>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="222">
@@ -7525,18 +7525,18 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="B223" t="n">
         <v>1006.935</v>
@@ -7557,18 +7557,18 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3392</v>
+        <v>3390</v>
       </c>
       <c r="B224" t="n">
         <v>984.373</v>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779124802267</v>
+        <v>1779131102204</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46160.95141512732</v>
+        <v>46161.02433106481</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779131402394</v>
+        <v>1779137402100</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.02780548611</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779131402394</v>
+        <v>1779137402100</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.02780548611</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="4">
@@ -549,18 +549,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779131402394</v>
+        <v>1779137402100</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.02780548611</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="n">
         <v>29501.632</v>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="10">
@@ -741,18 +741,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B11" t="n">
         <v>14139.885</v>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="13">
@@ -837,18 +837,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B14" t="n">
         <v>11445.012</v>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779131402395</v>
+        <v>1779137402100</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724652778</v>
       </c>
     </row>
     <row r="15">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="16">
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B17" t="n">
         <v>9252.380999999999</v>
@@ -965,18 +965,18 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B18" t="n">
         <v>9229.285</v>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="19">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="20">
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B21" t="n">
         <v>7877.188</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="25">
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B26" t="n">
         <v>6473.386</v>
@@ -1253,18 +1253,18 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B27" t="n">
         <v>6149.447</v>
@@ -1285,18 +1285,18 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B28" t="n">
         <v>5899.196</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="30">
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B31" t="n">
         <v>5177.898</v>
@@ -1413,18 +1413,18 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B32" t="n">
         <v>5177.898</v>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="37">
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B38" t="n">
         <v>4996.846</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="39">
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B40" t="n">
         <v>4961.495</v>
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B41" t="n">
         <v>4953.328</v>
@@ -1733,18 +1733,18 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B42" t="n">
         <v>4695.998</v>
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B43" t="n">
         <v>4651.997</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="44">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="45">
@@ -1861,18 +1861,18 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B46" t="n">
         <v>4371.578</v>
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="47">
@@ -1925,18 +1925,18 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B48" t="n">
         <v>4287.14</v>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B49" t="n">
         <v>4091.609</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="50">
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B51" t="n">
         <v>3920.534</v>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B52" t="n">
         <v>3837.168</v>
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B53" t="n">
         <v>3812.24</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="56">
@@ -2213,18 +2213,18 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B57" t="n">
         <v>3692.361</v>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B58" t="n">
-        <v>3673.138</v>
+        <v>3673.219</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,18 +2277,18 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B59" t="n">
         <v>3542.882</v>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="60">
@@ -2341,18 +2341,18 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B61" t="n">
         <v>3517.715</v>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="63">
@@ -2437,18 +2437,18 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B64" t="n">
         <v>3461.525</v>
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="B65" t="n">
         <v>3457.731</v>
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B66" t="n">
         <v>3437.408</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="67">
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B68" t="n">
         <v>3358.115</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="72">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="73">
@@ -2757,18 +2757,18 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B74" t="n">
         <v>3085.258</v>
@@ -2789,18 +2789,18 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B75" t="n">
         <v>3068.446</v>
@@ -2821,18 +2821,18 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="80">
@@ -2981,18 +2981,18 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B81" t="n">
         <v>2991.225</v>
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B82" t="n">
         <v>2953.701</v>
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B83" t="n">
         <v>2946.291</v>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="85">
@@ -3141,18 +3141,18 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B86" t="n">
         <v>2819.016</v>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="87">
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="88">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="89">
@@ -3269,18 +3269,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B90" t="n">
         <v>2744.293</v>
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="91">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="92">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="93">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="94">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="95">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="96">
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="97">
@@ -3525,18 +3525,18 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B98" t="n">
         <v>2587.632</v>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="99">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="100">
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B101" t="n">
         <v>2515.184</v>
@@ -3653,18 +3653,18 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B102" t="n">
         <v>2494.136</v>
@@ -3685,18 +3685,18 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B103" t="n">
         <v>2490.279</v>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="104">
@@ -3749,18 +3749,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B105" t="n">
         <v>2457.642</v>
@@ -3781,18 +3781,18 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B106" t="n">
         <v>2435.956</v>
@@ -3813,18 +3813,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B107" t="n">
         <v>2410.942</v>
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779131402395</v>
+        <v>1779137402101</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.02780549769</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B108" t="n">
         <v>2366.47</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B109" t="n">
         <v>2355.803</v>
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="110">
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="111">
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B113" t="n">
         <v>2270.559</v>
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="114">
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B115" t="n">
         <v>2243.02</v>
@@ -4101,18 +4101,18 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B116" t="n">
         <v>2237.983</v>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B117" t="n">
         <v>2203.177</v>
@@ -4165,18 +4165,18 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B118" t="n">
         <v>2189.241</v>
@@ -4197,18 +4197,18 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B119" t="n">
         <v>2182.036</v>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="121">
@@ -4293,18 +4293,18 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B122" t="n">
         <v>2105.407</v>
@@ -4325,18 +4325,18 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="B123" t="n">
         <v>2101.476</v>
@@ -4357,18 +4357,18 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="B124" t="n">
         <v>2100.998</v>
@@ -4389,18 +4389,18 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="B126" t="n">
         <v>2091.564</v>
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B127" t="n">
         <v>2054.429</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B128" t="n">
         <v>2054.069</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="B129" t="n">
         <v>2023.611</v>
@@ -4549,18 +4549,18 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="B130" t="n">
         <v>2017.058</v>
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="B131" t="n">
         <v>2016.395</v>
@@ -4613,18 +4613,18 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="B132" t="n">
         <v>1971.957</v>
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="133">
@@ -4677,18 +4677,18 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B134" t="n">
         <v>1950.98</v>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="135">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="136">
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="137">
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="B138" t="n">
         <v>1871.373</v>
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="B139" t="n">
         <v>1853.32</v>
@@ -4869,18 +4869,18 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="B140" t="n">
         <v>1843.48</v>
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="141">
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B142" t="n">
         <v>1813.92</v>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="143">
@@ -4997,18 +4997,18 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="B144" t="n">
         <v>1766.869</v>
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="B145" t="n">
         <v>1760.675</v>
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="B146" t="n">
         <v>1755.532</v>
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="147">
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="B148" t="n">
         <v>1699.828</v>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="149">
@@ -5189,18 +5189,18 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="B150" t="n">
         <v>1677.252</v>
@@ -5221,18 +5221,18 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B151" t="n">
         <v>1676.783</v>
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B152" t="n">
         <v>1674.745</v>
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="154">
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="B155" t="n">
         <v>1664.253</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="B156" t="n">
         <v>1663.143</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="B157" t="n">
         <v>1657.112</v>
@@ -5445,18 +5445,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B158" t="n">
         <v>1638.82</v>
@@ -5477,18 +5477,18 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B159" t="n">
         <v>1633.314</v>
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="B160" t="n">
         <v>1607.589</v>
@@ -5541,18 +5541,18 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="B161" t="n">
         <v>1602.739</v>
@@ -5573,18 +5573,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="B162" t="n">
         <v>1568.294</v>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="163">
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="B164" t="n">
         <v>1554.411</v>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="165">
@@ -5701,18 +5701,18 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="B166" t="n">
         <v>1534.485</v>
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="B167" t="n">
         <v>1532.656</v>
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="168">
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="B169" t="n">
         <v>1499.185</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="B170" t="n">
         <v>1494.058</v>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="171">
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="172">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="173">
@@ -5957,18 +5957,18 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="B174" t="n">
         <v>1454.351</v>
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="175">
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="B176" t="n">
         <v>1448.537</v>
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="177">
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="B178" t="n">
         <v>1410.982</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="B179" t="n">
         <v>1409.964</v>
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="B180" t="n">
         <v>1409.921</v>
@@ -6181,18 +6181,18 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="B181" t="n">
         <v>1397.551</v>
@@ -6213,18 +6213,18 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="B182" t="n">
         <v>1393.31</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="183">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="184">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="185">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="186">
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="187">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="188">
@@ -6437,18 +6437,18 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="B189" t="n">
         <v>1316.638</v>
@@ -6469,18 +6469,18 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2897</v>
+        <v>2899</v>
       </c>
       <c r="B190" t="n">
         <v>1304.387</v>
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2911</v>
+        <v>2913</v>
       </c>
       <c r="B191" t="n">
         <v>1297.945</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2918</v>
+        <v>2920</v>
       </c>
       <c r="B192" t="n">
         <v>1293.862</v>
@@ -6565,18 +6565,18 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2944</v>
+        <v>2947</v>
       </c>
       <c r="B193" t="n">
         <v>1276.294</v>
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2954</v>
+        <v>2956</v>
       </c>
       <c r="B194" t="n">
         <v>1270.546</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B195" t="n">
         <v>1270.507</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2956</v>
+        <v>2958</v>
       </c>
       <c r="B196" t="n">
         <v>1270.493</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2956</v>
+        <v>2958</v>
       </c>
       <c r="B197" t="n">
         <v>1270.493</v>
@@ -6725,18 +6725,18 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="B198" t="n">
         <v>1264.62</v>
@@ -6757,18 +6757,18 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="B199" t="n">
         <v>1246.285</v>
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="200">
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3014</v>
+        <v>3016</v>
       </c>
       <c r="B201" t="n">
         <v>1226.325</v>
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3019</v>
+        <v>3021</v>
       </c>
       <c r="B202" t="n">
         <v>1222.617</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3019</v>
+        <v>3021</v>
       </c>
       <c r="B203" t="n">
         <v>1222.617</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3028</v>
+        <v>3030</v>
       </c>
       <c r="B204" t="n">
         <v>1219.798</v>
@@ -6949,18 +6949,18 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="B205" t="n">
         <v>1207.273</v>
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="206">
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3139</v>
+        <v>3141</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="B208" t="n">
         <v>1146.05</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="B209" t="n">
         <v>1132.544</v>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="B210" t="n">
         <v>1126.872</v>
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="B211" t="n">
         <v>1122.12</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="212">
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B213" t="n">
         <v>1111.63</v>
@@ -7237,18 +7237,18 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="B214" t="n">
         <v>1102.434</v>
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3246</v>
+        <v>3248</v>
       </c>
       <c r="B215" t="n">
         <v>1093.128</v>
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
@@ -7365,18 +7365,18 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="B218" t="n">
         <v>1070.911</v>
@@ -7397,18 +7397,18 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="B219" t="n">
         <v>1069.408</v>
@@ -7429,18 +7429,18 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3300</v>
+        <v>3302</v>
       </c>
       <c r="B220" t="n">
         <v>1059.625</v>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="222">
@@ -7525,18 +7525,18 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="B223" t="n">
         <v>1006.935</v>
@@ -7557,18 +7557,18 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3390</v>
+        <v>3392</v>
       </c>
       <c r="B224" t="n">
         <v>984.373</v>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779131102204</v>
+        <v>1779137402101</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.02433106481</v>
+        <v>46161.09724653935</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="4">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="5">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="11">
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="13">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779137402100</v>
+        <v>1779141302115</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238559028</v>
       </c>
     </row>
     <row r="14">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779137402100</v>
+        <v>1779141302116</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.09724652778</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="15">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="16">
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="17">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="18">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="19">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="20">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="21">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="25">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="26">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="27">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="28">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="30">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="32">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="37">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="38">
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="39">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="40">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="41">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="42">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="43">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="44">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="45">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="48">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="49">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="50">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="51">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="52">
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="53">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="56">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="57">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="58">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="59">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="60">
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="61">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="63">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="64">
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="65">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="66">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="67">
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="68">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="69">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="72">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="74">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="75">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="76">
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="80">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="81">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="82">
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="83">
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="84">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="85">
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="86">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="87">
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="88">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="89">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="91">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="92">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="93">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="94">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="95">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="96">
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="97">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="98">
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="99">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="100">
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="101">
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="102">
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="103">
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="104">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="105">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="106">
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="107">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="108">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="109">
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="110">
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="111">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="112">
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="113">
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="114">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="115">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="116">
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="117">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="118">
@@ -4197,13 +4197,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="119">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="120">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="121">
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="122">
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="123">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="125">
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="126">
@@ -4453,13 +4453,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="127">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="128">
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="129">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="130">
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="131">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="132">
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="133">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="134">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="135">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="136">
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="137">
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="138">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="139">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="140">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="141">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="142">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="143">
@@ -4997,13 +4997,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="144">
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="145">
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="146">
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="147">
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="148">
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="149">
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="150">
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="151">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="152">
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="154">
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="155">
@@ -5381,13 +5381,13 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="156">
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="157">
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="158">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="159">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="160">
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="161">
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="162">
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="163">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="164">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="165">
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="166">
@@ -5733,13 +5733,13 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="167">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="168">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="169">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="170">
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="171">
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="172">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="173">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="174">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="175">
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="176">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="177">
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="178">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="179">
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="180">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="181">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="182">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="183">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="184">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="185">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="186">
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="187">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="188">
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="189">
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="190">
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="191">
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="192">
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="193">
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="194">
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="195">
@@ -6661,13 +6661,13 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="196">
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="197">
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="198">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="199">
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="200">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="201">
@@ -6853,13 +6853,13 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="202">
@@ -6885,13 +6885,13 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="203">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="204">
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="205">
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="206">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="207">
@@ -7045,13 +7045,13 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="208">
@@ -7077,13 +7077,13 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="209">
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="210">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="211">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="212">
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="213">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="214">
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="215">
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="216">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="217">
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="218">
@@ -7397,13 +7397,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="219">
@@ -7429,13 +7429,13 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="220">
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="222">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="223">
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
     <row r="224">
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779137402101</v>
+        <v>1779141302116</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.09724653935</v>
+        <v>46161.14238560185</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="4">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="5">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="11">
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="13">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779141302115</v>
+        <v>1779144902034</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.14238559028</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="14">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="15">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="16">
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="17">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="18">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="19">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="20">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="21">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="25">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="26">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="27">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="28">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="30">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="32">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="37">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="38">
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="39">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="40">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="41">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="42">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="43">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="44">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="45">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="48">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779141302116</v>
+        <v>1779144902034</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18405131945</v>
       </c>
     </row>
     <row r="49">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="50">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="51">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="52">
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="53">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="56">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="57">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="58">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="59">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="60">
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="61">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="63">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="64">
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="65">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="66">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="67">
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="68">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="69">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="72">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="74">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="75">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="76">
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="80">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="81">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="82">
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="83">
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="84">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="85">
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="86">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="87">
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="88">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="89">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="91">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="92">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="93">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="94">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="95">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="96">
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="97">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="98">
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="99">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="100">
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="101">
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="102">
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="103">
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="104">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="105">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="106">
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="107">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="108">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="109">
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="110">
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="111">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="112">
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="113">
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="114">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="115">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="116">
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="117">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="118">
@@ -4197,13 +4197,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="119">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="120">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="121">
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="122">
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="123">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="125">
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="126">
@@ -4453,13 +4453,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="127">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="128">
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="129">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="130">
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="131">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="132">
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="133">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="134">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="135">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="136">
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="137">
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="138">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="139">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="140">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="141">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="142">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="143">
@@ -4997,13 +4997,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="144">
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="145">
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="146">
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="147">
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="148">
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="149">
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="150">
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="151">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="152">
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="154">
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="155">
@@ -5381,13 +5381,13 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="156">
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="157">
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="158">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="159">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="160">
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="161">
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="162">
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="163">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="164">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="165">
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="166">
@@ -5733,13 +5733,13 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="167">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="168">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="169">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="170">
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="171">
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="172">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="173">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="174">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="175">
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="176">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="177">
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="178">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="179">
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="180">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="181">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="182">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="183">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="184">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="185">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="186">
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="187">
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B188" t="n">
         <v>1344.894</v>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="189">
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="190">
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="191">
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="192">
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="193">
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="194">
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="195">
@@ -6661,13 +6661,13 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="196">
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="197">
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="198">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="199">
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="200">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="201">
@@ -6853,13 +6853,13 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="202">
@@ -6885,13 +6885,13 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="203">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="204">
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="205">
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="206">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="207">
@@ -7045,13 +7045,13 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="208">
@@ -7077,13 +7077,13 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="209">
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="210">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="211">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="212">
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="213">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="214">
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="215">
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="216">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="217">
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="218">
@@ -7397,13 +7397,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="219">
@@ -7429,13 +7429,13 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="220">
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="222">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="223">
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
     <row r="224">
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779141302116</v>
+        <v>1779144602239</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.14238560185</v>
+        <v>46161.18058146991</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="4">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="5">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="11">
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="13">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="14">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="15">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="16">
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="17">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="18">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="19">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="20">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="21">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="22">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="24">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="25">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="26">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="27">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="28">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="29">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="30">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="32">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="33">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="34">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="35">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="36">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="37">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="38">
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="39">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="40">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="41">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="42">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="43">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="44">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="45">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="48">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779144902034</v>
+        <v>1779148202215</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.18405131945</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="49">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="50">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="51">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="52">
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="53">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="54">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="56">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="57">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="58">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="59">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="60">
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G60" t="n">
         <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="61">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="63">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="64">
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="65">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="66">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="67">
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="68">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="69">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="70">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="72">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="74">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="75">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="76">
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="80">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="81">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="82">
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="83">
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="84">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="85">
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="86">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="87">
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="88">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="89">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="91">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="92">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="93">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="94">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="95">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="96">
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="97">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="98">
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="99">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="100">
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="101">
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="102">
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="103">
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="104">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="105">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="106">
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="107">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="108">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="109">
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="110">
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B111" t="n">
         <v>2328.854</v>
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="112">
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="113">
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="114">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="115">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="116">
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="117">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="118">
@@ -4197,13 +4197,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="119">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="120">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="121">
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="122">
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="123">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="124">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="125">
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="126">
@@ -4453,13 +4453,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="127">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="128">
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="129">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="130">
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="131">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="132">
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="133">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="134">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="135">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="136">
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="137">
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="138">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="139">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="140">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="141">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="142">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="143">
@@ -4997,13 +4997,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="144">
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="145">
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="146">
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="147">
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="148">
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="149">
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="150">
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="151">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="152">
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="153">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="154">
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="155">
@@ -5381,13 +5381,13 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="156">
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="157">
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="158">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="159">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="160">
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="161">
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="162">
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="163">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="164">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="165">
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779144602239</v>
+        <v>1779148202215</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224785879</v>
       </c>
     </row>
     <row r="166">
@@ -5733,13 +5733,13 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="167">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="168">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="169">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="170">
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="171">
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="172">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="173">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="174">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="175">
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="176">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="177">
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="178">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="179">
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="180">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="181">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="182">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="183">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="184">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="185">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="186">
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="187">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="188">
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="189">
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="190">
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="191">
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="192">
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="193">
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="194">
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="195">
@@ -6661,13 +6661,13 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="196">
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="197">
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="198">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="199">
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="200">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="201">
@@ -6853,13 +6853,13 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="202">
@@ -6885,13 +6885,13 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="203">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="204">
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="205">
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="206">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="207">
@@ -7045,13 +7045,13 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="208">
@@ -7077,13 +7077,13 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="209">
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="210">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="211">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="212">
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="213">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="214">
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="215">
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="216">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="217">
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="218">
@@ -7397,13 +7397,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="219">
@@ -7429,13 +7429,13 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="220">
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="222">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="223">
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
     <row r="224">
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779144602239</v>
+        <v>1779148202216</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.18058146991</v>
+        <v>46161.22224787037</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G2" t="n">
         <v>90.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G3" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="4">
@@ -549,18 +549,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G4" t="n">
         <v>37.96</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="n">
         <v>29501.632</v>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G6" t="n">
         <v>26.67</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="7">
@@ -645,18 +645,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G7" t="n">
         <v>26.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" t="n">
         <v>25354.315</v>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G8" t="n">
         <v>25.35</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="9">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G9" t="n">
         <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" t="n">
         <v>16501.504</v>
@@ -741,18 +741,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G10" t="n">
         <v>16.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B11" t="n">
         <v>14139.885</v>
@@ -773,18 +773,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G11" t="n">
         <v>14.14</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" t="n">
         <v>13062.151</v>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G12" t="n">
         <v>13.06</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="13">
@@ -837,18 +837,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G13" t="n">
         <v>12.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B14" t="n">
         <v>11445.012</v>
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G14" t="n">
         <v>11.45</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B15" t="n">
         <v>10376.047</v>
@@ -901,18 +901,18 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G15" t="n">
         <v>10.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B16" t="n">
         <v>10139.4</v>
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G16" t="n">
         <v>10.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B17" t="n">
         <v>9252.380999999999</v>
@@ -965,18 +965,18 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G17" t="n">
         <v>9.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B18" t="n">
         <v>9229.285</v>
@@ -997,18 +997,18 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G18" t="n">
         <v>9.23</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B19" t="n">
         <v>8387.036</v>
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G19" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B20" t="n">
         <v>8252.09</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="21">
@@ -1093,18 +1093,18 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G21" t="n">
         <v>7.88</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B22" t="n">
         <v>7731.099</v>
@@ -1125,18 +1125,18 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G22" t="n">
         <v>7.73</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B23" t="n">
         <v>7730.956</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G23" t="n">
         <v>7.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="24">
@@ -1189,18 +1189,18 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B25" t="n">
         <v>7289.86</v>
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B26" t="n">
         <v>6473.386</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G26" t="n">
         <v>6.47</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="27">
@@ -1285,18 +1285,18 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B28" t="n">
         <v>5899.196</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="29">
@@ -1349,18 +1349,18 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B30" t="n">
         <v>5453.212</v>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G30" t="n">
         <v>5.45</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G31" t="n">
         <v>5.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="32">
@@ -1445,18 +1445,18 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G32" t="n">
         <v>5.18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B33" t="n">
         <v>5150.844</v>
@@ -1477,18 +1477,18 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B34" t="n">
         <v>5084.179</v>
@@ -1509,18 +1509,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G34" t="n">
         <v>5.08</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B35" t="n">
         <v>5071.275</v>
@@ -1541,18 +1541,18 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B36" t="n">
         <v>5050.542</v>
@@ -1573,18 +1573,18 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G36" t="n">
         <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B37" t="n">
         <v>5050.537</v>
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G37" t="n">
         <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B38" t="n">
         <v>4996.846</v>
@@ -1637,18 +1637,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B39" t="n">
         <v>4986.26</v>
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G39" t="n">
         <v>4.99</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B40" t="n">
         <v>4961.495</v>
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B41" t="n">
         <v>4953.328</v>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G41" t="n">
         <v>4.95</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="42">
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B43" t="n">
         <v>4651.997</v>
@@ -1797,18 +1797,18 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B44" t="n">
         <v>4599.875</v>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G44" t="n">
         <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B45" t="n">
         <v>4394.112</v>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G45" t="n">
         <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G46" t="n">
         <v>4.37</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G47" t="n">
         <v>4.31</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="48">
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B49" t="n">
         <v>4091.609</v>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="B51" t="n">
         <v>3920.534</v>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G51" t="n">
         <v>3.92</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B52" t="n">
         <v>3837.168</v>
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G52" t="n">
         <v>3.84</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="B53" t="n">
         <v>3812.24</v>
@@ -2117,18 +2117,18 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G53" t="n">
         <v>3.81</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B54" t="n">
         <v>3742.953</v>
@@ -2149,18 +2149,18 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G54" t="n">
         <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B55" t="n">
         <v>3742.915</v>
@@ -2181,18 +2181,18 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G55" t="n">
         <v>3.74</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B56" t="n">
         <v>3742.915</v>
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G56" t="n">
         <v>3.74</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="57">
@@ -2245,18 +2245,18 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779148202215</v>
+        <v>1779156002253</v>
       </c>
       <c r="G57" t="n">
         <v>3.69</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252607639</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B58" t="n">
         <v>3673.219</v>
@@ -2277,18 +2277,18 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G58" t="n">
         <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B59" t="n">
         <v>3542.882</v>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G59" t="n">
         <v>3.54</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B60" t="n">
-        <v>3531.797</v>
+        <v>3539.965</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,18 +2341,18 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G60" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B61" t="n">
         <v>3517.715</v>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G61" t="n">
         <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="62">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G62" t="n">
         <v>3.49</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="63">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G63" t="n">
         <v>3.46</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="64">
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G64" t="n">
         <v>3.46</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="65">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G65" t="n">
         <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="66">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="67">
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G67" t="n">
         <v>3.43</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B68" t="n">
         <v>3358.115</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="B70" t="n">
         <v>3221.232</v>
@@ -2661,18 +2661,18 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B71" t="n">
         <v>3212.603</v>
@@ -2693,18 +2693,18 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B72" t="n">
         <v>3152.624</v>
@@ -2725,18 +2725,18 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G72" t="n">
         <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B73" t="n">
         <v>3113.024</v>
@@ -2757,18 +2757,18 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="B74" t="n">
         <v>3085.258</v>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G74" t="n">
         <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="75">
@@ -2821,18 +2821,18 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -2853,18 +2853,18 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B77" t="n">
         <v>3047.215</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G77" t="n">
         <v>3.05</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G78" t="n">
         <v>3.01</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="79">
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G79" t="n">
         <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="80">
@@ -2981,18 +2981,18 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B81" t="n">
         <v>2991.225</v>
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G81" t="n">
         <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="B82" t="n">
         <v>2953.701</v>
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G82" t="n">
         <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B83" t="n">
         <v>2946.291</v>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G83" t="n">
         <v>2.95</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B84" t="n">
         <v>2895</v>
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="B85" t="n">
         <v>2835.87</v>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G85" t="n">
         <v>2.84</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B86" t="n">
-        <v>2819.016</v>
+        <v>2815.045</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G86" t="n">
         <v>2.82</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,18 +3205,18 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B88" t="n">
         <v>2749.231</v>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G88" t="n">
         <v>2.75</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B89" t="n">
         <v>2749.231</v>
@@ -3269,18 +3269,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G89" t="n">
         <v>2.75</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B90" t="n">
         <v>2744.293</v>
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G90" t="n">
         <v>2.74</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B91" t="n">
         <v>2717.279</v>
@@ -3333,18 +3333,18 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G91" t="n">
         <v>2.72</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B92" t="n">
         <v>2707.811</v>
@@ -3365,18 +3365,18 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G92" t="n">
         <v>2.71</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B93" t="n">
         <v>2627.533</v>
@@ -3397,18 +3397,18 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B94" t="n">
         <v>2622.743</v>
@@ -3429,18 +3429,18 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B95" t="n">
         <v>2622.743</v>
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B96" t="n">
         <v>2622.743</v>
@@ -3493,18 +3493,18 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B97" t="n">
         <v>2622.743</v>
@@ -3525,18 +3525,18 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="B98" t="n">
         <v>2587.632</v>
@@ -3557,18 +3557,18 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G98" t="n">
         <v>2.59</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="B99" t="n">
         <v>2552.876</v>
@@ -3589,18 +3589,18 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G99" t="n">
         <v>2.55</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="B100" t="n">
         <v>2551.171</v>
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G100" t="n">
         <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="101">
@@ -3653,18 +3653,18 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G101" t="n">
         <v>2.52</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B102" t="n">
         <v>2494.136</v>
@@ -3685,18 +3685,18 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G102" t="n">
         <v>2.49</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="B103" t="n">
         <v>2490.279</v>
@@ -3717,18 +3717,18 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G103" t="n">
         <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="B104" t="n">
         <v>2465.589</v>
@@ -3749,18 +3749,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G104" t="n">
         <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B105" t="n">
         <v>2457.642</v>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="106">
@@ -3813,18 +3813,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G106" t="n">
         <v>2.44</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="B107" t="n">
         <v>2410.942</v>
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G107" t="n">
         <v>2.41</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B108" t="n">
         <v>2366.47</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G108" t="n">
         <v>2.37</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="B109" t="n">
         <v>2355.803</v>
@@ -3909,18 +3909,18 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="B110" t="n">
         <v>2338.44</v>
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G110" t="n">
         <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1792</v>
+        <v>1788</v>
       </c>
       <c r="B111" t="n">
         <v>2328.854</v>
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G111" t="n">
         <v>2.33</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="B112" t="n">
         <v>2271.057</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G112" t="n">
         <v>2.27</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1851</v>
+        <v>1847</v>
       </c>
       <c r="B113" t="n">
         <v>2270.559</v>
@@ -4037,18 +4037,18 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B114" t="n">
         <v>2250.673</v>
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="115">
@@ -4101,18 +4101,18 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B116" t="n">
         <v>2237.983</v>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G116" t="n">
         <v>2.24</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B117" t="n">
         <v>2203.177</v>
@@ -4165,18 +4165,18 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G117" t="n">
         <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B118" t="n">
         <v>2189.241</v>
@@ -4197,18 +4197,18 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B119" t="n">
         <v>2182.036</v>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G119" t="n">
         <v>2.18</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1936</v>
+        <v>1940</v>
       </c>
       <c r="B120" t="n">
         <v>2154.507</v>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B121" t="n">
         <v>2142.349</v>
@@ -4293,18 +4293,18 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G121" t="n">
         <v>2.14</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="B122" t="n">
         <v>2105.407</v>
@@ -4325,18 +4325,18 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G122" t="n">
         <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="B123" t="n">
         <v>2101.476</v>
@@ -4357,18 +4357,18 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="B124" t="n">
         <v>2100.998</v>
@@ -4389,18 +4389,18 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B126" t="n">
         <v>2091.564</v>
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="B127" t="n">
         <v>2054.429</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G127" t="n">
         <v>2.05</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B128" t="n">
         <v>2054.069</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="B129" t="n">
         <v>2023.611</v>
@@ -4549,18 +4549,18 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B130" t="n">
         <v>2017.058</v>
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G130" t="n">
         <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="B131" t="n">
         <v>2016.395</v>
@@ -4613,18 +4613,18 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G131" t="n">
         <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2126</v>
+        <v>2122</v>
       </c>
       <c r="B132" t="n">
         <v>1971.957</v>
@@ -4645,18 +4645,18 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G132" t="n">
         <v>1.97</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="B133" t="n">
         <v>1952.485</v>
@@ -4677,18 +4677,18 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G133" t="n">
         <v>1.95</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="B134" t="n">
         <v>1950.98</v>
@@ -4709,18 +4709,18 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="B135" t="n">
         <v>1943.862</v>
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="B136" t="n">
         <v>1920.8</v>
@@ -4773,18 +4773,18 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G136" t="n">
         <v>1.92</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="B137" t="n">
         <v>1888.225</v>
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G137" t="n">
         <v>1.89</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B138" t="n">
         <v>1871.373</v>
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B139" t="n">
         <v>1853.32</v>
@@ -4869,18 +4869,18 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G139" t="n">
         <v>1.85</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="B140" t="n">
         <v>1843.48</v>
@@ -4901,18 +4901,18 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G140" t="n">
         <v>1.84</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="B141" t="n">
         <v>1831.051</v>
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="B142" t="n">
         <v>1813.92</v>
@@ -4965,18 +4965,18 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="B143" t="n">
         <v>1809.194</v>
@@ -4997,13 +4997,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="144">
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G144" t="n">
         <v>1.77</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="B145" t="n">
         <v>1760.675</v>
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G145" t="n">
         <v>1.76</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="B146" t="n">
         <v>1755.532</v>
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="B148" t="n">
         <v>1699.828</v>
@@ -5157,18 +5157,18 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G148" t="n">
         <v>1.7</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2415</v>
+        <v>2419</v>
       </c>
       <c r="B149" t="n">
         <v>1684.006</v>
@@ -5189,18 +5189,18 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G149" t="n">
         <v>1.68</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="B150" t="n">
         <v>1677.252</v>
@@ -5221,18 +5221,18 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G150" t="n">
         <v>1.68</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="B151" t="n">
         <v>1676.783</v>
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G151" t="n">
         <v>1.68</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="B152" t="n">
         <v>1674.745</v>
@@ -5285,18 +5285,18 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G152" t="n">
         <v>1.67</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="B153" t="n">
         <v>1672.564</v>
@@ -5317,18 +5317,18 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G153" t="n">
         <v>1.67</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="B154" t="n">
         <v>1671.06</v>
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G154" t="n">
         <v>1.67</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="B155" t="n">
         <v>1664.253</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G155" t="n">
         <v>1.66</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="B156" t="n">
         <v>1663.143</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2446</v>
+        <v>2450</v>
       </c>
       <c r="B157" t="n">
         <v>1657.112</v>
@@ -5445,18 +5445,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G157" t="n">
         <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="B158" t="n">
         <v>1638.82</v>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="159">
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B160" t="n">
         <v>1607.589</v>
@@ -5541,18 +5541,18 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G160" t="n">
         <v>1.61</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="B161" t="n">
         <v>1602.739</v>
@@ -5573,18 +5573,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2532</v>
+        <v>2540</v>
       </c>
       <c r="B162" t="n">
         <v>1568.294</v>
@@ -5605,18 +5605,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G162" t="n">
         <v>1.57</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="B163" t="n">
         <v>1558.753</v>
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="B164" t="n">
         <v>1554.411</v>
@@ -5669,18 +5669,18 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2562</v>
+        <v>2567</v>
       </c>
       <c r="B165" t="n">
         <v>1553.807</v>
@@ -5701,18 +5701,18 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779148202215</v>
+        <v>1779156002254</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.22224785879</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2593</v>
+        <v>2598</v>
       </c>
       <c r="B166" t="n">
         <v>1534.485</v>
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G166" t="n">
         <v>1.53</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="B167" t="n">
         <v>1532.656</v>
@@ -5765,18 +5765,18 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G167" t="n">
         <v>1.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="B168" t="n">
         <v>1500</v>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G168" t="n">
         <v>1.5</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="B169" t="n">
         <v>1499.185</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G169" t="n">
         <v>1.5</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="B170" t="n">
         <v>1494.058</v>
@@ -5861,18 +5861,18 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G170" t="n">
         <v>1.49</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="B171" t="n">
         <v>1485.365</v>
@@ -5893,18 +5893,18 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="B172" t="n">
         <v>1480.068</v>
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G172" t="n">
         <v>1.48</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="B173" t="n">
         <v>1480.068</v>
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="174">
@@ -5989,18 +5989,18 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G174" t="n">
         <v>1.45</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="B175" t="n">
         <v>1452.72</v>
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2698</v>
+        <v>2702</v>
       </c>
       <c r="B176" t="n">
         <v>1448.537</v>
@@ -6053,18 +6053,18 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2734</v>
+        <v>2736</v>
       </c>
       <c r="B177" t="n">
         <v>1414.525</v>
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="B178" t="n">
         <v>1410.982</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="B179" t="n">
         <v>1409.964</v>
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="B180" t="n">
         <v>1409.921</v>
@@ -6181,18 +6181,18 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2769</v>
+        <v>2773</v>
       </c>
       <c r="B181" t="n">
         <v>1397.551</v>
@@ -6213,18 +6213,18 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2776</v>
+        <v>2780</v>
       </c>
       <c r="B182" t="n">
         <v>1393.31</v>
@@ -6245,18 +6245,18 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G182" t="n">
         <v>1.39</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="B183" t="n">
         <v>1389.701</v>
@@ -6277,18 +6277,18 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2808</v>
+        <v>2810</v>
       </c>
       <c r="B184" t="n">
         <v>1372.472</v>
@@ -6309,18 +6309,18 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G184" t="n">
         <v>1.37</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="B185" t="n">
         <v>1369.934</v>
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2820</v>
+        <v>2823</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,18 +6373,18 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2822</v>
+        <v>2824</v>
       </c>
       <c r="B187" t="n">
         <v>1361.194</v>
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2838</v>
+        <v>2840</v>
       </c>
       <c r="B188" t="n">
         <v>1344.894</v>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="189">
@@ -6469,18 +6469,18 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G189" t="n">
         <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2899</v>
+        <v>2901</v>
       </c>
       <c r="B190" t="n">
         <v>1304.387</v>
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G190" t="n">
         <v>1.3</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B191" t="n">
         <v>1297.945</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G191" t="n">
         <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2920</v>
+        <v>2922</v>
       </c>
       <c r="B192" t="n">
         <v>1293.862</v>
@@ -6565,18 +6565,18 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2947</v>
+        <v>2950</v>
       </c>
       <c r="B193" t="n">
         <v>1276.294</v>
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G193" t="n">
         <v>1.28</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="B194" t="n">
         <v>1270.546</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G194" t="n">
         <v>1.27</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B195" t="n">
         <v>1270.507</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G195" t="n">
         <v>1.27</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B196" t="n">
         <v>1270.493</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B197" t="n">
         <v>1270.493</v>
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="198">
@@ -6757,18 +6757,18 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2988</v>
+        <v>2992</v>
       </c>
       <c r="B199" t="n">
         <v>1246.285</v>
@@ -6789,18 +6789,18 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2994</v>
+        <v>3000</v>
       </c>
       <c r="B200" t="n">
         <v>1237.687</v>
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G200" t="n">
         <v>1.24</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3016</v>
+        <v>3025</v>
       </c>
       <c r="B201" t="n">
         <v>1226.325</v>
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G201" t="n">
         <v>1.23</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3021</v>
+        <v>3031</v>
       </c>
       <c r="B202" t="n">
         <v>1222.617</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G202" t="n">
         <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3021</v>
+        <v>3031</v>
       </c>
       <c r="B203" t="n">
         <v>1222.617</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3030</v>
+        <v>3039</v>
       </c>
       <c r="B204" t="n">
         <v>1219.798</v>
@@ -6949,18 +6949,18 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G204" t="n">
         <v>1.22</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3054</v>
+        <v>3056</v>
       </c>
       <c r="B205" t="n">
         <v>1207.273</v>
@@ -6981,18 +6981,18 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G205" t="n">
         <v>1.21</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3106</v>
+        <v>3108</v>
       </c>
       <c r="B206" t="n">
         <v>1172.514</v>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G206" t="n">
         <v>1.17</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3141</v>
+        <v>3146</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3152</v>
+        <v>3158</v>
       </c>
       <c r="B208" t="n">
         <v>1146.05</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G208" t="n">
         <v>1.15</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3174</v>
+        <v>3179</v>
       </c>
       <c r="B209" t="n">
         <v>1132.544</v>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G209" t="n">
         <v>1.13</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3189</v>
+        <v>3191</v>
       </c>
       <c r="B210" t="n">
         <v>1126.872</v>
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3197</v>
+        <v>3200</v>
       </c>
       <c r="B211" t="n">
         <v>1122.12</v>
@@ -7173,18 +7173,18 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3212</v>
+        <v>3216</v>
       </c>
       <c r="B212" t="n">
         <v>1111.893</v>
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3215</v>
+        <v>3219</v>
       </c>
       <c r="B213" t="n">
         <v>1111.63</v>
@@ -7237,18 +7237,18 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3228</v>
+        <v>3234</v>
       </c>
       <c r="B214" t="n">
         <v>1102.434</v>
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3248</v>
+        <v>3251</v>
       </c>
       <c r="B215" t="n">
         <v>1093.128</v>
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3269</v>
+        <v>3271</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3269</v>
+        <v>3271</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
@@ -7365,18 +7365,18 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3286</v>
+        <v>3292</v>
       </c>
       <c r="B218" t="n">
         <v>1070.911</v>
@@ -7397,18 +7397,18 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G218" t="n">
         <v>1.07</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3290</v>
+        <v>3298</v>
       </c>
       <c r="B219" t="n">
         <v>1069.408</v>
@@ -7429,18 +7429,18 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="B220" t="n">
         <v>1059.625</v>
@@ -7461,18 +7461,18 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G220" t="n">
         <v>1.06</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -7493,18 +7493,18 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -7525,18 +7525,18 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="B223" t="n">
         <v>1006.935</v>
@@ -7557,18 +7557,18 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G223" t="n">
         <v>1.01</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3392</v>
+        <v>3389</v>
       </c>
       <c r="B224" t="n">
         <v>984.373</v>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779148202216</v>
+        <v>1779156002254</v>
       </c>
       <c r="G224" t="n">
         <v>0.98</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.22224787037</v>
+        <v>46161.31252608796</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -467,7 +467,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>90360.864</v>
+        <v>90491.412</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -485,21 +485,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G2" t="n">
-        <v>90.36</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>80845.08199999999</v>
+        <v>81621.079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>37956.283</v>
+        <v>37944.272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G4" t="n">
-        <v>37.96</v>
+        <v>37.94</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="5">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G5" t="n">
         <v>29.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         <v>91</v>
       </c>
       <c r="B6" t="n">
-        <v>26668.92</v>
+        <v>26639.14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -613,21 +613,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G6" t="n">
-        <v>26.67</v>
+        <v>26.64</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" t="n">
-        <v>26624.834</v>
+        <v>26554.882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -645,21 +645,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G7" t="n">
-        <v>26.62</v>
+        <v>26.55</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B8" t="n">
-        <v>25354.315</v>
+        <v>25899.021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -677,21 +677,21 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G8" t="n">
-        <v>25.35</v>
+        <v>25.9</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="n">
-        <v>21391.106</v>
+        <v>21497.481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G9" t="n">
-        <v>21.39</v>
+        <v>21.5</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         <v>175</v>
       </c>
       <c r="B10" t="n">
-        <v>16501.504</v>
+        <v>16281.083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G10" t="n">
-        <v>16.5</v>
+        <v>16.28</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>212</v>
       </c>
       <c r="B11" t="n">
-        <v>14139.885</v>
+        <v>14018.69</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,21 +773,21 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G11" t="n">
-        <v>14.14</v>
+        <v>14.02</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B12" t="n">
-        <v>13062.151</v>
+        <v>12930.004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G12" t="n">
-        <v>13.06</v>
+        <v>12.93</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B13" t="n">
-        <v>12471.668</v>
+        <v>12598.725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -837,21 +837,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G13" t="n">
-        <v>12.47</v>
+        <v>12.6</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B14" t="n">
-        <v>11445.012</v>
+        <v>11606.473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -869,21 +869,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G14" t="n">
-        <v>11.45</v>
+        <v>11.61</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B15" t="n">
-        <v>10376.047</v>
+        <v>10362.024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G15" t="n">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B16" t="n">
-        <v>10139.4</v>
+        <v>10233.441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G16" t="n">
-        <v>10.14</v>
+        <v>10.23</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B17" t="n">
-        <v>9252.380999999999</v>
+        <v>9173.076999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G17" t="n">
-        <v>9.25</v>
+        <v>9.17</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B18" t="n">
-        <v>9229.285</v>
+        <v>9149.982</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G18" t="n">
-        <v>9.23</v>
+        <v>9.15</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B19" t="n">
-        <v>8387.036</v>
+        <v>8532.804</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G19" t="n">
-        <v>8.390000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B20" t="n">
-        <v>8252.09</v>
+        <v>8287.675999999999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G20" t="n">
-        <v>8.25</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B21" t="n">
-        <v>7877.188</v>
+        <v>7942.155</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G21" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B22" t="n">
-        <v>7731.099</v>
+        <v>7780.081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G22" t="n">
-        <v>7.73</v>
+        <v>7.78</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B23" t="n">
-        <v>7730.956</v>
+        <v>7779.941</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G23" t="n">
-        <v>7.73</v>
+        <v>7.78</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="24">
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B25" t="n">
-        <v>7289.86</v>
+        <v>7391.473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G25" t="n">
-        <v>7.29</v>
+        <v>7.39</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B26" t="n">
-        <v>6473.386</v>
+        <v>6388.016</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G26" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B27" t="n">
-        <v>6149.447</v>
+        <v>6154.172</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G27" t="n">
         <v>6.15</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="28">
@@ -1299,7 +1299,7 @@
         <v>702</v>
       </c>
       <c r="B28" t="n">
-        <v>5899.196</v>
+        <v>5901.348</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G28" t="n">
         <v>5.9</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="29">
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B30" t="n">
-        <v>5453.212</v>
+        <v>5467.894</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1381,30 +1381,30 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G30" t="n">
-        <v>5.45</v>
+        <v>5.47</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="B31" t="n">
-        <v>5177.898</v>
+        <v>5320.329</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rajiv Bajaj</t>
+          <t>Mangal Prabhat Lodha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1413,30 +1413,30 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G31" t="n">
-        <v>5.18</v>
+        <v>5.32</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B32" t="n">
-        <v>5177.898</v>
+        <v>5208.666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sanjiv Bajaj</t>
+          <t>Nusli Wadia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1445,30 +1445,30 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779156002253</v>
+        <v>1779172202278</v>
       </c>
       <c r="G32" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002636574</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B33" t="n">
-        <v>5150.844</v>
+        <v>5184.622</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nusli Wadia</t>
+          <t>Rajiv Bajaj</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1477,30 +1477,30 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G33" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="B34" t="n">
-        <v>5084.179</v>
+        <v>5184.622</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mangal Prabhat Lodha</t>
+          <t>Sanjiv Bajaj</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1509,18 +1509,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G34" t="n">
-        <v>5.08</v>
+        <v>5.18</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B35" t="n">
         <v>5071.275</v>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B36" t="n">
-        <v>5050.542</v>
+        <v>5056.082</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G36" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B37" t="n">
-        <v>5050.537</v>
+        <v>5056.077</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1605,30 +1605,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G37" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="B38" t="n">
-        <v>4996.846</v>
+        <v>5055.761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chandru Raheja</t>
+          <t>Kailashchandra Nuwal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Industrial explosives</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="39">
@@ -1651,16 +1651,16 @@
         <v>848</v>
       </c>
       <c r="B39" t="n">
-        <v>4986.26</v>
+        <v>5010.079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kailashchandra Nuwal</t>
+          <t>Chandru Raheja</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Industrial explosives</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G39" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="40">
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="B41" t="n">
-        <v>4953.328</v>
+        <v>4875.158</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G41" t="n">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="42">
@@ -1765,21 +1765,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B43" t="n">
-        <v>4651.997</v>
+        <v>4645.435</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G43" t="n">
         <v>4.65</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B44" t="n">
-        <v>4599.875</v>
+        <v>4640.022</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1829,30 +1829,30 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G44" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B45" t="n">
-        <v>4394.112</v>
+        <v>4398.875</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abhay Firodia</t>
+          <t>Mahendra Choksi &amp; family</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Paints</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1861,30 +1861,30 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B46" t="n">
-        <v>4371.578</v>
+        <v>4394.112</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mahendra Choksi &amp; family</t>
+          <t>Abhay Firodia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Paints</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G46" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="47">
@@ -1907,7 +1907,7 @@
         <v>988</v>
       </c>
       <c r="B47" t="n">
-        <v>4311.644</v>
+        <v>4304.651</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G47" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B48" t="n">
-        <v>4287.14</v>
+        <v>4286.893</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="B49" t="n">
-        <v>4091.609</v>
+        <v>4088.995</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G49" t="n">
         <v>4.09</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1090</v>
+        <v>1079</v>
       </c>
       <c r="B51" t="n">
-        <v>3920.534</v>
+        <v>3976.858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G51" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1118</v>
+        <v>1095</v>
       </c>
       <c r="B52" t="n">
-        <v>3837.168</v>
+        <v>3893.492</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G52" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1124</v>
+        <v>1136</v>
       </c>
       <c r="B53" t="n">
-        <v>3812.24</v>
+        <v>3765.59</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nirmal Minda</t>
+          <t>N.R. Narayana Murthy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Auto parts</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2117,21 +2117,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G53" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B54" t="n">
-        <v>3742.953</v>
+        <v>3746.775</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G54" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B55" t="n">
-        <v>3742.915</v>
+        <v>3746.739</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G55" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B56" t="n">
-        <v>3742.915</v>
+        <v>3746.739</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2213,30 +2213,30 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G56" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B57" t="n">
-        <v>3692.361</v>
+        <v>3704.765</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>N.R. Narayana Murthy</t>
+          <t>Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Biopharmaceuticals</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2245,30 +2245,30 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779156002253</v>
+        <v>1779172202279</v>
       </c>
       <c r="G57" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.31252607639</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="B58" t="n">
-        <v>3673.219</v>
+        <v>3701.015</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw</t>
+          <t>Nirmal Minda</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Biopharmaceuticals</t>
+          <t>Auto parts</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G58" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1211</v>
+        <v>1184</v>
       </c>
       <c r="B59" t="n">
-        <v>3542.882</v>
+        <v>3623.491</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G59" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="B60" t="n">
-        <v>3539.965</v>
+        <v>3564.214</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,30 +2341,30 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G60" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="B61" t="n">
-        <v>3517.715</v>
+        <v>3534.259</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>G. M. Rao</t>
+          <t>P.V. Ramprasad Reddy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2373,30 +2373,30 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G61" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="B62" t="n">
-        <v>3494.663</v>
+        <v>3528.552</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>P.V. Ramprasad Reddy</t>
+          <t>Sanjiv Goenka</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2405,30 +2405,30 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G62" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1234</v>
+        <v>1219</v>
       </c>
       <c r="B63" t="n">
-        <v>3463.696</v>
+        <v>3519.085</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sanjiv Goenka</t>
+          <t>G. M. Rao</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1236</v>
+        <v>1220</v>
       </c>
       <c r="B64" t="n">
-        <v>3461.525</v>
+        <v>3517.475</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2469,21 +2469,21 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G64" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="B65" t="n">
-        <v>3457.731</v>
+        <v>3475.298</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B66" t="n">
-        <v>3437.408</v>
+        <v>3424.632</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G66" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B67" t="n">
-        <v>3426.048</v>
+        <v>3414.959</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B68" t="n">
-        <v>3358.115</v>
+        <v>3361.025</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G68" t="n">
         <v>3.36</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B70" t="n">
         <v>3221.232</v>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1323</v>
+        <v>1332</v>
       </c>
       <c r="B71" t="n">
-        <v>3212.603</v>
+        <v>3188.805</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2693,21 +2693,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1357</v>
+        <v>1342</v>
       </c>
       <c r="B72" t="n">
-        <v>3152.624</v>
+        <v>3176.501</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G72" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="73">
@@ -2757,30 +2757,30 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B74" t="n">
-        <v>3085.258</v>
+        <v>3101.264</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nikhil Kamath</t>
+          <t>Madhukar Parekh</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Adhesives</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2789,30 +2789,30 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G74" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="B75" t="n">
-        <v>3068.446</v>
+        <v>3085.258</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Madhukar Parekh</t>
+          <t>Nikhil Kamath</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Adhesives</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2821,30 +2821,30 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G75" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="B76" t="n">
-        <v>3063.21</v>
+        <v>3079.961</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arvind Tiku</t>
+          <t>Surender Saluja</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Renewable energy, real estate</t>
+          <t>Solar energy</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2853,30 +2853,30 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G76" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B77" t="n">
-        <v>3047.215</v>
+        <v>3063.21</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Surender Saluja</t>
+          <t>Arvind Tiku</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Solar energy</t>
+          <t>Renewable energy, real estate</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2885,30 +2885,30 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G77" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1406</v>
+        <v>1391</v>
       </c>
       <c r="B78" t="n">
-        <v>3011.155</v>
+        <v>3060.146</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mahima Datla</t>
+          <t>Ramesh Juneja</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Vaccines</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G78" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="B79" t="n">
-        <v>3011.141</v>
+        <v>3033.557</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2949,30 +2949,30 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B80" t="n">
-        <v>3003.735</v>
+        <v>3011.155</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ramesh Juneja</t>
+          <t>Mahima Datla</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Vaccines</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2981,30 +2981,30 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="B81" t="n">
-        <v>2991.225</v>
+        <v>3008.474</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Leena Tewari</t>
+          <t>Rajeev Juneja</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Phamaceuticals</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3013,30 +3013,30 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G81" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1430</v>
+        <v>1415</v>
       </c>
       <c r="B82" t="n">
-        <v>2953.701</v>
+        <v>2991.225</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rajeev Juneja</t>
+          <t>Leena Tewari</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Phamaceuticals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G82" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B83" t="n">
-        <v>2946.291</v>
+        <v>2939.516</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3077,30 +3077,30 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G83" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="B84" t="n">
-        <v>2895</v>
+        <v>2904.772</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Karthik Sarma</t>
+          <t>Senapathy Gopalakrishnan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Hedge fund</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3109,30 +3109,30 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1482</v>
+        <v>1460</v>
       </c>
       <c r="B85" t="n">
-        <v>2835.87</v>
+        <v>2895</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Senapathy Gopalakrishnan</t>
+          <t>Karthik Sarma</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Hedge fund</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G85" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B86" t="n">
-        <v>2815.045</v>
+        <v>2810.689</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G86" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,30 +3205,30 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="B88" t="n">
-        <v>2749.231</v>
+        <v>2744.674</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gurbachan Singh Dhingra</t>
+          <t>Harsh Goenka</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paints</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3237,30 +3237,30 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G88" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1536</v>
+        <v>1551</v>
       </c>
       <c r="B89" t="n">
-        <v>2749.231</v>
+        <v>2717.279</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kuldip Singh Dhingra</t>
+          <t>M.Satyanarayana Reddy</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paints</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3269,30 +3269,30 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G89" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="B90" t="n">
-        <v>2744.293</v>
+        <v>2707.811</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Harsh Goenka</t>
+          <t>Ranjan Pai</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Education, healthcare</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3301,30 +3301,30 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G90" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="B91" t="n">
-        <v>2717.279</v>
+        <v>2693.898</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>M.Satyanarayana Reddy</t>
+          <t>Gurbachan Singh Dhingra</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Paints</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G91" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="92">
@@ -3347,16 +3347,16 @@
         <v>1558</v>
       </c>
       <c r="B92" t="n">
-        <v>2707.811</v>
+        <v>2693.898</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ranjan Pai</t>
+          <t>Kuldip Singh Dhingra</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Education, healthcare</t>
+          <t>Paints</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G92" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1588</v>
+        <v>1573</v>
       </c>
       <c r="B93" t="n">
-        <v>2627.533</v>
+        <v>2654.904</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G93" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="B94" t="n">
-        <v>2622.743</v>
+        <v>2612.233</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G94" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="B95" t="n">
-        <v>2622.743</v>
+        <v>2612.233</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G95" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="B96" t="n">
-        <v>2622.743</v>
+        <v>2612.233</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G96" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="B97" t="n">
-        <v>2622.743</v>
+        <v>2612.233</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G97" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1620</v>
+        <v>1604</v>
       </c>
       <c r="B98" t="n">
-        <v>2587.632</v>
+        <v>2611.855</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3557,30 +3557,30 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G98" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1642</v>
+        <v>1629</v>
       </c>
       <c r="B99" t="n">
-        <v>2552.876</v>
+        <v>2576.349</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Devi Shetty</t>
+          <t>Inder Jaisinghani</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3589,30 +3589,30 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G99" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1646</v>
+        <v>1633</v>
       </c>
       <c r="B100" t="n">
-        <v>2551.171</v>
+        <v>2565.002</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Inder Jaisinghani</t>
+          <t>Devi Shetty</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3621,30 +3621,30 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1660</v>
+        <v>1650</v>
       </c>
       <c r="B101" t="n">
-        <v>2515.184</v>
+        <v>2542.867</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yusuf Hamied</t>
+          <t>Nandan Nilekani</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3653,30 +3653,30 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G101" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1675</v>
+        <v>1651</v>
       </c>
       <c r="B102" t="n">
-        <v>2494.136</v>
+        <v>2539.459</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nandan Nilekani</t>
+          <t>Abhay Soi</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3685,30 +3685,30 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1679</v>
+        <v>1656</v>
       </c>
       <c r="B103" t="n">
-        <v>2490.279</v>
+        <v>2523.931</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Abhay Soi</t>
+          <t>Anand Deshpande</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3717,30 +3717,30 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G103" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1691</v>
+        <v>1665</v>
       </c>
       <c r="B104" t="n">
-        <v>2465.589</v>
+        <v>2502.637</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ramesh Jaisinghani</t>
+          <t>Yusuf Hamied</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cables and wires</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3749,30 +3749,30 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G104" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1699</v>
+        <v>1680</v>
       </c>
       <c r="B105" t="n">
-        <v>2457.642</v>
+        <v>2489.52</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ajay Jaisinghani</t>
+          <t>Ramesh Jaisinghani</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wires and cables</t>
+          <t>Cables and wires</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3781,30 +3781,30 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1718</v>
+        <v>1684</v>
       </c>
       <c r="B106" t="n">
-        <v>2435.956</v>
+        <v>2481.23</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ajay Bhardwaj</t>
+          <t>Ajay Jaisinghani</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Biopharma</t>
+          <t>Wires and cables</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3813,30 +3813,30 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G106" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1739</v>
+        <v>1706</v>
       </c>
       <c r="B107" t="n">
-        <v>2410.942</v>
+        <v>2449.678</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Anand Deshpande</t>
+          <t>Ajay Bhardwaj</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biopharma</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3845,30 +3845,30 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G107" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1770</v>
+        <v>1726</v>
       </c>
       <c r="B108" t="n">
-        <v>2366.47</v>
+        <v>2429.582</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sandeep Engineer</t>
+          <t>Bhadresh Shah</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Plastic pipes</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3877,30 +3877,30 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G108" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1775</v>
+        <v>1756</v>
       </c>
       <c r="B109" t="n">
-        <v>2355.803</v>
+        <v>2381.939</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bhadresh Shah</t>
+          <t>Prem Kumar Arora</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3909,30 +3909,30 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G109" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1785</v>
+        <v>1765</v>
       </c>
       <c r="B110" t="n">
-        <v>2338.44</v>
+        <v>2378.801</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prem Kumar Arora</t>
+          <t>Salil Singhal</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Agrochemicals</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3941,30 +3941,30 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G110" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1788</v>
+        <v>1822</v>
       </c>
       <c r="B111" t="n">
-        <v>2328.854</v>
+        <v>2292.243</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Salil Singhal</t>
+          <t>Sunil Vachani</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Agrochemicals</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3973,30 +3973,30 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G111" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="B112" t="n">
-        <v>2271.057</v>
+        <v>2278.094</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rishad Naoroji</t>
+          <t>Rafique Malik</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Consumer goods, real estate</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4005,30 +4005,30 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G112" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B113" t="n">
-        <v>2270.559</v>
+        <v>2271.057</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rafique Malik</t>
+          <t>Rishad Naoroji</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Consumer goods, real estate</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4037,30 +4037,30 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B114" t="n">
-        <v>2250.673</v>
+        <v>2253.546</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Acharya Balkrishna</t>
+          <t>Sandeep Engineer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Plastic pipes</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4069,30 +4069,30 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1867</v>
+        <v>1860</v>
       </c>
       <c r="B115" t="n">
-        <v>2243.02</v>
+        <v>2250.673</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sunil Vachani</t>
+          <t>Acharya Balkrishna</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G115" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1870</v>
+        <v>1862</v>
       </c>
       <c r="B116" t="n">
-        <v>2237.983</v>
+        <v>2249.071</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4133,21 +4133,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G116" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1895</v>
+        <v>1870</v>
       </c>
       <c r="B117" t="n">
-        <v>2203.177</v>
+        <v>2241.451</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4165,30 +4165,30 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G117" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B118" t="n">
-        <v>2189.241</v>
+        <v>2191.007</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jupally Rameshwar Rao</t>
+          <t>Vivek Chand Burman</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4197,30 +4197,30 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="B119" t="n">
-        <v>2182.036</v>
+        <v>2189.241</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Vivek Chand Burman</t>
+          <t>Jupally Rameshwar Rao</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4229,30 +4229,30 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G119" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1940</v>
+        <v>1929</v>
       </c>
       <c r="B120" t="n">
-        <v>2154.507</v>
+        <v>2169.892</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kabir Mulchandani</t>
+          <t>Anurang Jain</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Auto parts</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4261,30 +4261,30 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G120" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1948</v>
+        <v>1942</v>
       </c>
       <c r="B121" t="n">
-        <v>2142.349</v>
+        <v>2154.507</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Anurang Jain</t>
+          <t>Kabir Mulchandani</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Auto parts</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4293,30 +4293,30 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G121" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1977</v>
+        <v>1960</v>
       </c>
       <c r="B122" t="n">
-        <v>2105.407</v>
+        <v>2133.961</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ajay Parekh</t>
+          <t>Sanjeev Bikhchandani</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Adhesives</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4325,25 +4325,25 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G122" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1983</v>
+        <v>1968</v>
       </c>
       <c r="B123" t="n">
-        <v>2101.476</v>
+        <v>2126.555</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Narendrakumar Parekh</t>
+          <t>Ajay Parekh</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4357,30 +4357,30 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G123" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1984</v>
+        <v>1971</v>
       </c>
       <c r="B124" t="n">
-        <v>2100.998</v>
+        <v>2121.361</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kishore Jain</t>
+          <t>Narendrakumar Parekh</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Jewellery</t>
+          <t>Adhesives</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G124" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="125">
@@ -4403,16 +4403,16 @@
         <v>1985</v>
       </c>
       <c r="B125" t="n">
-        <v>2100</v>
+        <v>2100.998</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Aravind Srinivas</t>
+          <t>Kishore Jain</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial intelligence </t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4421,30 +4421,30 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1997</v>
+        <v>1986</v>
       </c>
       <c r="B126" t="n">
-        <v>2091.564</v>
+        <v>2100</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sanjeev Bikhchandani</t>
+          <t>Aravind Srinivas</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t xml:space="preserve">Artificial intelligence </t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4453,30 +4453,30 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G126" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="B127" t="n">
-        <v>2054.429</v>
+        <v>2073.764</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jitendra Virwani</t>
+          <t>Girdhari Jaisinghani</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4485,30 +4485,30 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G127" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="B128" t="n">
-        <v>2054.069</v>
+        <v>2064.139</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Girdhari Jaisinghani</t>
+          <t>Lalit Khaitan</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4517,30 +4517,30 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G128" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2061</v>
+        <v>2016</v>
       </c>
       <c r="B129" t="n">
-        <v>2023.611</v>
+        <v>2062.573</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>T.S. Kalyanaraman</t>
+          <t>Jitendra Virwani</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Jewelry</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4549,30 +4549,30 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G129" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2064</v>
+        <v>2020</v>
       </c>
       <c r="B130" t="n">
-        <v>2017.058</v>
+        <v>2058.287</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Radha Vembu</t>
+          <t>K. Dinesh</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Business software</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4581,30 +4581,30 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G130" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="B131" t="n">
-        <v>2016.395</v>
+        <v>2025.386</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>K. Dinesh</t>
+          <t>T.S. Kalyanaraman</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Jewelry</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4613,30 +4613,30 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G131" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2122</v>
+        <v>2068</v>
       </c>
       <c r="B132" t="n">
-        <v>1971.957</v>
+        <v>2017.058</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>G. Rajendran</t>
+          <t>Radha Vembu</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Jewellery</t>
+          <t>Business software</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4645,30 +4645,30 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G132" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2142</v>
+        <v>2122</v>
       </c>
       <c r="B133" t="n">
-        <v>1952.485</v>
+        <v>1971.957</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lalit Khaitan</t>
+          <t>G. Rajendran</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4677,25 +4677,25 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G133" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2147</v>
+        <v>2135</v>
       </c>
       <c r="B134" t="n">
-        <v>1950.98</v>
+        <v>1955.751</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hemendra Kothari</t>
+          <t>Raamdeo Agrawal</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4709,30 +4709,30 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G134" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2154</v>
+        <v>2147</v>
       </c>
       <c r="B135" t="n">
-        <v>1943.862</v>
+        <v>1950.98</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>P.V. Krishna Reddy</t>
+          <t>Hemendra Kothari</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4741,30 +4741,30 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G135" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2171</v>
+        <v>2156</v>
       </c>
       <c r="B136" t="n">
-        <v>1920.8</v>
+        <v>1943.862</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Raamdeo Agrawal</t>
+          <t>P.V. Krishna Reddy</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G136" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2207</v>
+        <v>2182</v>
       </c>
       <c r="B137" t="n">
-        <v>1888.225</v>
+        <v>1908.24</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G137" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="B138" t="n">
         <v>1871.373</v>
@@ -4837,25 +4837,25 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2238</v>
+        <v>2232</v>
       </c>
       <c r="B139" t="n">
-        <v>1853.32</v>
+        <v>1861.504</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Anju Agarwal</t>
+          <t>Satish Mehta</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4869,25 +4869,25 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G139" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2253</v>
+        <v>2241</v>
       </c>
       <c r="B140" t="n">
-        <v>1843.48</v>
+        <v>1853.32</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Satish Mehta</t>
+          <t>Anju Agarwal</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G140" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2260</v>
+        <v>2247</v>
       </c>
       <c r="B141" t="n">
-        <v>1831.051</v>
+        <v>1848.844</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -4933,30 +4933,30 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G141" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2276</v>
+        <v>2264</v>
       </c>
       <c r="B142" t="n">
-        <v>1813.92</v>
+        <v>1826.941</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Girdhari Lal Bawri</t>
+          <t>Anil Gupta</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cables</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4965,30 +4965,30 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G142" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2280</v>
+        <v>2275</v>
       </c>
       <c r="B143" t="n">
-        <v>1809.194</v>
+        <v>1813.92</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Anil Gupta</t>
+          <t>Girdhari Lal Bawri</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cables</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2319</v>
+        <v>2302</v>
       </c>
       <c r="B144" t="n">
-        <v>1766.869</v>
+        <v>1788.292</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5029,30 +5029,30 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G144" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B145" t="n">
-        <v>1760.675</v>
+        <v>1767.773</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Banwari Lal Bawri</t>
+          <t>Pawan Munjal</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5061,30 +5061,30 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G145" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2337</v>
+        <v>2331</v>
       </c>
       <c r="B146" t="n">
-        <v>1755.532</v>
+        <v>1760.675</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pawan Munjal</t>
+          <t>Banwari Lal Bawri</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="B147" t="n">
         <v>1716.6</v>
@@ -5125,30 +5125,30 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G147" t="n">
         <v>1.72</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2402</v>
+        <v>2392</v>
       </c>
       <c r="B148" t="n">
-        <v>1699.828</v>
+        <v>1712.104</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dhruv Sawhney</t>
+          <t>Arvind Lal</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Engineering, sugar</t>
+          <t>Medical diagnostics</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5157,30 +5157,30 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G148" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2419</v>
+        <v>2394</v>
       </c>
       <c r="B149" t="n">
-        <v>1684.006</v>
+        <v>1708.887</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Suman Munjal</t>
+          <t>Shyam Bhartia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Pharmaceuticals, food</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5189,30 +5189,30 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G149" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2425</v>
+        <v>2396</v>
       </c>
       <c r="B150" t="n">
-        <v>1677.252</v>
+        <v>1704.524</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Renu Munjal</t>
+          <t>Hari Bhartia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5221,30 +5221,30 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G150" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2426</v>
+        <v>2407</v>
       </c>
       <c r="B151" t="n">
-        <v>1676.783</v>
+        <v>1695.593</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Shyam Bhartia</t>
+          <t>Suman Munjal</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, food</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5253,30 +5253,30 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G151" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2429</v>
+        <v>2413</v>
       </c>
       <c r="B152" t="n">
-        <v>1674.745</v>
+        <v>1693.42</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Aloke Lohia</t>
+          <t>Motilal Oswal</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Petrochemicals</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5285,30 +5285,30 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G152" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2430</v>
+        <v>2414</v>
       </c>
       <c r="B153" t="n">
-        <v>1672.564</v>
+        <v>1693.328</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hari Bhartia</t>
+          <t>Viren Doshi</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5317,30 +5317,30 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G153" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2432</v>
+        <v>2420</v>
       </c>
       <c r="B154" t="n">
-        <v>1671.06</v>
+        <v>1688.779</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Viren Doshi</t>
+          <t>Renu Munjal</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5349,30 +5349,30 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G154" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="B155" t="n">
-        <v>1664.253</v>
+        <v>1680.313</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Arvind Lal</t>
+          <t>Aloke Lohia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Medical diagnostics</t>
+          <t>Petrochemicals</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5381,30 +5381,30 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G155" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2443</v>
+        <v>2433</v>
       </c>
       <c r="B156" t="n">
-        <v>1663.143</v>
+        <v>1674.233</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Motilal Oswal</t>
+          <t>Dhruv Sawhney</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Engineering, sugar</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G156" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2450</v>
+        <v>2442</v>
       </c>
       <c r="B157" t="n">
-        <v>1657.112</v>
+        <v>1665.522</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G157" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2466</v>
+        <v>2443</v>
       </c>
       <c r="B158" t="n">
-        <v>1638.82</v>
+        <v>1665.153</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -5477,30 +5477,30 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G158" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2469</v>
+        <v>2461</v>
       </c>
       <c r="B159" t="n">
-        <v>1633.314</v>
+        <v>1645.717</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Premchand Godha</t>
+          <t>R.G. Chandramogan</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5509,30 +5509,30 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G159" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2490</v>
+        <v>2466</v>
       </c>
       <c r="B160" t="n">
-        <v>1607.589</v>
+        <v>1639.031</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>R.G. Chandramogan</t>
+          <t>Premchand Godha</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5541,30 +5541,30 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G160" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="B161" t="n">
-        <v>1602.739</v>
+        <v>1597.238</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saroj Rani Gupta</t>
+          <t>S.D. Shibulal</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Steel tubes</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5573,30 +5573,30 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2540</v>
+        <v>2505</v>
       </c>
       <c r="B162" t="n">
-        <v>1568.294</v>
+        <v>1593.089</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>S.D. Shibulal</t>
+          <t>Saroj Rani Gupta</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>Steel tubes</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5605,30 +5605,30 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G162" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="B163" t="n">
-        <v>1558.753</v>
+        <v>1563.836</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>G.V. Prasad</t>
+          <t>D.V. Manjunatha</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Solar panels</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5637,25 +5637,25 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G163" t="n">
         <v>1.56</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="B164" t="n">
-        <v>1554.411</v>
+        <v>1553.985</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Satish Reddy</t>
+          <t>G.V. Prasad</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G164" t="n">
         <v>1.55</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2567</v>
+        <v>2574</v>
       </c>
       <c r="B165" t="n">
-        <v>1553.807</v>
+        <v>1550.093</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -5701,30 +5701,30 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2598</v>
+        <v>2577</v>
       </c>
       <c r="B166" t="n">
-        <v>1534.485</v>
+        <v>1549.448</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ronnie Screwvala</t>
+          <t>Satish Reddy</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>edtech, entertainment</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5733,30 +5733,30 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G166" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2602</v>
+        <v>2585</v>
       </c>
       <c r="B167" t="n">
-        <v>1532.656</v>
+        <v>1543.514</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>D.V. Manjunatha</t>
+          <t>Ronnie Screwvala</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Solar panels</t>
+          <t>edtech, entertainment</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5765,30 +5765,30 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G167" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2628</v>
+        <v>2612</v>
       </c>
       <c r="B168" t="n">
-        <v>1500</v>
+        <v>1521.801</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prasanna Sankar</t>
+          <t>Manoj Upadhyay</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>solar energy</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5797,30 +5797,30 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G168" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2640</v>
+        <v>2619</v>
       </c>
       <c r="B169" t="n">
-        <v>1499.185</v>
+        <v>1515.317</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Manoj Upadhyay</t>
+          <t>Shamsheer Vayalil</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>solar energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5829,30 +5829,30 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G169" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2648</v>
+        <v>2629</v>
       </c>
       <c r="B170" t="n">
-        <v>1494.058</v>
+        <v>1500</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Shamsheer Vayalil</t>
+          <t>Prasanna Sankar</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5861,30 +5861,30 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G170" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2659</v>
+        <v>2651</v>
       </c>
       <c r="B171" t="n">
-        <v>1485.365</v>
+        <v>1490.919</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sekar Vembu</t>
+          <t>Chaitanya Desai</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Business software</t>
+          <t>Electric cables</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5893,30 +5893,30 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G171" t="n">
         <v>1.49</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2665</v>
+        <v>2651</v>
       </c>
       <c r="B172" t="n">
-        <v>1480.068</v>
+        <v>1490.919</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chaitanya Desai</t>
+          <t>Kushal Desai</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Electric cables</t>
+          <t>Electrical cables</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5925,30 +5925,30 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G172" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2665</v>
+        <v>2658</v>
       </c>
       <c r="B173" t="n">
-        <v>1480.068</v>
+        <v>1485.365</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kushal Desai</t>
+          <t>Sekar Vembu</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Electrical cables</t>
+          <t>Business software</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G173" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2692</v>
+        <v>2673</v>
       </c>
       <c r="B174" t="n">
-        <v>1454.351</v>
+        <v>1473.779</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G174" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2697</v>
+        <v>2676</v>
       </c>
       <c r="B175" t="n">
-        <v>1452.72</v>
+        <v>1472.145</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -6021,21 +6021,21 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G175" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2702</v>
+        <v>2677</v>
       </c>
       <c r="B176" t="n">
-        <v>1448.537</v>
+        <v>1471.511</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -6053,30 +6053,30 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779156002254</v>
+        <v>1779172202279</v>
       </c>
       <c r="G176" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002637732</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2736</v>
+        <v>2726</v>
       </c>
       <c r="B177" t="n">
-        <v>1414.525</v>
+        <v>1425.809</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rajeev Gulati</t>
+          <t>Mofatraj Munot</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6085,30 +6085,30 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G177" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2739</v>
+        <v>2731</v>
       </c>
       <c r="B178" t="n">
-        <v>1410.982</v>
+        <v>1420.221</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Aditya Khemka</t>
+          <t>Shrikant Badve</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Security solutions</t>
+          <t>auto parts</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6117,30 +6117,30 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G178" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2741</v>
+        <v>2737</v>
       </c>
       <c r="B179" t="n">
-        <v>1409.964</v>
+        <v>1414.525</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Mofatraj Munot</t>
+          <t>Rajeev Gulati</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="B180" t="n">
         <v>1409.921</v>
@@ -6181,30 +6181,30 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2773</v>
+        <v>2745</v>
       </c>
       <c r="B181" t="n">
-        <v>1397.551</v>
+        <v>1408.802</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Shrikant Badve</t>
+          <t>Habil Khorakiwala</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>auto parts</t>
+          <t>pharmaceuticals</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G181" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="B182" t="n">
-        <v>1393.31</v>
+        <v>1395.84</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G182" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="B183" t="n">
-        <v>1389.701</v>
+        <v>1390.731</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G183" t="n">
         <v>1.39</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2810</v>
+        <v>2786</v>
       </c>
       <c r="B184" t="n">
-        <v>1372.472</v>
+        <v>1387.281</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -6309,30 +6309,30 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G184" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2812</v>
+        <v>2788</v>
       </c>
       <c r="B185" t="n">
-        <v>1369.934</v>
+        <v>1384.891</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Habil Khorakiwala</t>
+          <t>Aditya Khemka</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>pharmaceuticals</t>
+          <t>Security solutions</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G185" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2823</v>
+        <v>2817</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,30 +6373,30 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2824</v>
+        <v>2818</v>
       </c>
       <c r="B187" t="n">
-        <v>1361.194</v>
+        <v>1360.832</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Vinod Saraf</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Readymade garments</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6405,30 +6405,30 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G187" t="n">
         <v>1.36</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2840</v>
+        <v>2834</v>
       </c>
       <c r="B188" t="n">
-        <v>1344.894</v>
+        <v>1349.816</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Deepinder Goyal</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Readymade garments</t>
+          <t>Food delivery service</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6437,30 +6437,30 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2881</v>
+        <v>2839</v>
       </c>
       <c r="B189" t="n">
-        <v>1316.638</v>
+        <v>1344.394</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Deepinder Goyal</t>
+          <t>Vinod Saraf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Food delivery service</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6469,30 +6469,30 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G189" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2901</v>
+        <v>2882</v>
       </c>
       <c r="B190" t="n">
-        <v>1304.387</v>
+        <v>1316.645</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bina Chhabria</t>
+          <t>Irfan Razack</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Alcoholic beverages</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6501,30 +6501,30 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G190" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2914</v>
+        <v>2883</v>
       </c>
       <c r="B191" t="n">
-        <v>1297.945</v>
+        <v>1316.631</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bhikhabai Virani</t>
+          <t>Noaman Razack</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6533,30 +6533,30 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G191" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2922</v>
+        <v>2883</v>
       </c>
       <c r="B192" t="n">
-        <v>1293.862</v>
+        <v>1316.631</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Kamlesh Jain</t>
+          <t>Rezwan Razack</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Recycling</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6565,30 +6565,30 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G192" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2950</v>
+        <v>2898</v>
       </c>
       <c r="B193" t="n">
-        <v>1276.294</v>
+        <v>1309.339</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Aluru Jagadish Prasad</t>
+          <t>Bina Chhabria</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Alcoholic beverages</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6597,30 +6597,30 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G193" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2957</v>
+        <v>2903</v>
       </c>
       <c r="B194" t="n">
-        <v>1270.546</v>
+        <v>1305.492</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Onkar Kanwar</t>
+          <t>Aluru Jagadish Prasad</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Tires</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6629,30 +6629,30 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G194" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2958</v>
+        <v>2917</v>
       </c>
       <c r="B195" t="n">
-        <v>1270.507</v>
+        <v>1297.945</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Irfan Razack</t>
+          <t>Bhikhabai Virani</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6661,30 +6661,30 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2959</v>
+        <v>2947</v>
       </c>
       <c r="B196" t="n">
-        <v>1270.493</v>
+        <v>1281.616</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Noaman Razack</t>
+          <t>Kirit Doshi</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6693,30 +6693,30 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G196" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="B197" t="n">
-        <v>1270.493</v>
+        <v>1270.934</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Rezwan Razack</t>
+          <t>Onkar Kanwar</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Tires</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6725,30 +6725,30 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="B198" t="n">
-        <v>1264.62</v>
+        <v>1267.152</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kirit Doshi</t>
+          <t>Deepak Mehta</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6757,30 +6757,30 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G198" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2992</v>
+        <v>2970</v>
       </c>
       <c r="B199" t="n">
-        <v>1246.285</v>
+        <v>1258.166</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Subbamma Jasti</t>
+          <t>Alakh Pandey</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Edtech</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6789,30 +6789,30 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>3000</v>
+        <v>2970</v>
       </c>
       <c r="B200" t="n">
-        <v>1237.687</v>
+        <v>1258.166</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ashwin Desai</t>
+          <t>Prateek Boob</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Specialty chemicals</t>
+          <t>Edtech</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6821,30 +6821,30 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3025</v>
+        <v>2977</v>
       </c>
       <c r="B201" t="n">
-        <v>1226.325</v>
+        <v>1254.073</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ramesh Kunhikannan</t>
+          <t>Subbamma Jasti</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronics </t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6853,30 +6853,30 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G201" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3031</v>
+        <v>3014</v>
       </c>
       <c r="B202" t="n">
-        <v>1222.617</v>
+        <v>1227.408</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Alakh Pandey</t>
+          <t>Ramesh Kunhikannan</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t xml:space="preserve">Electronics </t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6885,30 +6885,30 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="B203" t="n">
-        <v>1222.617</v>
+        <v>1223.357</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prateek Boob</t>
+          <t>Ashwin Desai</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Specialty chemicals</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6917,30 +6917,30 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3039</v>
+        <v>3083</v>
       </c>
       <c r="B204" t="n">
-        <v>1219.798</v>
+        <v>1190.672</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Deepak Mehta</t>
+          <t>Krishna Kumar Bangur</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Graphite electrodes</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6949,30 +6949,30 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G204" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3056</v>
+        <v>3109</v>
       </c>
       <c r="B205" t="n">
-        <v>1207.273</v>
+        <v>1169.28</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Krishna Kumar Bangur</t>
+          <t>Mustafa Hamied</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Graphite electrodes</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6981,30 +6981,30 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G205" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3108</v>
+        <v>3137</v>
       </c>
       <c r="B206" t="n">
-        <v>1172.514</v>
+        <v>1156.812</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Mustafa Hamied</t>
+          <t>Bhaskara Rao Bollineni</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G206" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,21 +7045,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3158</v>
+        <v>3166</v>
       </c>
       <c r="B208" t="n">
-        <v>1146.05</v>
+        <v>1140.225</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -7077,30 +7077,30 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G208" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3179</v>
+        <v>3167</v>
       </c>
       <c r="B209" t="n">
-        <v>1132.544</v>
+        <v>1139.619</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sachin Bansal</t>
+          <t>C.C. Paarthipan</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>pharmaceuticals</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7109,30 +7109,30 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G209" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3191</v>
+        <v>3179</v>
       </c>
       <c r="B210" t="n">
-        <v>1126.872</v>
+        <v>1132.544</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bhaskara Rao Bollineni</t>
+          <t>Sachin Bansal</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="B211" t="n">
-        <v>1122.12</v>
+        <v>1121.795</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -7173,30 +7173,30 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G211" t="n">
         <v>1.12</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3216</v>
+        <v>3221</v>
       </c>
       <c r="B212" t="n">
-        <v>1111.893</v>
+        <v>1109.24</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>C.C. Paarthipan</t>
+          <t>Paritosh Garg</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>pharmaceuticals</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7205,30 +7205,30 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3219</v>
+        <v>3229</v>
       </c>
       <c r="B213" t="n">
-        <v>1111.63</v>
+        <v>1105.389</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paritosh Garg</t>
+          <t>Amit Burman</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7237,30 +7237,30 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3234</v>
+        <v>3239</v>
       </c>
       <c r="B214" t="n">
-        <v>1102.434</v>
+        <v>1099.93</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Amit Burman</t>
+          <t>Vijay Shekhar Sharma</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>financial technology</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7269,30 +7269,30 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3251</v>
+        <v>3254</v>
       </c>
       <c r="B215" t="n">
-        <v>1093.128</v>
+        <v>1091.185</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Vijay Shekhar Sharma</t>
+          <t>Lalit Keshre</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>financial technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="B216" t="n">
         <v>1081.614</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
@@ -7365,30 +7365,30 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3292</v>
+        <v>3282</v>
       </c>
       <c r="B218" t="n">
-        <v>1070.911</v>
+        <v>1075.912</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Lalit Keshre</t>
+          <t>Sachin Agarwal</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metal castings</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7397,30 +7397,30 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G218" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="B219" t="n">
-        <v>1069.408</v>
+        <v>1069.33</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sachin Agarwal</t>
+          <t>Kamlesh Jain</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Metal castings</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3304</v>
+        <v>3313</v>
       </c>
       <c r="B220" t="n">
-        <v>1059.625</v>
+        <v>1050.013</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G220" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="221">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="222">
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3365</v>
+        <v>3384</v>
       </c>
       <c r="B223" t="n">
-        <v>1006.935</v>
+        <v>999.122</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G223" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="B224" t="n">
-        <v>984.373</v>
+        <v>991.968</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779156002254</v>
+        <v>1779172202280</v>
       </c>
       <c r="G224" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.31252608796</v>
+        <v>46161.50002638889</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -464,10 +464,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>90491.412</v>
+        <v>89618.795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -485,21 +485,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G2" t="n">
-        <v>90.48999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>81621.079</v>
+        <v>80996.633</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G3" t="n">
-        <v>81.62</v>
+        <v>81</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>37944.272</v>
+        <v>37759.864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -549,21 +549,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G4" t="n">
-        <v>37.94</v>
+        <v>37.76</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B5" t="n">
-        <v>29501.632</v>
+        <v>29791.243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,21 +581,21 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G5" t="n">
-        <v>29.5</v>
+        <v>29.79</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" t="n">
-        <v>26639.14</v>
+        <v>26605.574</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G6" t="n">
-        <v>26.64</v>
+        <v>26.61</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +627,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="n">
-        <v>26554.882</v>
+        <v>26358.147</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G7" t="n">
-        <v>26.55</v>
+        <v>26.36</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="8">
@@ -659,7 +659,7 @@
         <v>96</v>
       </c>
       <c r="B8" t="n">
-        <v>25899.021</v>
+        <v>25910.005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -677,21 +677,21 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G8" t="n">
-        <v>25.9</v>
+        <v>25.91</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" t="n">
-        <v>21497.481</v>
+        <v>21385.715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,21 +709,21 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G9" t="n">
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" t="n">
-        <v>16281.083</v>
+        <v>16255.917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -741,21 +741,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G10" t="n">
-        <v>16.28</v>
+        <v>16.26</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B11" t="n">
-        <v>14018.69</v>
+        <v>14052.528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,21 +773,21 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G11" t="n">
-        <v>14.02</v>
+        <v>14.05</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B12" t="n">
-        <v>12930.004</v>
+        <v>12799.192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G12" t="n">
-        <v>12.93</v>
+        <v>12.8</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B13" t="n">
-        <v>12598.725</v>
+        <v>12554.841</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -837,21 +837,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779172202278</v>
+        <v>1779186603044</v>
       </c>
       <c r="G13" t="n">
-        <v>12.6</v>
+        <v>12.55</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.66670189815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B14" t="n">
-        <v>11606.473</v>
+        <v>11523.354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -869,21 +869,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G14" t="n">
-        <v>11.61</v>
+        <v>11.52</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B15" t="n">
-        <v>10362.024</v>
+        <v>10337.976</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G15" t="n">
-        <v>10.36</v>
+        <v>10.34</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B16" t="n">
-        <v>10233.441</v>
+        <v>10253.654</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G16" t="n">
-        <v>10.23</v>
+        <v>10.25</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="17">
@@ -947,7 +947,7 @@
         <v>376</v>
       </c>
       <c r="B17" t="n">
-        <v>9173.076999999999</v>
+        <v>9194.939</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G17" t="n">
-        <v>9.17</v>
+        <v>9.19</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B18" t="n">
-        <v>9149.982</v>
+        <v>9171.843000000001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G18" t="n">
-        <v>9.15</v>
+        <v>9.17</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B19" t="n">
-        <v>8532.804</v>
+        <v>8610.450000000001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G19" t="n">
-        <v>8.529999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B20" t="n">
-        <v>8287.675999999999</v>
+        <v>8275.162</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G20" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="21">
@@ -1075,7 +1075,7 @@
         <v>461</v>
       </c>
       <c r="B21" t="n">
-        <v>7942.155</v>
+        <v>7925.958</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G21" t="n">
-        <v>7.94</v>
+        <v>7.93</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B22" t="n">
-        <v>7780.081</v>
+        <v>7748.682</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G22" t="n">
-        <v>7.78</v>
+        <v>7.75</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B23" t="n">
-        <v>7779.941</v>
+        <v>7748.543</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G23" t="n">
-        <v>7.78</v>
+        <v>7.75</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="24">
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B25" t="n">
-        <v>7391.473</v>
+        <v>7320.275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G25" t="n">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B26" t="n">
-        <v>6388.016</v>
+        <v>6378.025</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G26" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="B27" t="n">
-        <v>6154.172</v>
+        <v>6097.057</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1285,21 +1285,21 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G27" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B28" t="n">
-        <v>5901.348</v>
+        <v>5883.814</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1317,18 +1317,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B30" t="n">
-        <v>5467.894</v>
+        <v>5476.526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="B31" t="n">
-        <v>5320.329</v>
+        <v>5268.225</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G31" t="n">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B32" t="n">
-        <v>5208.666</v>
+        <v>5186.245</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779172202278</v>
+        <v>1779186302266</v>
       </c>
       <c r="G32" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.50002636574</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B33" t="n">
-        <v>5184.622</v>
+        <v>5166.264</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G33" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B34" t="n">
-        <v>5184.622</v>
+        <v>5166.264</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1509,18 +1509,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G34" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B35" t="n">
         <v>5071.275</v>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G35" t="n">
         <v>5.07</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B36" t="n">
-        <v>5056.082</v>
+        <v>5053.227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G36" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B37" t="n">
-        <v>5056.077</v>
+        <v>5053.221</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1605,30 +1605,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G37" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B38" t="n">
-        <v>5055.761</v>
+        <v>5047.042</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kailashchandra Nuwal</t>
+          <t>Chandru Raheja</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Industrial explosives</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1637,30 +1637,30 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G38" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B39" t="n">
-        <v>5010.079</v>
+        <v>5007.063</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chandru Raheja</t>
+          <t>Kailashchandra Nuwal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Industrial explosives</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G39" t="n">
         <v>5.01</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B40" t="n">
         <v>4961.495</v>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G40" t="n">
         <v>4.96</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="B41" t="n">
-        <v>4875.158</v>
+        <v>4944.127</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G41" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="42">
@@ -1765,30 +1765,30 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G42" t="n">
         <v>4.7</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B43" t="n">
-        <v>4645.435</v>
+        <v>4659.006</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baba Kalyani</t>
+          <t>Vikas Oberoi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1797,30 +1797,30 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G43" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B44" t="n">
-        <v>4640.022</v>
+        <v>4602.24</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vikas Oberoi</t>
+          <t>Baba Kalyani</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1829,30 +1829,30 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G44" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B45" t="n">
-        <v>4398.875</v>
+        <v>4394.112</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mahendra Choksi &amp; family</t>
+          <t>Abhay Firodia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paints</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1861,30 +1861,30 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G45" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B46" t="n">
-        <v>4394.112</v>
+        <v>4351.719</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Abhay Firodia</t>
+          <t>Mahendra Choksi &amp; family</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Paints</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G46" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B47" t="n">
-        <v>4304.651</v>
+        <v>4289.109</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="48">
@@ -1939,7 +1939,7 @@
         <v>993</v>
       </c>
       <c r="B48" t="n">
-        <v>4286.893</v>
+        <v>4287.111</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G48" t="n">
         <v>4.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="B49" t="n">
-        <v>4088.995</v>
+        <v>4080.498</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G49" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="50">
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B51" t="n">
-        <v>3976.858</v>
+        <v>3954.628</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G51" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="B52" t="n">
-        <v>3893.492</v>
+        <v>3871.262</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G52" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B53" t="n">
-        <v>3765.59</v>
+        <v>3778.096</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2117,30 +2117,30 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G53" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B54" t="n">
-        <v>3746.775</v>
+        <v>3744.192</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shekhar Bajaj</t>
+          <t>Nirmal Minda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Auto parts</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2149,25 +2149,25 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G54" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B55" t="n">
-        <v>3746.739</v>
+        <v>3733.492</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kumud Bajaj</t>
+          <t>Shekhar Bajaj</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2181,25 +2181,25 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G55" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="B56" t="n">
-        <v>3746.739</v>
+        <v>3733.456</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Niraj Bajaj</t>
+          <t>Kumud Bajaj</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2213,30 +2213,30 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G56" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1162</v>
+        <v>1145</v>
       </c>
       <c r="B57" t="n">
-        <v>3704.765</v>
+        <v>3733.456</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw</t>
+          <t>Niraj Bajaj</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Biopharmaceuticals</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2245,30 +2245,30 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G57" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B58" t="n">
-        <v>3701.015</v>
+        <v>3687.63</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nirmal Minda</t>
+          <t>Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Auto parts</t>
+          <t>Biopharmaceuticals</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G58" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1184</v>
+        <v>1195</v>
       </c>
       <c r="B59" t="n">
-        <v>3623.491</v>
+        <v>3596.955</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G59" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="B60" t="n">
-        <v>3564.214</v>
+        <v>3533.587</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G60" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="B61" t="n">
-        <v>3534.259</v>
+        <v>3519.081</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G61" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="B62" t="n">
-        <v>3528.552</v>
+        <v>3513.769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2405,30 +2405,30 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G62" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1219</v>
+        <v>1228</v>
       </c>
       <c r="B63" t="n">
-        <v>3519.085</v>
+        <v>3496.098</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>G. M. Rao</t>
+          <t>Vinod Rai Gupta</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Electrical equipment</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2437,30 +2437,30 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G63" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="B64" t="n">
-        <v>3517.475</v>
+        <v>3493.7</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vinod Rai Gupta</t>
+          <t>G. M. Rao</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Electrical equipment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2469,21 +2469,21 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G64" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="B65" t="n">
-        <v>3475.298</v>
+        <v>3459.744</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="B66" t="n">
-        <v>3424.632</v>
+        <v>3454.187</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G66" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B67" t="n">
-        <v>3414.959</v>
+        <v>3419.689</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G67" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B68" t="n">
-        <v>3361.025</v>
+        <v>3372.476</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G68" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B70" t="n">
         <v>3221.232</v>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G70" t="n">
         <v>3.22</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1332</v>
+        <v>1319</v>
       </c>
       <c r="B71" t="n">
-        <v>3188.805</v>
+        <v>3220.04</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2693,21 +2693,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G71" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1342</v>
+        <v>1359</v>
       </c>
       <c r="B72" t="n">
-        <v>3176.501</v>
+        <v>3148.373</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G72" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="73">
@@ -2757,30 +2757,30 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G73" t="n">
         <v>3.11</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="B74" t="n">
-        <v>3101.264</v>
+        <v>3085.258</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Madhukar Parekh</t>
+          <t>Nikhil Kamath</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Adhesives</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2789,30 +2789,30 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G74" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B75" t="n">
-        <v>3085.258</v>
+        <v>3080.661</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nikhil Kamath</t>
+          <t>Madhukar Parekh</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Adhesives</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2821,30 +2821,30 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G75" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="B76" t="n">
-        <v>3079.961</v>
+        <v>3063.21</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Surender Saluja</t>
+          <t>Arvind Tiku</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Solar energy</t>
+          <t>Renewable energy, real estate</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2853,30 +2853,30 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G76" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1388</v>
+        <v>1397</v>
       </c>
       <c r="B77" t="n">
-        <v>3063.21</v>
+        <v>3034.539</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arvind Tiku</t>
+          <t>Surender Saluja</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Renewable energy, real estate</t>
+          <t>Solar energy</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2885,30 +2885,30 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G77" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="B78" t="n">
-        <v>3060.146</v>
+        <v>3027.962</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ramesh Juneja</t>
+          <t>Rajan Raheja &amp; family</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2917,30 +2917,30 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G78" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1400</v>
+        <v>1407</v>
       </c>
       <c r="B79" t="n">
-        <v>3033.557</v>
+        <v>3011.155</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rajan Raheja &amp; family</t>
+          <t>Mahima Datla</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Vaccines</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2949,30 +2949,30 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G79" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="B80" t="n">
-        <v>3011.155</v>
+        <v>3001.181</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mahima Datla</t>
+          <t>Ramesh Juneja</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Vaccines</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2981,30 +2981,30 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="B81" t="n">
-        <v>3008.474</v>
+        <v>2991.225</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rajeev Juneja</t>
+          <t>Leena Tewari</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Phamaceuticals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3013,30 +3013,30 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G81" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="B82" t="n">
-        <v>2991.225</v>
+        <v>2951.221</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Leena Tewari</t>
+          <t>Rajeev Juneja</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Phamaceuticals</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G82" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B83" t="n">
-        <v>2939.516</v>
+        <v>2938.114</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G83" t="n">
         <v>2.94</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="B84" t="n">
-        <v>2904.772</v>
+        <v>2916.539</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B85" t="n">
         <v>2895</v>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G85" t="n">
         <v>2.9</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B86" t="n">
-        <v>2810.689</v>
+        <v>2812.482</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G86" t="n">
         <v>2.81</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1539</v>
+        <v>1544</v>
       </c>
       <c r="B88" t="n">
-        <v>2744.674</v>
+        <v>2737.369</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G88" t="n">
         <v>2.74</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B89" t="n">
         <v>2717.279</v>
@@ -3269,18 +3269,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G89" t="n">
         <v>2.72</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="B90" t="n">
         <v>2707.811</v>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G90" t="n">
         <v>2.71</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="B91" t="n">
-        <v>2693.898</v>
+        <v>2670.444</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G91" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="B92" t="n">
-        <v>2693.898</v>
+        <v>2670.444</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G92" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="B93" t="n">
-        <v>2654.904</v>
+        <v>2642.764</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G93" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="B94" t="n">
-        <v>2612.233</v>
+        <v>2631.796</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G94" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="B95" t="n">
-        <v>2612.233</v>
+        <v>2631.796</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G95" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="B96" t="n">
-        <v>2612.233</v>
+        <v>2631.796</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G96" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="B97" t="n">
-        <v>2612.233</v>
+        <v>2631.796</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779172202279</v>
+        <v>1779186302266</v>
       </c>
       <c r="G97" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.6632206713</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1604</v>
+        <v>1622</v>
       </c>
       <c r="B98" t="n">
-        <v>2611.855</v>
+        <v>2584.62</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3557,30 +3557,30 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G98" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B99" t="n">
-        <v>2576.349</v>
+        <v>2573.626</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Inder Jaisinghani</t>
+          <t>Devi Shetty</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3589,30 +3589,30 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G99" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="B100" t="n">
-        <v>2565.002</v>
+        <v>2554.137</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Devi Shetty</t>
+          <t>Inder Jaisinghani</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G100" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1650</v>
+        <v>1646</v>
       </c>
       <c r="B101" t="n">
-        <v>2542.867</v>
+        <v>2551.19</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G101" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1651</v>
+        <v>1663</v>
       </c>
       <c r="B102" t="n">
-        <v>2539.459</v>
+        <v>2510.119</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3685,30 +3685,30 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G102" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1656</v>
+        <v>1679</v>
       </c>
       <c r="B103" t="n">
-        <v>2523.931</v>
+        <v>2488.836</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Anand Deshpande</t>
+          <t>Yusuf Hamied</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3717,30 +3717,30 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G103" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1665</v>
+        <v>1687</v>
       </c>
       <c r="B104" t="n">
-        <v>2502.637</v>
+        <v>2468.407</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Yusuf Hamied</t>
+          <t>Ramesh Jaisinghani</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cables and wires</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3749,30 +3749,30 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G104" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1680</v>
+        <v>1688</v>
       </c>
       <c r="B105" t="n">
-        <v>2489.52</v>
+        <v>2468</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ramesh Jaisinghani</t>
+          <t>Anand Deshpande</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cables and wires</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G105" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1684</v>
+        <v>1698</v>
       </c>
       <c r="B106" t="n">
-        <v>2481.23</v>
+        <v>2460.42</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G106" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1706</v>
+        <v>1729</v>
       </c>
       <c r="B107" t="n">
-        <v>2449.678</v>
+        <v>2427.167</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3845,21 +3845,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G107" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="B108" t="n">
-        <v>2429.582</v>
+        <v>2423.126</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -3877,30 +3877,30 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G108" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1756</v>
+        <v>1783</v>
       </c>
       <c r="B109" t="n">
-        <v>2381.939</v>
+        <v>2349.219</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Prem Kumar Arora</t>
+          <t>Salil Singhal</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Agrochemicals</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3909,30 +3909,30 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G109" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1765</v>
+        <v>1789</v>
       </c>
       <c r="B110" t="n">
-        <v>2378.801</v>
+        <v>2336.471</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Salil Singhal</t>
+          <t>Prem Kumar Arora</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Agrochemicals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G110" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B111" t="n">
-        <v>2292.243</v>
+        <v>2290.906</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G111" t="n">
         <v>2.29</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="B112" t="n">
-        <v>2278.094</v>
+        <v>2287.563</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G112" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="113">
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G113" t="n">
         <v>2.27</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="114">
@@ -4051,16 +4051,16 @@
         <v>1859</v>
       </c>
       <c r="B114" t="n">
-        <v>2253.546</v>
+        <v>2251.381</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sandeep Engineer</t>
+          <t>Kalanithi Maran</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Plastic pipes</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G114" t="n">
         <v>2.25</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="115">
@@ -4101,30 +4101,30 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G115" t="n">
         <v>2.25</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1862</v>
+        <v>1879</v>
       </c>
       <c r="B116" t="n">
-        <v>2249.071</v>
+        <v>2223.968</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kalanithi Maran</t>
+          <t>Sandeep Engineer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Plastic pipes</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4133,21 +4133,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G116" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1870</v>
+        <v>1895</v>
       </c>
       <c r="B117" t="n">
-        <v>2241.451</v>
+        <v>2201.48</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4165,30 +4165,30 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G117" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B118" t="n">
-        <v>2191.007</v>
+        <v>2189.241</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Vivek Chand Burman</t>
+          <t>Jupally Rameshwar Rao</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4197,30 +4197,30 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G118" t="n">
         <v>2.19</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1912</v>
+        <v>1920</v>
       </c>
       <c r="B119" t="n">
-        <v>2189.241</v>
+        <v>2174.099</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jupally Rameshwar Rao</t>
+          <t>Vivek Chand Burman</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G119" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1929</v>
+        <v>1943</v>
       </c>
       <c r="B120" t="n">
-        <v>2169.892</v>
+        <v>2156.795</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G120" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="B121" t="n">
         <v>2154.507</v>
@@ -4293,30 +4293,30 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G121" t="n">
         <v>2.15</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="B122" t="n">
-        <v>2133.961</v>
+        <v>2113.28</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sanjeev Bikhchandani</t>
+          <t>Ajay Parekh</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Adhesives</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4325,30 +4325,30 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G122" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1968</v>
+        <v>1972</v>
       </c>
       <c r="B123" t="n">
-        <v>2126.555</v>
+        <v>2110.419</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ajay Parekh</t>
+          <t>Sanjeev Bikhchandani</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Adhesives</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4357,21 +4357,21 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G123" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="B124" t="n">
-        <v>2121.361</v>
+        <v>2108.878</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G124" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="125">
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="126">
@@ -4453,30 +4453,30 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G126" t="n">
         <v>2.1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="B127" t="n">
-        <v>2073.764</v>
+        <v>2065.441</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Girdhari Jaisinghani</t>
+          <t>K. Dinesh</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>Software services</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4485,30 +4485,30 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G127" t="n">
         <v>2.07</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="B128" t="n">
-        <v>2064.139</v>
+        <v>2058.928</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lalit Khaitan</t>
+          <t>Jitendra Virwani</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4517,30 +4517,30 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G128" t="n">
         <v>2.06</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="B129" t="n">
-        <v>2062.573</v>
+        <v>2056.389</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jitendra Virwani</t>
+          <t>Girdhari Jaisinghani</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4549,30 +4549,30 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G129" t="n">
         <v>2.06</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2020</v>
+        <v>2059</v>
       </c>
       <c r="B130" t="n">
-        <v>2058.287</v>
+        <v>2024.789</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>K. Dinesh</t>
+          <t>Lalit Khaitan</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Software services</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4581,30 +4581,30 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G130" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2058</v>
+        <v>2067</v>
       </c>
       <c r="B131" t="n">
-        <v>2025.386</v>
+        <v>2017.058</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T.S. Kalyanaraman</t>
+          <t>Radha Vembu</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Jewelry</t>
+          <t>Business software</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4613,30 +4613,30 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G131" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="B132" t="n">
-        <v>2017.058</v>
+        <v>2012.966</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Radha Vembu</t>
+          <t>T.S. Kalyanaraman</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Business software</t>
+          <t>Jewelry</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4645,18 +4645,18 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G132" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="B133" t="n">
         <v>1971.957</v>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G133" t="n">
         <v>1.97</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B134" t="n">
-        <v>1955.751</v>
+        <v>1956.171</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -4709,18 +4709,18 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G134" t="n">
         <v>1.96</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B135" t="n">
         <v>1950.98</v>
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G135" t="n">
         <v>1.95</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B136" t="n">
         <v>1943.862</v>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G136" t="n">
         <v>1.94</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2182</v>
+        <v>2189</v>
       </c>
       <c r="B137" t="n">
-        <v>1908.24</v>
+        <v>1906.339</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G137" t="n">
         <v>1.91</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="138">
@@ -4819,16 +4819,16 @@
         <v>2222</v>
       </c>
       <c r="B138" t="n">
-        <v>1871.373</v>
+        <v>1872.728</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>P.P. Reddy</t>
+          <t>Satish Mehta</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4837,30 +4837,30 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2232</v>
+        <v>2227</v>
       </c>
       <c r="B139" t="n">
-        <v>1861.504</v>
+        <v>1871.373</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Satish Mehta</t>
+          <t>P.P. Reddy</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4869,18 +4869,18 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G139" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="B140" t="n">
         <v>1853.32</v>
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G140" t="n">
         <v>1.85</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2247</v>
+        <v>2262</v>
       </c>
       <c r="B141" t="n">
-        <v>1848.844</v>
+        <v>1837.674</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -4933,30 +4933,30 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G141" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2264</v>
+        <v>2278</v>
       </c>
       <c r="B142" t="n">
-        <v>1826.941</v>
+        <v>1813.92</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Anil Gupta</t>
+          <t>Girdhari Lal Bawri</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cables</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4965,30 +4965,30 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G142" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="B143" t="n">
-        <v>1813.92</v>
+        <v>1805.935</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Girdhari Lal Bawri</t>
+          <t>Anil Gupta</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cables</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G143" t="n">
         <v>1.81</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="B144" t="n">
-        <v>1788.292</v>
+        <v>1790.258</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5029,30 +5029,30 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G144" t="n">
         <v>1.79</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2320</v>
+        <v>2305</v>
       </c>
       <c r="B145" t="n">
-        <v>1767.773</v>
+        <v>1788.339</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pawan Munjal</t>
+          <t>Dhruv Sawhney</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Engineering, sugar</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5061,30 +5061,30 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G145" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2331</v>
+        <v>2325</v>
       </c>
       <c r="B146" t="n">
-        <v>1760.675</v>
+        <v>1767.873</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Banwari Lal Bawri</t>
+          <t>Pawan Munjal</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5093,30 +5093,30 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G146" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2388</v>
+        <v>2333</v>
       </c>
       <c r="B147" t="n">
-        <v>1716.6</v>
+        <v>1760.675</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Madhusudan Agarwal</t>
+          <t>Banwari Lal Bawri</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Indian sweets and snacks</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G147" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="B148" t="n">
-        <v>1712.104</v>
+        <v>1718.608</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -5157,30 +5157,30 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G148" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="B149" t="n">
-        <v>1708.887</v>
+        <v>1716.6</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Shyam Bhartia</t>
+          <t>Madhusudan Agarwal</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, food</t>
+          <t>Indian sweets and snacks</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5189,30 +5189,30 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G149" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2396</v>
+        <v>2404</v>
       </c>
       <c r="B150" t="n">
-        <v>1704.524</v>
+        <v>1699.486</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hari Bhartia</t>
+          <t>Shyam Bhartia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Pharmaceuticals, food</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G150" t="n">
         <v>1.7</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="B151" t="n">
-        <v>1695.593</v>
+        <v>1695.688</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -5253,30 +5253,30 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G151" t="n">
         <v>1.7</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="B152" t="n">
-        <v>1693.42</v>
+        <v>1695.255</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Motilal Oswal</t>
+          <t>Hari Bhartia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G152" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="153">
@@ -5299,16 +5299,16 @@
         <v>2414</v>
       </c>
       <c r="B153" t="n">
-        <v>1693.328</v>
+        <v>1693.784</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Viren Doshi</t>
+          <t>Motilal Oswal</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Financial services</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G153" t="n">
         <v>1.69</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="B154" t="n">
-        <v>1688.779</v>
+        <v>1688.873</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G154" t="n">
         <v>1.69</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B155" t="n">
-        <v>1680.313</v>
+        <v>1685.88</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -5381,30 +5381,30 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G155" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="B156" t="n">
-        <v>1674.233</v>
+        <v>1671.091</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dhruv Sawhney</t>
+          <t>Viren Doshi</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Engineering, sugar</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5413,30 +5413,30 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G156" t="n">
         <v>1.67</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2442</v>
+        <v>2452</v>
       </c>
       <c r="B157" t="n">
-        <v>1665.522</v>
+        <v>1655.092</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Anand Burman</t>
+          <t>Surjit Kumar Gupta</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Electrical equipment</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5445,30 +5445,30 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G157" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2443</v>
+        <v>2458</v>
       </c>
       <c r="B158" t="n">
-        <v>1665.153</v>
+        <v>1649.634</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Surjit Kumar Gupta</t>
+          <t>Anand Burman</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Electrical equipment</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G158" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="B159" t="n">
-        <v>1645.717</v>
+        <v>1643.084</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G159" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="160">
@@ -5523,7 +5523,7 @@
         <v>2466</v>
       </c>
       <c r="B160" t="n">
-        <v>1639.031</v>
+        <v>1641.211</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G160" t="n">
         <v>1.64</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B161" t="n">
-        <v>1597.238</v>
+        <v>1602.181</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -5573,21 +5573,21 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="B162" t="n">
-        <v>1593.089</v>
+        <v>1592.229</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G162" t="n">
         <v>1.59</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2553</v>
+        <v>2529</v>
       </c>
       <c r="B163" t="n">
-        <v>1563.836</v>
+        <v>1577.405</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G163" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2568</v>
+        <v>2558</v>
       </c>
       <c r="B164" t="n">
-        <v>1553.985</v>
+        <v>1561.647</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -5669,30 +5669,30 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G164" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2574</v>
+        <v>2567</v>
       </c>
       <c r="B165" t="n">
-        <v>1550.093</v>
+        <v>1557.424</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sanjay Agarwal</t>
+          <t>Satish Reddy</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5701,30 +5701,30 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G165" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2577</v>
+        <v>2583</v>
       </c>
       <c r="B166" t="n">
-        <v>1549.448</v>
+        <v>1545.866</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Satish Reddy</t>
+          <t>Ronnie Screwvala</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>edtech, entertainment</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5733,30 +5733,30 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G166" t="n">
         <v>1.55</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2585</v>
+        <v>2590</v>
       </c>
       <c r="B167" t="n">
-        <v>1543.514</v>
+        <v>1542.27</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ronnie Screwvala</t>
+          <t>Sanjay Agarwal</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>edtech, entertainment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5765,21 +5765,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G167" t="n">
         <v>1.54</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2612</v>
+        <v>2591</v>
       </c>
       <c r="B168" t="n">
-        <v>1521.801</v>
+        <v>1539.947</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="B169" t="n">
-        <v>1515.317</v>
+        <v>1518.805</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -5829,30 +5829,30 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G169" t="n">
         <v>1.52</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2629</v>
+        <v>2632</v>
       </c>
       <c r="B170" t="n">
-        <v>1500</v>
+        <v>1502.901</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Prasanna Sankar</t>
+          <t>Chaitanya Desai</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>Electric cables</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5861,30 +5861,30 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G170" t="n">
         <v>1.5</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2651</v>
+        <v>2632</v>
       </c>
       <c r="B171" t="n">
-        <v>1490.919</v>
+        <v>1502.901</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chaitanya Desai</t>
+          <t>Kushal Desai</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Electric cables</t>
+          <t>Electrical cables</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5893,30 +5893,30 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G171" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2651</v>
+        <v>2636</v>
       </c>
       <c r="B172" t="n">
-        <v>1490.919</v>
+        <v>1500</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kushal Desai</t>
+          <t>Prasanna Sankar</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Electrical cables</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G172" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="B173" t="n">
         <v>1485.365</v>
@@ -5957,30 +5957,30 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G173" t="n">
         <v>1.49</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="B174" t="n">
-        <v>1473.779</v>
+        <v>1475.369</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hitesh Doshi</t>
+          <t>Chirayu Amin</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Solar panels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5989,25 +5989,25 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G174" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2676</v>
+        <v>2693</v>
       </c>
       <c r="B175" t="n">
-        <v>1472.145</v>
+        <v>1454.362</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Pankaj Doshi</t>
+          <t>Hitesh Doshi</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6021,30 +6021,30 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G175" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2677</v>
+        <v>2694</v>
       </c>
       <c r="B176" t="n">
-        <v>1471.511</v>
+        <v>1452.764</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chirayu Amin</t>
+          <t>Pankaj Doshi</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Solar panels</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6053,30 +6053,30 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779172202279</v>
+        <v>1779186302267</v>
       </c>
       <c r="G176" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.50002637732</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="B177" t="n">
-        <v>1425.809</v>
+        <v>1420.559</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mofatraj Munot</t>
+          <t>Shrikant Badve</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>auto parts</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6085,30 +6085,30 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G177" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2731</v>
+        <v>2735</v>
       </c>
       <c r="B178" t="n">
-        <v>1420.221</v>
+        <v>1417.648</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Shrikant Badve</t>
+          <t>Mofatraj Munot</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>auto parts</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G178" t="n">
         <v>1.42</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="179">
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="180">
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2745</v>
+        <v>2748</v>
       </c>
       <c r="B181" t="n">
-        <v>1408.802</v>
+        <v>1407.706</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G181" t="n">
         <v>1.41</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2778</v>
+        <v>2790</v>
       </c>
       <c r="B182" t="n">
-        <v>1395.84</v>
+        <v>1381.927</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6245,30 +6245,30 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G182" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2781</v>
+        <v>2791</v>
       </c>
       <c r="B183" t="n">
-        <v>1390.731</v>
+        <v>1381.569</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kapil Bhatia</t>
+          <t>Aditya Khemka</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Aviation</t>
+          <t>Security solutions</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G183" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2786</v>
+        <v>2794</v>
       </c>
       <c r="B184" t="n">
-        <v>1387.281</v>
+        <v>1380.898</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -6309,30 +6309,30 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G184" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2788</v>
+        <v>2802</v>
       </c>
       <c r="B185" t="n">
-        <v>1384.891</v>
+        <v>1378.286</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Aditya Khemka</t>
+          <t>Kapil Bhatia</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Security solutions</t>
+          <t>Aviation</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G185" t="n">
         <v>1.38</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2817</v>
+        <v>2822</v>
       </c>
       <c r="B186" t="n">
         <v>1361.928</v>
@@ -6373,30 +6373,30 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2818</v>
+        <v>2835</v>
       </c>
       <c r="B187" t="n">
-        <v>1360.832</v>
+        <v>1350.105</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Deepinder Goyal</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Readymade garments</t>
+          <t>Food delivery service</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6405,30 +6405,30 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G187" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2834</v>
+        <v>2840</v>
       </c>
       <c r="B188" t="n">
-        <v>1349.816</v>
+        <v>1345.558</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Deepinder Goyal</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Food delivery service</t>
+          <t>Readymade garments</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G188" t="n">
         <v>1.35</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2839</v>
+        <v>2879</v>
       </c>
       <c r="B189" t="n">
-        <v>1344.394</v>
+        <v>1320.331</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -6469,30 +6469,30 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G189" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2882</v>
+        <v>2897</v>
       </c>
       <c r="B190" t="n">
-        <v>1316.645</v>
+        <v>1312.169</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Irfan Razack</t>
+          <t>Bina Chhabria</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Alcoholic beverages</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6501,25 +6501,25 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2883</v>
+        <v>2910</v>
       </c>
       <c r="B191" t="n">
-        <v>1316.631</v>
+        <v>1300.232</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Noaman Razack</t>
+          <t>Irfan Razack</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6533,25 +6533,25 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G191" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2883</v>
+        <v>2911</v>
       </c>
       <c r="B192" t="n">
-        <v>1316.631</v>
+        <v>1300.218</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Rezwan Razack</t>
+          <t>Noaman Razack</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6565,30 +6565,30 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G192" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2898</v>
+        <v>2911</v>
       </c>
       <c r="B193" t="n">
-        <v>1309.339</v>
+        <v>1300.218</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bina Chhabria</t>
+          <t>Rezwan Razack</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Alcoholic beverages</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6597,30 +6597,30 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G193" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2903</v>
+        <v>2922</v>
       </c>
       <c r="B194" t="n">
-        <v>1305.492</v>
+        <v>1297.945</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Aluru Jagadish Prasad</t>
+          <t>Bhikhabai Virani</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6629,30 +6629,30 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G194" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2917</v>
+        <v>2943</v>
       </c>
       <c r="B195" t="n">
-        <v>1297.945</v>
+        <v>1284.149</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bhikhabai Virani</t>
+          <t>Aluru Jagadish Prasad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6661,30 +6661,30 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G195" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2947</v>
+        <v>2961</v>
       </c>
       <c r="B196" t="n">
-        <v>1281.616</v>
+        <v>1271.581</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Kirit Doshi</t>
+          <t>Subbamma Jasti</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Solar modules</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G196" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2960</v>
+        <v>2963</v>
       </c>
       <c r="B197" t="n">
-        <v>1270.934</v>
+        <v>1267.103</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -6725,30 +6725,30 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G197" t="n">
         <v>1.27</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2961</v>
+        <v>2965</v>
       </c>
       <c r="B198" t="n">
-        <v>1267.152</v>
+        <v>1264.69</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Deepak Mehta</t>
+          <t>Kirit Doshi</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Solar modules</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6757,30 +6757,30 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G198" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2970</v>
+        <v>2972</v>
       </c>
       <c r="B199" t="n">
-        <v>1258.166</v>
+        <v>1258.844</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Alakh Pandey</t>
+          <t>Deepak Mehta</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6789,25 +6789,25 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G199" t="n">
         <v>1.26</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2970</v>
+        <v>2977</v>
       </c>
       <c r="B200" t="n">
-        <v>1258.166</v>
+        <v>1255.473</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prateek Boob</t>
+          <t>Alakh Pandey</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G200" t="n">
         <v>1.26</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="201">
@@ -6835,16 +6835,16 @@
         <v>2977</v>
       </c>
       <c r="B201" t="n">
-        <v>1254.073</v>
+        <v>1255.473</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Subbamma Jasti</t>
+          <t>Prateek Boob</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Edtech</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6853,21 +6853,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G201" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3014</v>
+        <v>3038</v>
       </c>
       <c r="B202" t="n">
-        <v>1227.408</v>
+        <v>1215.681</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G202" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3027</v>
+        <v>3039</v>
       </c>
       <c r="B203" t="n">
-        <v>1223.357</v>
+        <v>1215.597</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G203" t="n">
         <v>1.22</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3083</v>
+        <v>3085</v>
       </c>
       <c r="B204" t="n">
-        <v>1190.672</v>
+        <v>1190.277</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G204" t="n">
         <v>1.19</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3109</v>
+        <v>3121</v>
       </c>
       <c r="B205" t="n">
-        <v>1169.28</v>
+        <v>1165.724</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -6981,21 +6981,21 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G205" t="n">
         <v>1.17</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3137</v>
+        <v>3131</v>
       </c>
       <c r="B206" t="n">
-        <v>1156.812</v>
+        <v>1160.581</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G206" t="n">
         <v>1.16</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3143</v>
+        <v>3145</v>
       </c>
       <c r="B207" t="n">
         <v>1153.849</v>
@@ -7045,21 +7045,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="B208" t="n">
-        <v>1140.225</v>
+        <v>1142.722</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -7077,13 +7077,13 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G208" t="n">
         <v>1.14</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="209">
@@ -7091,7 +7091,7 @@
         <v>3167</v>
       </c>
       <c r="B209" t="n">
-        <v>1139.619</v>
+        <v>1140.038</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G209" t="n">
         <v>1.14</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="B210" t="n">
         <v>1132.544</v>
@@ -7141,30 +7141,30 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3198</v>
+        <v>3220</v>
       </c>
       <c r="B211" t="n">
-        <v>1121.795</v>
+        <v>1109.972</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kochouseph Chittilappilly</t>
+          <t>Paritosh Garg</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Electrical appliances</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G211" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="212">
@@ -7187,16 +7187,16 @@
         <v>3221</v>
       </c>
       <c r="B212" t="n">
-        <v>1109.24</v>
+        <v>1109.232</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Paritosh Garg</t>
+          <t>Vijay Shekhar Sharma</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>financial technology</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7205,30 +7205,30 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G212" t="n">
         <v>1.11</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3229</v>
+        <v>3223</v>
       </c>
       <c r="B213" t="n">
-        <v>1105.389</v>
+        <v>1108.893</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Amit Burman</t>
+          <t>Kochouseph Chittilappilly</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Electrical appliances</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7237,30 +7237,30 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G213" t="n">
         <v>1.11</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3239</v>
+        <v>3236</v>
       </c>
       <c r="B214" t="n">
-        <v>1099.93</v>
+        <v>1100.423</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Vijay Shekhar Sharma</t>
+          <t>Kamlesh Jain</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>financial technology</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7269,30 +7269,30 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3254</v>
+        <v>3251</v>
       </c>
       <c r="B215" t="n">
-        <v>1091.185</v>
+        <v>1094.662</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Lalit Keshre</t>
+          <t>Amit Burman</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7301,30 +7301,30 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3273</v>
+        <v>3266</v>
       </c>
       <c r="B216" t="n">
-        <v>1081.614</v>
+        <v>1086.292</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Chandubhai Virani</t>
+          <t>Lalit Keshre</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7333,25 +7333,25 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G216" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="B217" t="n">
         <v>1081.614</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Kanjibhai Virani</t>
+          <t>Chandubhai Virani</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -7365,30 +7365,30 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="B218" t="n">
-        <v>1075.912</v>
+        <v>1081.614</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sachin Agarwal</t>
+          <t>Kanjibhai Virani</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Metal castings</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7397,30 +7397,30 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G218" t="n">
         <v>1.08</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3296</v>
+        <v>3298</v>
       </c>
       <c r="B219" t="n">
-        <v>1069.33</v>
+        <v>1065.647</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Kamlesh Jain</t>
+          <t>Sachin Agarwal</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Recycling</t>
+          <t>Metal castings</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G219" t="n">
         <v>1.07</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3313</v>
+        <v>3327</v>
       </c>
       <c r="B220" t="n">
-        <v>1050.013</v>
+        <v>1036.496</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7461,18 +7461,18 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G220" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -7493,18 +7493,18 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3384</v>
+        <v>3386</v>
       </c>
       <c r="B223" t="n">
-        <v>999.122</v>
+        <v>999.617</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="B224" t="n">
-        <v>991.968</v>
+        <v>989.6900000000001</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1779172202280</v>
+        <v>1779186302267</v>
       </c>
       <c r="G224" t="n">
         <v>0.99</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46161.50002638889</v>
+        <v>46161.66322068287</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,10 +464,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
-        <v>89618.795</v>
+        <v>89252.531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G2" t="n">
-        <v>89.62</v>
+        <v>89.25</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>80996.633</v>
+        <v>80667.64999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>80.67</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>37759.864</v>
+        <v>37605.543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -549,21 +549,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G4" t="n">
-        <v>37.76</v>
+        <v>37.61</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>29791.243</v>
+        <v>29293.929</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G5" t="n">
-        <v>29.79</v>
+        <v>29.29</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         <v>92</v>
       </c>
       <c r="B6" t="n">
-        <v>26605.574</v>
+        <v>26257.331</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G6" t="n">
-        <v>26.61</v>
+        <v>26.26</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +627,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="n">
-        <v>26358.147</v>
+        <v>26250.423</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -645,21 +645,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G7" t="n">
-        <v>26.36</v>
+        <v>26.25</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" t="n">
-        <v>25910.005</v>
+        <v>25824.343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -677,21 +677,21 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G8" t="n">
-        <v>25.91</v>
+        <v>25.82</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B9" t="n">
-        <v>21385.715</v>
+        <v>21309.892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G9" t="n">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         <v>177</v>
       </c>
       <c r="B10" t="n">
-        <v>16255.917</v>
+        <v>16189.48</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -741,21 +741,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G10" t="n">
-        <v>16.26</v>
+        <v>16.19</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B11" t="n">
-        <v>14052.528</v>
+        <v>13982.76</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,21 +773,21 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G11" t="n">
-        <v>14.05</v>
+        <v>13.98</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B12" t="n">
-        <v>12799.192</v>
+        <v>12746.882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G12" t="n">
-        <v>12.8</v>
+        <v>12.75</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B13" t="n">
-        <v>12554.841</v>
+        <v>12503.122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -837,21 +837,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779186603044</v>
+        <v>1779198002270</v>
       </c>
       <c r="G13" t="n">
-        <v>12.55</v>
+        <v>12.5</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.66670189815</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B14" t="n">
-        <v>11523.354</v>
+        <v>11476.259</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -869,21 +869,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G14" t="n">
-        <v>11.52</v>
+        <v>11.48</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B15" t="n">
-        <v>10337.976</v>
+        <v>10295.725</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G15" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B16" t="n">
-        <v>10253.654</v>
+        <v>10211.748</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G16" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B17" t="n">
-        <v>9194.939</v>
+        <v>9149.147999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,21 +965,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G17" t="n">
-        <v>9.19</v>
+        <v>9.15</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B18" t="n">
-        <v>9171.843000000001</v>
+        <v>9126.147000000001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G18" t="n">
-        <v>9.17</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B19" t="n">
-        <v>8610.450000000001</v>
+        <v>8575.26</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G19" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B20" t="n">
-        <v>8275.162</v>
+        <v>8250.538</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G20" t="n">
-        <v>8.279999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B21" t="n">
-        <v>7925.958</v>
+        <v>7893.565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G21" t="n">
-        <v>7.93</v>
+        <v>7.89</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B22" t="n">
-        <v>7748.682</v>
+        <v>7717.014</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G22" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B23" t="n">
-        <v>7748.543</v>
+        <v>7716.876</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="24">
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B25" t="n">
-        <v>7320.275</v>
+        <v>7290.358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G25" t="n">
-        <v>7.32</v>
+        <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B26" t="n">
-        <v>6378.025</v>
+        <v>6351.959</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G26" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B27" t="n">
-        <v>6097.057</v>
+        <v>6073.892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1285,21 +1285,21 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G27" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B28" t="n">
-        <v>5883.814</v>
+        <v>5859.767</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1317,18 +1317,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G28" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779186302266</v>
+        <v>1779198002270</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863738426</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B30" t="n">
-        <v>5476.526</v>
+        <v>5469.746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G30" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B31" t="n">
-        <v>5268.225</v>
+        <v>5246.694</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G31" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="B32" t="n">
-        <v>5186.245</v>
+        <v>5165.05</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G32" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B33" t="n">
-        <v>5166.264</v>
+        <v>5145.149</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G33" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B34" t="n">
-        <v>5166.264</v>
+        <v>5145.149</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1509,30 +1509,30 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G34" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B35" t="n">
-        <v>5071.275</v>
+        <v>5032.575</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lachhman Das Mittal</t>
+          <t>Jamshyd Godrej</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tractors</t>
+          <t>Consumer goods, real estate</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1541,30 +1541,30 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G35" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B36" t="n">
-        <v>5053.227</v>
+        <v>5032.569</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jamshyd Godrej</t>
+          <t>Smita Crishna Godrej</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Consumer goods, real estate</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1573,30 +1573,30 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G36" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B37" t="n">
-        <v>5053.221</v>
+        <v>5026.415</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Smita Crishna Godrej</t>
+          <t>Chandru Raheja</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1605,30 +1605,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G37" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="B38" t="n">
-        <v>5047.042</v>
+        <v>4986.6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chandru Raheja</t>
+          <t>Kailashchandra Nuwal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Industrial explosives</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1637,30 +1637,30 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G38" t="n">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="B39" t="n">
-        <v>5007.063</v>
+        <v>4949.227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kailashchandra Nuwal</t>
+          <t>Lachhman Das Mittal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Industrial explosives</t>
+          <t>Tractors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G39" t="n">
-        <v>5.01</v>
+        <v>4.95</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B40" t="n">
-        <v>4961.495</v>
+        <v>4945.018</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G40" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B41" t="n">
-        <v>4944.127</v>
+        <v>4923.921</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G41" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="42">
@@ -1747,7 +1747,7 @@
         <v>909</v>
       </c>
       <c r="B42" t="n">
-        <v>4695.998</v>
+        <v>4676.806</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1765,21 +1765,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G42" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B43" t="n">
-        <v>4659.006</v>
+        <v>4639.965</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B44" t="n">
-        <v>4602.24</v>
+        <v>4583.431</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G44" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B45" t="n">
-        <v>4394.112</v>
+        <v>4376.154</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="B46" t="n">
-        <v>4351.719</v>
+        <v>4333.934</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G46" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B47" t="n">
-        <v>4289.109</v>
+        <v>4271.58</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G47" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="B48" t="n">
-        <v>4287.111</v>
+        <v>4257.587</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G48" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="B49" t="n">
-        <v>4080.498</v>
+        <v>4063.822</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G49" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="B51" t="n">
-        <v>3954.628</v>
+        <v>3938.466</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="B52" t="n">
-        <v>3871.262</v>
+        <v>3855.441</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G52" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B53" t="n">
-        <v>3778.096</v>
+        <v>3766.742</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G53" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B54" t="n">
-        <v>3744.192</v>
+        <v>3728.89</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G54" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="B55" t="n">
-        <v>3733.492</v>
+        <v>3718.234</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G55" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="B56" t="n">
-        <v>3733.456</v>
+        <v>3718.198</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G56" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="B57" t="n">
-        <v>3733.456</v>
+        <v>3718.198</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G57" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="B58" t="n">
-        <v>3687.63</v>
+        <v>3673.75</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G58" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="59">
@@ -2291,7 +2291,7 @@
         <v>1195</v>
       </c>
       <c r="B59" t="n">
-        <v>3596.955</v>
+        <v>3582.255</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G59" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="B60" t="n">
-        <v>3533.587</v>
+        <v>3520.169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G60" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B61" t="n">
-        <v>3519.081</v>
+        <v>3504.698</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G61" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="B62" t="n">
-        <v>3513.769</v>
+        <v>3499.409</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G62" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B63" t="n">
-        <v>3496.098</v>
+        <v>3481.809</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G63" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B64" t="n">
-        <v>3493.7</v>
+        <v>3480.546</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2469,21 +2469,21 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G64" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="B65" t="n">
-        <v>3459.744</v>
+        <v>3445.605</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B66" t="n">
-        <v>3454.187</v>
+        <v>3440.07</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G66" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="B67" t="n">
-        <v>3419.689</v>
+        <v>3405.713</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G67" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1274</v>
+        <v>1285</v>
       </c>
       <c r="B68" t="n">
-        <v>3372.476</v>
+        <v>3337.25</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G68" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="B70" t="n">
-        <v>3221.232</v>
+        <v>3208.067</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G70" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="B71" t="n">
-        <v>3220.04</v>
+        <v>3206.88</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2693,21 +2693,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G71" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B72" t="n">
-        <v>3148.373</v>
+        <v>3135.506</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G72" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="B73" t="n">
-        <v>3113.024</v>
+        <v>3100.307</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G73" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="B74" t="n">
-        <v>3085.258</v>
+        <v>3072.649</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G74" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="B75" t="n">
-        <v>3080.661</v>
+        <v>3068.071</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2821,18 +2821,18 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G75" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B77" t="n">
-        <v>3034.539</v>
+        <v>3022.137</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G77" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B78" t="n">
-        <v>3027.962</v>
+        <v>3015.587</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G78" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B79" t="n">
-        <v>3011.155</v>
+        <v>2998.849</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="B80" t="n">
-        <v>3001.181</v>
+        <v>2988.916</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B81" t="n">
-        <v>2991.225</v>
+        <v>2979</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G81" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="B82" t="n">
-        <v>2951.221</v>
+        <v>2939.16</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G82" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="B83" t="n">
-        <v>2938.114</v>
+        <v>2926.106</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G83" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="B84" t="n">
-        <v>2916.539</v>
+        <v>2904.619</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G84" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B85" t="n">
         <v>2895</v>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G85" t="n">
         <v>2.9</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B86" t="n">
-        <v>2812.482</v>
+        <v>2811.471</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G86" t="n">
         <v>2.81</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1544</v>
+        <v>1549</v>
       </c>
       <c r="B88" t="n">
-        <v>2737.369</v>
+        <v>2726.181</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G88" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="B89" t="n">
-        <v>2717.279</v>
+        <v>2706.174</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3269,21 +3269,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G89" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="B90" t="n">
-        <v>2707.811</v>
+        <v>2702.317</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G90" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B91" t="n">
-        <v>2670.444</v>
+        <v>2660.688</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G91" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B92" t="n">
-        <v>2670.444</v>
+        <v>2660.688</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G92" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="B93" t="n">
-        <v>2642.764</v>
+        <v>2631.963</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G93" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="B94" t="n">
-        <v>2631.796</v>
+        <v>2621.04</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G94" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="B95" t="n">
-        <v>2631.796</v>
+        <v>2621.04</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G95" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="B96" t="n">
-        <v>2631.796</v>
+        <v>2621.04</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G96" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="B97" t="n">
-        <v>2631.796</v>
+        <v>2621.04</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779186302266</v>
+        <v>1779198002271</v>
       </c>
       <c r="G97" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.6632206713</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1622</v>
+        <v>1628</v>
       </c>
       <c r="B98" t="n">
-        <v>2584.62</v>
+        <v>2575.208</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G98" t="n">
         <v>2.58</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1627</v>
+        <v>1634</v>
       </c>
       <c r="B99" t="n">
-        <v>2573.626</v>
+        <v>2563.107</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G99" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1640</v>
+        <v>1652</v>
       </c>
       <c r="B100" t="n">
-        <v>2554.137</v>
+        <v>2543.714</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="B101" t="n">
-        <v>2551.19</v>
+        <v>2540.764</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G101" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1663</v>
+        <v>1674</v>
       </c>
       <c r="B102" t="n">
-        <v>2510.119</v>
+        <v>2499.861</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G102" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1679</v>
+        <v>1684</v>
       </c>
       <c r="B103" t="n">
-        <v>2488.836</v>
+        <v>2478.664</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3717,21 +3717,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G103" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1687</v>
+        <v>1698</v>
       </c>
       <c r="B104" t="n">
-        <v>2468.407</v>
+        <v>2458.319</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G104" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1688</v>
+        <v>1699</v>
       </c>
       <c r="B105" t="n">
-        <v>2468</v>
+        <v>2457.914</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G105" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1698</v>
+        <v>1711</v>
       </c>
       <c r="B106" t="n">
-        <v>2460.42</v>
+        <v>2450.365</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="B107" t="n">
-        <v>2427.167</v>
+        <v>2417.248</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3845,21 +3845,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G107" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="B108" t="n">
-        <v>2423.126</v>
+        <v>2413.223</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G108" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="B109" t="n">
-        <v>2349.219</v>
+        <v>2339.618</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -3909,21 +3909,21 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G109" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="B110" t="n">
-        <v>2336.471</v>
+        <v>2326.922</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G110" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1823</v>
+        <v>1834</v>
       </c>
       <c r="B111" t="n">
-        <v>2290.906</v>
+        <v>2281.543</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G111" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="B112" t="n">
-        <v>2287.563</v>
+        <v>2278.214</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G112" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1849</v>
+        <v>1855</v>
       </c>
       <c r="B113" t="n">
-        <v>2271.057</v>
+        <v>2261.775</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G113" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1859</v>
+        <v>1867</v>
       </c>
       <c r="B114" t="n">
-        <v>2251.381</v>
+        <v>2241.256</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4069,21 +4069,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G114" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1860</v>
+        <v>1872</v>
       </c>
       <c r="B115" t="n">
-        <v>2250.673</v>
+        <v>2235.788</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G115" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1879</v>
+        <v>1890</v>
       </c>
       <c r="B116" t="n">
-        <v>2223.968</v>
+        <v>2214.878</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4133,21 +4133,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G116" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1895</v>
+        <v>1910</v>
       </c>
       <c r="B117" t="n">
-        <v>2201.48</v>
+        <v>2192.483</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4165,21 +4165,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G117" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="B118" t="n">
-        <v>2189.241</v>
+        <v>2180.293</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G118" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1920</v>
+        <v>1931</v>
       </c>
       <c r="B119" t="n">
-        <v>2174.099</v>
+        <v>2165.214</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -4229,30 +4229,30 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G119" t="n">
         <v>2.17</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B120" t="n">
-        <v>2156.795</v>
+        <v>2154.281</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Anurang Jain</t>
+          <t>Kabir Mulchandani</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Auto parts</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4261,30 +4261,30 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G120" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1945</v>
+        <v>1950</v>
       </c>
       <c r="B121" t="n">
-        <v>2154.507</v>
+        <v>2147.981</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kabir Mulchandani</t>
+          <t>Anurang Jain</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Auto parts</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G121" t="n">
         <v>2.15</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="B122" t="n">
-        <v>2113.28</v>
+        <v>2104.643</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4325,21 +4325,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G122" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1972</v>
+        <v>1985</v>
       </c>
       <c r="B123" t="n">
-        <v>2110.419</v>
+        <v>2101.794</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4357,21 +4357,21 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G123" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="B124" t="n">
-        <v>2108.878</v>
+        <v>2100.259</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -4389,30 +4389,30 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G124" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="B125" t="n">
-        <v>2100.998</v>
+        <v>2100</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kishore Jain</t>
+          <t>Aravind Srinivas</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Jewellery</t>
+          <t xml:space="preserve">Artificial intelligence </t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4421,30 +4421,30 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1986</v>
+        <v>2002</v>
       </c>
       <c r="B126" t="n">
-        <v>2100</v>
+        <v>2092.411</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Aravind Srinivas</t>
+          <t>Kishore Jain</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial intelligence </t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G126" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="B127" t="n">
-        <v>2065.441</v>
+        <v>2057</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -4485,30 +4485,30 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G127" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="B128" t="n">
-        <v>2058.928</v>
+        <v>2047.984</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jitendra Virwani</t>
+          <t>Girdhari Jaisinghani</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Cables &amp; wires</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4517,30 +4517,30 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G128" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2023</v>
+        <v>2069</v>
       </c>
       <c r="B129" t="n">
-        <v>2056.389</v>
+        <v>2016.514</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Girdhari Jaisinghani</t>
+          <t>Lalit Khaitan</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cables &amp; wires</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4549,30 +4549,30 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G129" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2059</v>
+        <v>2081</v>
       </c>
       <c r="B130" t="n">
-        <v>2024.789</v>
+        <v>2010.821</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lalit Khaitan</t>
+          <t>Jitendra Virwani</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G130" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2067</v>
+        <v>2084</v>
       </c>
       <c r="B131" t="n">
-        <v>2017.058</v>
+        <v>2008.814</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G131" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2069</v>
+        <v>2090</v>
       </c>
       <c r="B132" t="n">
-        <v>2012.966</v>
+        <v>2004.739</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G132" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2126</v>
+        <v>2133</v>
       </c>
       <c r="B133" t="n">
-        <v>1971.957</v>
+        <v>1963.898</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G133" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2136</v>
+        <v>2148</v>
       </c>
       <c r="B134" t="n">
-        <v>1956.171</v>
+        <v>1948.176</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -4709,21 +4709,21 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G134" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2145</v>
+        <v>2153</v>
       </c>
       <c r="B135" t="n">
-        <v>1950.98</v>
+        <v>1942.966</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -4741,21 +4741,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G135" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="B136" t="n">
-        <v>1943.862</v>
+        <v>1935.918</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G136" t="n">
         <v>1.94</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="B137" t="n">
-        <v>1906.339</v>
+        <v>1898.548</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4805,21 +4805,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G137" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2222</v>
+        <v>2234</v>
       </c>
       <c r="B138" t="n">
-        <v>1872.728</v>
+        <v>1865.074</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2227</v>
+        <v>2236</v>
       </c>
       <c r="B139" t="n">
-        <v>1871.373</v>
+        <v>1863.725</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -4869,30 +4869,30 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G139" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2245</v>
+        <v>2265</v>
       </c>
       <c r="B140" t="n">
-        <v>1853.32</v>
+        <v>1830.164</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Anju Agarwal</t>
+          <t>Mrudula Parekh</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Adhesives</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4901,30 +4901,30 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G140" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="B141" t="n">
-        <v>1837.674</v>
+        <v>1829.683</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mrudula Parekh</t>
+          <t>Anju Agarwal</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Adhesives</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G141" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2278</v>
+        <v>2285</v>
       </c>
       <c r="B142" t="n">
-        <v>1813.92</v>
+        <v>1806.507</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -4965,21 +4965,21 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2285</v>
+        <v>2299</v>
       </c>
       <c r="B143" t="n">
-        <v>1805.935</v>
+        <v>1798.554</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G143" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="B144" t="n">
-        <v>1790.258</v>
+        <v>1782.941</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5029,21 +5029,21 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G144" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="B145" t="n">
-        <v>1788.339</v>
+        <v>1781.03</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2325</v>
+        <v>2333</v>
       </c>
       <c r="B146" t="n">
-        <v>1767.873</v>
+        <v>1760.988</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G146" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="B147" t="n">
-        <v>1760.675</v>
+        <v>1753.479</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -5125,30 +5125,30 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G147" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2388</v>
+        <v>2392</v>
       </c>
       <c r="B148" t="n">
-        <v>1718.608</v>
+        <v>1716.6</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Arvind Lal</t>
+          <t>Madhusudan Agarwal</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Medical diagnostics</t>
+          <t>Indian sweets and snacks</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5157,30 +5157,30 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G148" t="n">
         <v>1.72</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2391</v>
+        <v>2398</v>
       </c>
       <c r="B149" t="n">
-        <v>1716.6</v>
+        <v>1711.584</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Madhusudan Agarwal</t>
+          <t>Arvind Lal</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Indian sweets and snacks</t>
+          <t>Medical diagnostics</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G149" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2404</v>
+        <v>2415</v>
       </c>
       <c r="B150" t="n">
-        <v>1699.486</v>
+        <v>1692.54</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2409</v>
+        <v>2418</v>
       </c>
       <c r="B151" t="n">
-        <v>1695.688</v>
+        <v>1689.098</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -5253,21 +5253,21 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G151" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2411</v>
+        <v>2419</v>
       </c>
       <c r="B152" t="n">
-        <v>1695.255</v>
+        <v>1688.326</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2414</v>
+        <v>2423</v>
       </c>
       <c r="B153" t="n">
-        <v>1693.784</v>
+        <v>1686.861</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -5317,30 +5317,30 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G153" t="n">
         <v>1.69</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2421</v>
+        <v>2425</v>
       </c>
       <c r="B154" t="n">
-        <v>1688.873</v>
+        <v>1686.397</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Renu Munjal</t>
+          <t>Aloke Lohia</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Petrochemicals</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5349,30 +5349,30 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G154" t="n">
         <v>1.69</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2424</v>
+        <v>2429</v>
       </c>
       <c r="B155" t="n">
-        <v>1685.88</v>
+        <v>1682.312</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Aloke Lohia</t>
+          <t>Renu Munjal</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Petrochemicals</t>
+          <t>Motorcycles</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5381,21 +5381,21 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G155" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2435</v>
+        <v>2447</v>
       </c>
       <c r="B156" t="n">
-        <v>1671.091</v>
+        <v>1664.261</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G156" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2452</v>
+        <v>2458</v>
       </c>
       <c r="B157" t="n">
-        <v>1655.092</v>
+        <v>1648.328</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G157" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2458</v>
+        <v>2463</v>
       </c>
       <c r="B158" t="n">
-        <v>1649.634</v>
+        <v>1642.892</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G158" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2462</v>
+        <v>2468</v>
       </c>
       <c r="B159" t="n">
-        <v>1643.084</v>
+        <v>1636.369</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G159" t="n">
         <v>1.64</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2466</v>
+        <v>2470</v>
       </c>
       <c r="B160" t="n">
-        <v>1641.211</v>
+        <v>1634.503</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G160" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="B161" t="n">
-        <v>1602.181</v>
+        <v>1598.308</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -5573,21 +5573,21 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2509</v>
+        <v>2516</v>
       </c>
       <c r="B162" t="n">
-        <v>1592.229</v>
+        <v>1585.722</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G162" t="n">
         <v>1.59</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2529</v>
+        <v>2547</v>
       </c>
       <c r="B163" t="n">
-        <v>1577.405</v>
+        <v>1570.959</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G163" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2558</v>
+        <v>2568</v>
       </c>
       <c r="B164" t="n">
-        <v>1561.647</v>
+        <v>1555.265</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G164" t="n">
         <v>1.56</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2567</v>
+        <v>2576</v>
       </c>
       <c r="B165" t="n">
-        <v>1557.424</v>
+        <v>1551.059</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G165" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="B166" t="n">
-        <v>1545.866</v>
+        <v>1544.473</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -5733,21 +5733,21 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G166" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2590</v>
+        <v>2597</v>
       </c>
       <c r="B167" t="n">
-        <v>1542.27</v>
+        <v>1535.967</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -5765,21 +5765,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G167" t="n">
         <v>1.54</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2591</v>
+        <v>2602</v>
       </c>
       <c r="B168" t="n">
-        <v>1539.947</v>
+        <v>1533.654</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G168" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2617</v>
+        <v>2608</v>
       </c>
       <c r="B169" t="n">
-        <v>1518.805</v>
+        <v>1527.065</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -5829,30 +5829,30 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779186302267</v>
+        <v>1779198002271</v>
       </c>
       <c r="G169" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863739583</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="B170" t="n">
-        <v>1502.901</v>
+        <v>1500</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chaitanya Desai</t>
+          <t>Prasanna Sankar</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Electric cables</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5861,30 +5861,30 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G170" t="n">
         <v>1.5</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2632</v>
+        <v>2645</v>
       </c>
       <c r="B171" t="n">
-        <v>1502.901</v>
+        <v>1496.758</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kushal Desai</t>
+          <t>Chaitanya Desai</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Electrical cables</t>
+          <t>Electric cables</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5893,30 +5893,30 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G171" t="n">
         <v>1.5</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2636</v>
+        <v>2645</v>
       </c>
       <c r="B172" t="n">
-        <v>1500</v>
+        <v>1496.758</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prasanna Sankar</t>
+          <t>Kushal Desai</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>Electrical cables</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G172" t="n">
         <v>1.5</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2662</v>
+        <v>2669</v>
       </c>
       <c r="B173" t="n">
-        <v>1485.365</v>
+        <v>1479.294</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G173" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2674</v>
+        <v>2677</v>
       </c>
       <c r="B174" t="n">
-        <v>1475.369</v>
+        <v>1469.34</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G174" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2693</v>
+        <v>2709</v>
       </c>
       <c r="B175" t="n">
-        <v>1454.362</v>
+        <v>1448.418</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -6021,21 +6021,21 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2694</v>
+        <v>2710</v>
       </c>
       <c r="B176" t="n">
-        <v>1452.764</v>
+        <v>1446.827</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -6053,21 +6053,21 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2729</v>
+        <v>2736</v>
       </c>
       <c r="B177" t="n">
-        <v>1420.559</v>
+        <v>1414.754</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -6085,21 +6085,21 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G177" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2735</v>
+        <v>2737</v>
       </c>
       <c r="B178" t="n">
-        <v>1417.648</v>
+        <v>1411.854</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -6117,30 +6117,30 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G178" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="B179" t="n">
-        <v>1414.525</v>
+        <v>1409.878</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Rajeev Gulati</t>
+          <t>Binny Bansal</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6149,30 +6149,30 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2741</v>
+        <v>2744</v>
       </c>
       <c r="B180" t="n">
-        <v>1409.921</v>
+        <v>1408.744</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Binny Bansal</t>
+          <t>Rajeev Gulati</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2748</v>
+        <v>2758</v>
       </c>
       <c r="B181" t="n">
-        <v>1407.706</v>
+        <v>1401.953</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G181" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2790</v>
+        <v>2802</v>
       </c>
       <c r="B182" t="n">
-        <v>1381.927</v>
+        <v>1376.279</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G182" t="n">
         <v>1.38</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2791</v>
+        <v>2803</v>
       </c>
       <c r="B183" t="n">
-        <v>1381.569</v>
+        <v>1375.923</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G183" t="n">
         <v>1.38</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2794</v>
+        <v>2805</v>
       </c>
       <c r="B184" t="n">
-        <v>1380.898</v>
+        <v>1375.254</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -6309,21 +6309,21 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G184" t="n">
         <v>1.38</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2802</v>
+        <v>2809</v>
       </c>
       <c r="B185" t="n">
-        <v>1378.286</v>
+        <v>1373.237</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G185" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2822</v>
+        <v>2827</v>
       </c>
       <c r="B186" t="n">
-        <v>1361.928</v>
+        <v>1356.362</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="B187" t="n">
-        <v>1350.105</v>
+        <v>1344.178</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -6405,21 +6405,21 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G187" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2840</v>
+        <v>2844</v>
       </c>
       <c r="B188" t="n">
-        <v>1345.558</v>
+        <v>1340.059</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2879</v>
+        <v>2889</v>
       </c>
       <c r="B189" t="n">
-        <v>1320.331</v>
+        <v>1314.935</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G189" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2897</v>
+        <v>2904</v>
       </c>
       <c r="B190" t="n">
-        <v>1312.169</v>
+        <v>1306.807</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -6501,21 +6501,21 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G190" t="n">
         <v>1.31</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2910</v>
+        <v>2924</v>
       </c>
       <c r="B191" t="n">
-        <v>1300.232</v>
+        <v>1294.918</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G191" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2911</v>
+        <v>2925</v>
       </c>
       <c r="B192" t="n">
-        <v>1300.218</v>
+        <v>1294.904</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -6565,21 +6565,21 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G192" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2911</v>
+        <v>2925</v>
       </c>
       <c r="B193" t="n">
-        <v>1300.218</v>
+        <v>1294.904</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -6597,21 +6597,21 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2922</v>
+        <v>2931</v>
       </c>
       <c r="B194" t="n">
-        <v>1297.945</v>
+        <v>1292.64</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G194" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2943</v>
+        <v>2951</v>
       </c>
       <c r="B195" t="n">
-        <v>1284.149</v>
+        <v>1278.9</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G195" t="n">
         <v>1.28</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2961</v>
+        <v>2964</v>
       </c>
       <c r="B196" t="n">
-        <v>1271.581</v>
+        <v>1266.384</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2963</v>
+        <v>2966</v>
       </c>
       <c r="B197" t="n">
-        <v>1267.103</v>
+        <v>1261.925</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G197" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2965</v>
+        <v>2971</v>
       </c>
       <c r="B198" t="n">
-        <v>1264.69</v>
+        <v>1259.521</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -6757,21 +6757,21 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2972</v>
+        <v>2979</v>
       </c>
       <c r="B199" t="n">
-        <v>1258.844</v>
+        <v>1253.699</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G199" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2977</v>
+        <v>2986</v>
       </c>
       <c r="B200" t="n">
-        <v>1255.473</v>
+        <v>1250.342</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G200" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2977</v>
+        <v>2986</v>
       </c>
       <c r="B201" t="n">
-        <v>1255.473</v>
+        <v>1250.342</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -6853,21 +6853,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G201" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3038</v>
+        <v>3047</v>
       </c>
       <c r="B202" t="n">
-        <v>1215.681</v>
+        <v>1210.713</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3039</v>
+        <v>3048</v>
       </c>
       <c r="B203" t="n">
-        <v>1215.597</v>
+        <v>1210.629</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -6917,21 +6917,21 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G203" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3085</v>
+        <v>3092</v>
       </c>
       <c r="B204" t="n">
-        <v>1190.277</v>
+        <v>1185.412</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G204" t="n">
         <v>1.19</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3121</v>
+        <v>3131</v>
       </c>
       <c r="B205" t="n">
-        <v>1165.724</v>
+        <v>1160.96</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -6981,21 +6981,21 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G205" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3131</v>
+        <v>3142</v>
       </c>
       <c r="B206" t="n">
-        <v>1160.581</v>
+        <v>1155.838</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -7013,21 +7013,21 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G206" t="n">
         <v>1.16</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3145</v>
+        <v>3152</v>
       </c>
       <c r="B207" t="n">
-        <v>1153.849</v>
+        <v>1149.133</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -7045,21 +7045,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3164</v>
+        <v>3172</v>
       </c>
       <c r="B208" t="n">
-        <v>1142.722</v>
+        <v>1138.052</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G208" t="n">
         <v>1.14</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3167</v>
+        <v>3178</v>
       </c>
       <c r="B209" t="n">
-        <v>1140.038</v>
+        <v>1135.379</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G209" t="n">
         <v>1.14</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3180</v>
+        <v>3190</v>
       </c>
       <c r="B210" t="n">
-        <v>1132.544</v>
+        <v>1127.916</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3220</v>
+        <v>3233</v>
       </c>
       <c r="B211" t="n">
-        <v>1109.972</v>
+        <v>1105.436</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -7173,21 +7173,21 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G211" t="n">
         <v>1.11</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3221</v>
+        <v>3234</v>
       </c>
       <c r="B212" t="n">
-        <v>1109.232</v>
+        <v>1104.74</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G212" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3223</v>
+        <v>3235</v>
       </c>
       <c r="B213" t="n">
-        <v>1108.893</v>
+        <v>1104.361</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G213" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3236</v>
+        <v>3255</v>
       </c>
       <c r="B214" t="n">
-        <v>1100.423</v>
+        <v>1095.926</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -7269,21 +7269,21 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3251</v>
+        <v>3267</v>
       </c>
       <c r="B215" t="n">
-        <v>1094.662</v>
+        <v>1090.188</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -7301,21 +7301,21 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3266</v>
+        <v>3275</v>
       </c>
       <c r="B216" t="n">
-        <v>1086.292</v>
+        <v>1081.852</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G216" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3274</v>
+        <v>3284</v>
       </c>
       <c r="B217" t="n">
-        <v>1081.614</v>
+        <v>1077.194</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -7365,21 +7365,21 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3274</v>
+        <v>3284</v>
       </c>
       <c r="B218" t="n">
-        <v>1081.614</v>
+        <v>1077.194</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G218" t="n">
         <v>1.08</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3298</v>
+        <v>3305</v>
       </c>
       <c r="B219" t="n">
-        <v>1065.647</v>
+        <v>1061.292</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G219" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3327</v>
+        <v>3335</v>
       </c>
       <c r="B220" t="n">
-        <v>1036.496</v>
+        <v>1032.26</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7461,18 +7461,18 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G220" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -7493,18 +7493,18 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3386</v>
+        <v>3388</v>
       </c>
       <c r="B223" t="n">
-        <v>999.617</v>
+        <v>996.251</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7557,45 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779186302267</v>
+        <v>1779198002272</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.66322068287</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>3390</v>
-      </c>
-      <c r="B224" t="n">
-        <v>989.6900000000001</v>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Rajinder Gupta</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Textiles, paper</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F224" t="n">
-        <v>1779186302267</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H224" s="1" t="n">
-        <v>46161.66322068287</v>
+        <v>46161.79863740741</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G2" t="n">
         <v>89.25</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="3">
@@ -517,18 +517,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G3" t="n">
         <v>80.67</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" t="n">
         <v>37605.543</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G4" t="n">
         <v>37.61</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>29293.929</v>
+        <v>28974.218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G5" t="n">
-        <v>29.29</v>
+        <v>28.97</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G6" t="n">
         <v>26.26</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="7">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G7" t="n">
         <v>26.25</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G8" t="n">
         <v>25.82</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="9">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G9" t="n">
         <v>21.31</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="10">
@@ -741,21 +741,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G10" t="n">
         <v>16.19</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B11" t="n">
-        <v>13982.76</v>
+        <v>13963.402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G11" t="n">
-        <v>13.98</v>
+        <v>13.96</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G12" t="n">
         <v>12.75</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="13">
@@ -837,18 +837,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G13" t="n">
         <v>12.5</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B14" t="n">
         <v>11476.259</v>
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G14" t="n">
         <v>11.48</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B15" t="n">
         <v>10295.725</v>
@@ -901,18 +901,18 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G15" t="n">
         <v>10.3</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B16" t="n">
         <v>10211.748</v>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G16" t="n">
         <v>10.21</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B17" t="n">
-        <v>9149.147999999999</v>
+        <v>9136.491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G17" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="18">
@@ -979,7 +979,7 @@
         <v>381</v>
       </c>
       <c r="B18" t="n">
-        <v>9126.147000000001</v>
+        <v>9113.49</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -997,18 +997,18 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G18" t="n">
-        <v>9.130000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B19" t="n">
         <v>8575.26</v>
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G19" t="n">
         <v>8.58</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B20" t="n">
         <v>8250.538</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G20" t="n">
         <v>8.25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="21">
@@ -1093,18 +1093,18 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G21" t="n">
         <v>7.89</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B22" t="n">
         <v>7717.014</v>
@@ -1125,18 +1125,18 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G22" t="n">
         <v>7.72</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B23" t="n">
         <v>7716.876</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G23" t="n">
         <v>7.72</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="24">
@@ -1189,18 +1189,18 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G24" t="n">
         <v>7.61</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B25" t="n">
         <v>7290.358</v>
@@ -1221,18 +1221,18 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G25" t="n">
         <v>7.29</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B26" t="n">
         <v>6351.959</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G26" t="n">
         <v>6.35</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="27">
@@ -1285,18 +1285,18 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G27" t="n">
         <v>6.07</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B28" t="n">
         <v>5859.767</v>
@@ -1317,18 +1317,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G28" t="n">
         <v>5.86</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1349,18 +1349,18 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1779198002270</v>
+        <v>1779208802311</v>
       </c>
       <c r="G29" t="n">
         <v>5.6</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46161.79863738426</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B30" t="n">
         <v>5469.746</v>
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G30" t="n">
         <v>5.47</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B31" t="n">
         <v>5246.694</v>
@@ -1413,18 +1413,18 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G31" t="n">
         <v>5.25</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B32" t="n">
         <v>5165.05</v>
@@ -1445,18 +1445,18 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G32" t="n">
         <v>5.17</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B33" t="n">
         <v>5145.149</v>
@@ -1477,18 +1477,18 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G33" t="n">
         <v>5.15</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B34" t="n">
         <v>5145.149</v>
@@ -1509,18 +1509,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G34" t="n">
         <v>5.15</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B35" t="n">
         <v>5032.575</v>
@@ -1541,18 +1541,18 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G35" t="n">
         <v>5.03</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B36" t="n">
         <v>5032.569</v>
@@ -1573,18 +1573,18 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G36" t="n">
         <v>5.03</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B37" t="n">
         <v>5026.415</v>
@@ -1605,18 +1605,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G37" t="n">
         <v>5.03</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B38" t="n">
         <v>4986.6</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G38" t="n">
         <v>4.99</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="39">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G39" t="n">
         <v>4.95</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="40">
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G40" t="n">
         <v>4.95</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B41" t="n">
         <v>4923.921</v>
@@ -1733,18 +1733,18 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G41" t="n">
         <v>4.92</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B42" t="n">
         <v>4676.806</v>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G42" t="n">
         <v>4.68</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="43">
@@ -1797,18 +1797,18 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G43" t="n">
         <v>4.64</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B44" t="n">
         <v>4583.431</v>
@@ -1829,18 +1829,18 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G44" t="n">
         <v>4.58</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B45" t="n">
         <v>4376.154</v>
@@ -1861,18 +1861,18 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G45" t="n">
         <v>4.38</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B46" t="n">
         <v>4333.934</v>
@@ -1893,18 +1893,18 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G46" t="n">
         <v>4.33</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B47" t="n">
         <v>4271.58</v>
@@ -1925,18 +1925,18 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G47" t="n">
         <v>4.27</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B48" t="n">
         <v>4257.587</v>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G48" t="n">
         <v>4.26</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B49" t="n">
         <v>4063.822</v>
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G49" t="n">
         <v>4.06</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G50" t="n">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B51" t="n">
         <v>3938.466</v>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G51" t="n">
         <v>3.94</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B52" t="n">
         <v>3855.441</v>
@@ -2085,18 +2085,18 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G52" t="n">
         <v>3.86</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B53" t="n">
         <v>3766.742</v>
@@ -2117,18 +2117,18 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G53" t="n">
         <v>3.77</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B54" t="n">
         <v>3728.89</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G54" t="n">
         <v>3.73</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="55">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G55" t="n">
         <v>3.72</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="56">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G56" t="n">
         <v>3.72</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="57">
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G57" t="n">
         <v>3.72</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B58" t="n">
-        <v>3673.75</v>
+        <v>3679.345</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2277,18 +2277,18 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G58" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B59" t="n">
         <v>3582.255</v>
@@ -2309,18 +2309,18 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G59" t="n">
         <v>3.58</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B60" t="n">
         <v>3520.169</v>
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G60" t="n">
         <v>3.52</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="61">
@@ -2373,18 +2373,18 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G61" t="n">
         <v>3.5</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B62" t="n">
         <v>3499.409</v>
@@ -2405,18 +2405,18 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G62" t="n">
         <v>3.5</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B63" t="n">
         <v>3481.809</v>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G63" t="n">
         <v>3.48</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="64">
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G64" t="n">
         <v>3.48</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B65" t="n">
         <v>3445.605</v>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G65" t="n">
         <v>3.45</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="66">
@@ -2533,18 +2533,18 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G66" t="n">
         <v>3.44</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B67" t="n">
         <v>3405.713</v>
@@ -2565,18 +2565,18 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G67" t="n">
         <v>3.41</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B68" t="n">
         <v>3337.25</v>
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G68" t="n">
         <v>3.34</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -2629,18 +2629,18 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G69" t="n">
         <v>3.28</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B70" t="n">
         <v>3208.067</v>
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G70" t="n">
         <v>3.21</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="71">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G71" t="n">
         <v>3.21</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="72">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G72" t="n">
         <v>3.14</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="73">
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G73" t="n">
         <v>3.1</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="74">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G74" t="n">
         <v>3.07</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="75">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G75" t="n">
         <v>3.07</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="76">
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G76" t="n">
         <v>3.06</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="77">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G77" t="n">
         <v>3.02</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="78">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G78" t="n">
         <v>3.02</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="79">
@@ -2949,18 +2949,18 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B80" t="n">
         <v>2988.916</v>
@@ -2981,18 +2981,18 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G80" t="n">
         <v>2.99</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B81" t="n">
         <v>2979</v>
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G81" t="n">
         <v>2.98</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B82" t="n">
         <v>2939.16</v>
@@ -3045,18 +3045,18 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G82" t="n">
         <v>2.94</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B83" t="n">
         <v>2926.106</v>
@@ -3077,18 +3077,18 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G83" t="n">
         <v>2.93</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B84" t="n">
         <v>2904.619</v>
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G84" t="n">
         <v>2.9</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B85" t="n">
         <v>2895</v>
@@ -3141,18 +3141,18 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G85" t="n">
         <v>2.9</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B86" t="n">
         <v>2811.471</v>
@@ -3173,18 +3173,18 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G86" t="n">
         <v>2.81</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -3205,18 +3205,18 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G87" t="n">
         <v>2.76</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="B88" t="n">
         <v>2726.181</v>
@@ -3237,18 +3237,18 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G88" t="n">
         <v>2.73</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B89" t="n">
         <v>2706.174</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G89" t="n">
         <v>2.71</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="90">
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G90" t="n">
         <v>2.7</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B91" t="n">
         <v>2660.688</v>
@@ -3333,18 +3333,18 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G91" t="n">
         <v>2.66</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B92" t="n">
         <v>2660.688</v>
@@ -3365,18 +3365,18 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G92" t="n">
         <v>2.66</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B93" t="n">
         <v>2631.963</v>
@@ -3397,18 +3397,18 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G93" t="n">
         <v>2.63</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B94" t="n">
         <v>2621.04</v>
@@ -3429,18 +3429,18 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G94" t="n">
         <v>2.62</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B95" t="n">
         <v>2621.04</v>
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G95" t="n">
         <v>2.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B96" t="n">
         <v>2621.04</v>
@@ -3493,18 +3493,18 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G96" t="n">
         <v>2.62</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B97" t="n">
         <v>2621.04</v>
@@ -3525,18 +3525,18 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G97" t="n">
         <v>2.62</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B98" t="n">
         <v>2575.208</v>
@@ -3557,18 +3557,18 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G98" t="n">
         <v>2.58</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B99" t="n">
         <v>2563.107</v>
@@ -3589,18 +3589,18 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G99" t="n">
         <v>2.56</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B100" t="n">
         <v>2543.714</v>
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G100" t="n">
         <v>2.54</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B101" t="n">
         <v>2540.764</v>
@@ -3653,18 +3653,18 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G101" t="n">
         <v>2.54</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="B102" t="n">
         <v>2499.861</v>
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G102" t="n">
         <v>2.5</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="103">
@@ -3717,18 +3717,18 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G103" t="n">
         <v>2.48</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="B104" t="n">
         <v>2458.319</v>
@@ -3749,18 +3749,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G104" t="n">
         <v>2.46</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B105" t="n">
         <v>2457.914</v>
@@ -3781,18 +3781,18 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G105" t="n">
         <v>2.46</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B106" t="n">
         <v>2450.365</v>
@@ -3813,18 +3813,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G106" t="n">
         <v>2.45</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="B107" t="n">
         <v>2417.248</v>
@@ -3845,18 +3845,18 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G107" t="n">
         <v>2.42</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B108" t="n">
         <v>2413.223</v>
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G108" t="n">
         <v>2.41</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B109" t="n">
         <v>2339.618</v>
@@ -3909,18 +3909,18 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G109" t="n">
         <v>2.34</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B110" t="n">
         <v>2326.922</v>
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G110" t="n">
         <v>2.33</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="B111" t="n">
         <v>2281.543</v>
@@ -3973,18 +3973,18 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G111" t="n">
         <v>2.28</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="B112" t="n">
         <v>2278.214</v>
@@ -4005,18 +4005,18 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G112" t="n">
         <v>2.28</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B113" t="n">
         <v>2261.775</v>
@@ -4037,18 +4037,18 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G113" t="n">
         <v>2.26</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B114" t="n">
         <v>2241.256</v>
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G114" t="n">
         <v>2.24</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B115" t="n">
         <v>2235.788</v>
@@ -4101,18 +4101,18 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G115" t="n">
         <v>2.24</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B116" t="n">
         <v>2214.878</v>
@@ -4133,18 +4133,18 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G116" t="n">
         <v>2.21</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="B117" t="n">
         <v>2192.483</v>
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G117" t="n">
         <v>2.19</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="118">
@@ -4197,18 +4197,18 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G118" t="n">
         <v>2.18</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B119" t="n">
         <v>2165.214</v>
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G119" t="n">
         <v>2.17</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B120" t="n">
         <v>2154.281</v>
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G120" t="n">
         <v>2.15</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="B121" t="n">
         <v>2147.981</v>
@@ -4293,18 +4293,18 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G121" t="n">
         <v>2.15</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B122" t="n">
         <v>2104.643</v>
@@ -4325,18 +4325,18 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G122" t="n">
         <v>2.1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B123" t="n">
         <v>2101.794</v>
@@ -4357,18 +4357,18 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G123" t="n">
         <v>2.1</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B124" t="n">
         <v>2100.259</v>
@@ -4389,18 +4389,18 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G124" t="n">
         <v>2.1</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G125" t="n">
         <v>2.1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="B126" t="n">
         <v>2092.411</v>
@@ -4453,18 +4453,18 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G126" t="n">
         <v>2.09</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B127" t="n">
         <v>2057</v>
@@ -4485,18 +4485,18 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G127" t="n">
         <v>2.06</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="B128" t="n">
         <v>2047.984</v>
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G128" t="n">
         <v>2.05</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2069</v>
+        <v>2063</v>
       </c>
       <c r="B129" t="n">
         <v>2016.514</v>
@@ -4549,18 +4549,18 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G129" t="n">
         <v>2.02</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2081</v>
+        <v>2073</v>
       </c>
       <c r="B130" t="n">
         <v>2010.821</v>
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G130" t="n">
         <v>2.01</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="B131" t="n">
         <v>2008.814</v>
@@ -4613,18 +4613,18 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G131" t="n">
         <v>2.01</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="B132" t="n">
         <v>2004.739</v>
@@ -4645,18 +4645,18 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G132" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2133</v>
+        <v>2129</v>
       </c>
       <c r="B133" t="n">
         <v>1963.898</v>
@@ -4677,18 +4677,18 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G133" t="n">
         <v>1.96</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B134" t="n">
         <v>1948.176</v>
@@ -4709,18 +4709,18 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G134" t="n">
         <v>1.95</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B135" t="n">
         <v>1942.966</v>
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G135" t="n">
         <v>1.94</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B136" t="n">
         <v>1935.918</v>
@@ -4773,18 +4773,18 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G136" t="n">
         <v>1.94</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="B137" t="n">
         <v>1898.548</v>
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G137" t="n">
         <v>1.9</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="B138" t="n">
         <v>1865.074</v>
@@ -4837,18 +4837,18 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G138" t="n">
         <v>1.87</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="B139" t="n">
         <v>1863.725</v>
@@ -4869,18 +4869,18 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1779198002271</v>
+        <v>1779208802311</v>
       </c>
       <c r="G139" t="n">
         <v>1.86</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.9236378588</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B140" t="n">
         <v>1830.164</v>
@@ -4901,18 +4901,18 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G140" t="n">
         <v>1.83</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B141" t="n">
         <v>1829.683</v>
@@ -4933,18 +4933,18 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G141" t="n">
         <v>1.83</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="B142" t="n">
         <v>1806.507</v>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G142" t="n">
         <v>1.81</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="143">
@@ -4997,18 +4997,18 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G143" t="n">
         <v>1.8</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="B144" t="n">
         <v>1782.941</v>
@@ -5029,18 +5029,18 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G144" t="n">
         <v>1.78</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="B145" t="n">
         <v>1781.03</v>
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G145" t="n">
         <v>1.78</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="B146" t="n">
         <v>1760.988</v>
@@ -5093,18 +5093,18 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G146" t="n">
         <v>1.76</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="B147" t="n">
         <v>1753.479</v>
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G147" t="n">
         <v>1.75</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="B148" t="n">
         <v>1716.6</v>
@@ -5157,18 +5157,18 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G148" t="n">
         <v>1.72</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B149" t="n">
         <v>1711.584</v>
@@ -5189,18 +5189,18 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G149" t="n">
         <v>1.71</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="B150" t="n">
         <v>1692.54</v>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G150" t="n">
         <v>1.69</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="151">
@@ -5253,18 +5253,18 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G151" t="n">
         <v>1.69</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B152" t="n">
         <v>1688.326</v>
@@ -5285,18 +5285,18 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G152" t="n">
         <v>1.69</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="B153" t="n">
         <v>1686.861</v>
@@ -5317,18 +5317,18 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G153" t="n">
         <v>1.69</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="B154" t="n">
         <v>1686.397</v>
@@ -5349,18 +5349,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G154" t="n">
         <v>1.69</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B155" t="n">
         <v>1682.312</v>
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G155" t="n">
         <v>1.68</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="B156" t="n">
         <v>1664.261</v>
@@ -5413,18 +5413,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G156" t="n">
         <v>1.66</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B157" t="n">
         <v>1648.328</v>
@@ -5445,18 +5445,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G157" t="n">
         <v>1.65</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B158" t="n">
         <v>1642.892</v>
@@ -5477,18 +5477,18 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G158" t="n">
         <v>1.64</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B159" t="n">
         <v>1636.369</v>
@@ -5509,18 +5509,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G159" t="n">
         <v>1.64</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="B160" t="n">
         <v>1634.503</v>
@@ -5541,18 +5541,18 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G160" t="n">
         <v>1.63</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2502</v>
+        <v>2497</v>
       </c>
       <c r="B161" t="n">
         <v>1598.308</v>
@@ -5573,18 +5573,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G161" t="n">
         <v>1.6</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B162" t="n">
         <v>1585.722</v>
@@ -5605,18 +5605,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G162" t="n">
         <v>1.59</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="B163" t="n">
         <v>1570.959</v>
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G163" t="n">
         <v>1.57</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="164">
@@ -5669,18 +5669,18 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G164" t="n">
         <v>1.56</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="B165" t="n">
         <v>1551.059</v>
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G165" t="n">
         <v>1.55</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="166">
@@ -5733,18 +5733,18 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G166" t="n">
         <v>1.54</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="B167" t="n">
         <v>1535.967</v>
@@ -5765,18 +5765,18 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G167" t="n">
         <v>1.54</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="B168" t="n">
         <v>1533.654</v>
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G168" t="n">
         <v>1.53</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="B169" t="n">
         <v>1527.065</v>
@@ -5829,18 +5829,18 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1779198002271</v>
+        <v>1779208802312</v>
       </c>
       <c r="G169" t="n">
         <v>1.53</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46161.79863739583</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2631</v>
+        <v>2636</v>
       </c>
       <c r="B170" t="n">
         <v>1500</v>
@@ -5861,18 +5861,18 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G170" t="n">
         <v>1.5</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="B171" t="n">
         <v>1496.758</v>
@@ -5893,18 +5893,18 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G171" t="n">
         <v>1.5</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="B172" t="n">
         <v>1496.758</v>
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G172" t="n">
         <v>1.5</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="B173" t="n">
         <v>1479.294</v>
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G173" t="n">
         <v>1.48</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="174">
@@ -5989,18 +5989,18 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G174" t="n">
         <v>1.47</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="B175" t="n">
         <v>1448.418</v>
@@ -6021,18 +6021,18 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G175" t="n">
         <v>1.45</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="B176" t="n">
         <v>1446.827</v>
@@ -6053,18 +6053,18 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G176" t="n">
         <v>1.45</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="B177" t="n">
         <v>1414.754</v>
@@ -6085,18 +6085,18 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G177" t="n">
         <v>1.41</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2737</v>
+        <v>2734</v>
       </c>
       <c r="B178" t="n">
         <v>1411.854</v>
@@ -6117,18 +6117,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G178" t="n">
         <v>1.41</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="B179" t="n">
         <v>1409.878</v>
@@ -6149,18 +6149,18 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G179" t="n">
         <v>1.41</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2744</v>
+        <v>2740</v>
       </c>
       <c r="B180" t="n">
         <v>1408.744</v>
@@ -6181,18 +6181,18 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G180" t="n">
         <v>1.41</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2758</v>
+        <v>2752</v>
       </c>
       <c r="B181" t="n">
         <v>1401.953</v>
@@ -6213,18 +6213,18 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G181" t="n">
         <v>1.4</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2802</v>
+        <v>2797</v>
       </c>
       <c r="B182" t="n">
         <v>1376.279</v>
@@ -6245,18 +6245,18 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G182" t="n">
         <v>1.38</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2803</v>
+        <v>2798</v>
       </c>
       <c r="B183" t="n">
         <v>1375.923</v>
@@ -6277,18 +6277,18 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G183" t="n">
         <v>1.38</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2805</v>
+        <v>2800</v>
       </c>
       <c r="B184" t="n">
         <v>1375.254</v>
@@ -6309,18 +6309,18 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G184" t="n">
         <v>1.38</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2809</v>
+        <v>2805</v>
       </c>
       <c r="B185" t="n">
         <v>1373.237</v>
@@ -6341,18 +6341,18 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G185" t="n">
         <v>1.37</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="B186" t="n">
         <v>1356.362</v>
@@ -6373,13 +6373,13 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G186" t="n">
         <v>1.36</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="187">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G187" t="n">
         <v>1.34</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="188">
@@ -6437,18 +6437,18 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G188" t="n">
         <v>1.34</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="B189" t="n">
         <v>1314.935</v>
@@ -6469,18 +6469,18 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G189" t="n">
         <v>1.31</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B190" t="n">
         <v>1306.807</v>
@@ -6501,18 +6501,18 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G190" t="n">
         <v>1.31</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="B191" t="n">
         <v>1294.918</v>
@@ -6533,18 +6533,18 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G191" t="n">
         <v>1.29</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B192" t="n">
         <v>1294.904</v>
@@ -6565,18 +6565,18 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G192" t="n">
         <v>1.29</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B193" t="n">
         <v>1294.904</v>
@@ -6597,18 +6597,18 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G193" t="n">
         <v>1.29</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="B194" t="n">
         <v>1292.64</v>
@@ -6629,18 +6629,18 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G194" t="n">
         <v>1.29</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B195" t="n">
         <v>1278.9</v>
@@ -6661,18 +6661,18 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G195" t="n">
         <v>1.28</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="B196" t="n">
         <v>1266.384</v>
@@ -6693,18 +6693,18 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G196" t="n">
         <v>1.27</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="B197" t="n">
         <v>1261.925</v>
@@ -6725,18 +6725,18 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G197" t="n">
         <v>1.26</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="B198" t="n">
         <v>1259.521</v>
@@ -6757,18 +6757,18 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G198" t="n">
         <v>1.26</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B199" t="n">
         <v>1253.699</v>
@@ -6789,18 +6789,18 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G199" t="n">
         <v>1.25</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B200" t="n">
         <v>1250.342</v>
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G200" t="n">
         <v>1.25</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B201" t="n">
         <v>1250.342</v>
@@ -6853,18 +6853,18 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G201" t="n">
         <v>1.25</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="B202" t="n">
         <v>1210.713</v>
@@ -6885,18 +6885,18 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G202" t="n">
         <v>1.21</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="B203" t="n">
         <v>1210.629</v>
@@ -6917,18 +6917,18 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G203" t="n">
         <v>1.21</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="B204" t="n">
         <v>1185.412</v>
@@ -6949,18 +6949,18 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G204" t="n">
         <v>1.19</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="B205" t="n">
         <v>1160.96</v>
@@ -6981,18 +6981,18 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G205" t="n">
         <v>1.16</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B206" t="n">
         <v>1155.838</v>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G206" t="n">
         <v>1.16</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="B207" t="n">
         <v>1149.133</v>
@@ -7045,18 +7045,18 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G207" t="n">
         <v>1.15</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3172</v>
+        <v>3169</v>
       </c>
       <c r="B208" t="n">
         <v>1138.052</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G208" t="n">
         <v>1.14</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3178</v>
+        <v>3175</v>
       </c>
       <c r="B209" t="n">
         <v>1135.379</v>
@@ -7109,18 +7109,18 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G209" t="n">
         <v>1.14</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3190</v>
+        <v>3192</v>
       </c>
       <c r="B210" t="n">
         <v>1127.916</v>
@@ -7141,18 +7141,18 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G210" t="n">
         <v>1.13</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3233</v>
+        <v>3230</v>
       </c>
       <c r="B211" t="n">
         <v>1105.436</v>
@@ -7173,18 +7173,18 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G211" t="n">
         <v>1.11</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3234</v>
+        <v>3231</v>
       </c>
       <c r="B212" t="n">
         <v>1104.74</v>
@@ -7205,18 +7205,18 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G212" t="n">
         <v>1.1</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3235</v>
+        <v>3232</v>
       </c>
       <c r="B213" t="n">
         <v>1104.361</v>
@@ -7237,18 +7237,18 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G213" t="n">
         <v>1.1</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3255</v>
+        <v>3252</v>
       </c>
       <c r="B214" t="n">
         <v>1095.926</v>
@@ -7269,18 +7269,18 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G214" t="n">
         <v>1.1</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="B215" t="n">
         <v>1090.188</v>
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G215" t="n">
         <v>1.09</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3275</v>
+        <v>3272</v>
       </c>
       <c r="B216" t="n">
         <v>1081.852</v>
@@ -7333,18 +7333,18 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G216" t="n">
         <v>1.08</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3284</v>
+        <v>3281</v>
       </c>
       <c r="B217" t="n">
         <v>1077.194</v>
@@ -7365,18 +7365,18 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G217" t="n">
         <v>1.08</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3284</v>
+        <v>3281</v>
       </c>
       <c r="B218" t="n">
         <v>1077.194</v>
@@ -7397,18 +7397,18 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G218" t="n">
         <v>1.08</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3305</v>
+        <v>3302</v>
       </c>
       <c r="B219" t="n">
         <v>1061.292</v>
@@ -7429,18 +7429,18 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G219" t="n">
         <v>1.06</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3335</v>
+        <v>3332</v>
       </c>
       <c r="B220" t="n">
         <v>1032.26</v>
@@ -7461,18 +7461,18 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G220" t="n">
         <v>1.03</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3338</v>
+        <v>3335</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -7493,18 +7493,18 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G221" t="n">
         <v>1.03</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3338</v>
+        <v>3335</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -7525,18 +7525,18 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G222" t="n">
         <v>1.03</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="B223" t="n">
         <v>996.251</v>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1779198002272</v>
+        <v>1779208802312</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46161.79863740741</v>
+        <v>46161.92363787037</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         <v>89.25</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>80.67</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>37.61</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>28.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>26.26</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="7">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>26.25</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>25.82</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="9">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
         <v>21.31</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B10" t="n">
         <v>16189.48</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -893,12 +893,12 @@
         <v>16.19</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B11" t="n">
         <v>13963.402</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,12 +940,12 @@
         <v>13.96</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B12" t="n">
         <v>12746.882</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>12.75</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="13">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1034,12 +1034,12 @@
         <v>12.5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B14" t="n">
         <v>11476.259</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="15">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>10.3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="16">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1779215402562</v>
+        <v>1779222002410</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1175,12 +1175,12 @@
         <v>10.21</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46162.00002965278</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B17" t="n">
         <v>9136.491</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="18">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1269,12 +1269,12 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B19" t="n">
         <v>8575.26</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1316,12 +1316,12 @@
         <v>8.58</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B20" t="n">
         <v>8250.538</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>8.25</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>7.89</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>7.72</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
         <v>7.72</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B24" t="n">
         <v>7608.8</v>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,12 +1551,12 @@
         <v>7.61</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B25" t="n">
         <v>7290.358</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>7.29</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
         <v>6.35</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B27" t="n">
         <v>6073.892</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1692,12 +1692,12 @@
         <v>6.07</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B28" t="n">
         <v>5859.767</v>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>5.86</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="29">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1786,12 +1786,12 @@
         <v>5.6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B30" t="n">
         <v>5469.746</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1833,12 +1833,12 @@
         <v>5.47</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B31" t="n">
         <v>5246.694</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1880,12 +1880,12 @@
         <v>5.25</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B32" t="n">
         <v>5165.05</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1927,12 +1927,12 @@
         <v>5.17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B33" t="n">
         <v>5145.149</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1974,12 +1974,12 @@
         <v>5.15</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B34" t="n">
         <v>5145.149</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>5.15</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="35">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>5.03</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="36">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>5.03</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="37">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2162,12 +2162,12 @@
         <v>5.03</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B38" t="n">
         <v>4986.6</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
         <v>4.99</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B39" t="n">
         <v>4949.227</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>4.95</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="40">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>4.95</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="41">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
         <v>4.92</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B42" t="n">
         <v>4676.806</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2397,12 +2397,12 @@
         <v>4.68</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B43" t="n">
         <v>4639.965</v>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2444,12 +2444,12 @@
         <v>4.64</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B44" t="n">
         <v>4583.431</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2491,12 +2491,12 @@
         <v>4.58</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B45" t="n">
         <v>4376.154</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>4.38</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="46">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>4.33</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="47">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2632,12 +2632,12 @@
         <v>4.27</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B48" t="n">
         <v>4257.587</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2679,12 +2679,12 @@
         <v>4.26</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B49" t="n">
         <v>4063.822</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2726,12 +2726,12 @@
         <v>4.06</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="51">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>3.94</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="52">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
         <v>3.86</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B53" t="n">
         <v>3766.742</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2914,12 +2914,12 @@
         <v>3.77</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B54" t="n">
         <v>3728.89</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>3.73</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="55">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>3.72</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="56">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>3.72</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="57">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>3.72</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="58">
@@ -3110,7 +3110,7 @@
         <v>1168</v>
       </c>
       <c r="B58" t="n">
-        <v>3680.318</v>
+        <v>3679.75</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
         <v>3.68</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B59" t="n">
         <v>3582.255</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1779215402563</v>
+        <v>1779222002410</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
         <v>3.58</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641678241</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B60" t="n">
         <v>3520.169</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3239,12 +3239,12 @@
         <v>3.52</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B61" t="n">
         <v>3504.698</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
         <v>3.5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B62" t="n">
         <v>3499.409</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
         <v>3.5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B63" t="n">
         <v>3481.809</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3380,12 +3380,12 @@
         <v>3.48</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B64" t="n">
         <v>3480.546</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
         <v>3.48</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B65" t="n">
         <v>3445.605</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3474,12 +3474,12 @@
         <v>3.45</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="B66" t="n">
         <v>3440.07</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3521,12 +3521,12 @@
         <v>3.44</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B67" t="n">
         <v>3405.713</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3568,12 +3568,12 @@
         <v>3.41</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B68" t="n">
         <v>3337.25</v>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.34</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="69">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>3.28</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="70">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>3.21</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="71">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3756,12 +3756,12 @@
         <v>3.21</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B72" t="n">
         <v>3135.506</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3803,12 +3803,12 @@
         <v>3.14</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B73" t="n">
         <v>3100.307</v>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>3.1</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="74">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>3.07</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="75">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3944,12 +3944,12 @@
         <v>3.07</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3991,12 +3991,12 @@
         <v>3.06</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B77" t="n">
         <v>3022.137</v>
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>3.02</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="78">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>3.02</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="79">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="80">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>2.99</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="81">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4226,12 +4226,12 @@
         <v>2.98</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B82" t="n">
         <v>2939.16</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
         <v>2.94</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B83" t="n">
         <v>2926.106</v>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>2.93</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="84">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4367,12 +4367,12 @@
         <v>2.9</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B85" t="n">
         <v>2895</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4414,12 +4414,12 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B86" t="n">
         <v>2811.471</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4461,12 +4461,12 @@
         <v>2.81</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4508,12 +4508,12 @@
         <v>2.76</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B88" t="n">
         <v>2726.181</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>2.73</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="89">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>2.71</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="90">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>2.7</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="91">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>2.66</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="92">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>2.66</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="93">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4790,12 +4790,12 @@
         <v>2.63</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B94" t="n">
         <v>2621.04</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4837,12 +4837,12 @@
         <v>2.62</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B95" t="n">
         <v>2621.04</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4884,12 +4884,12 @@
         <v>2.62</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B96" t="n">
         <v>2621.04</v>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4931,12 +4931,12 @@
         <v>2.62</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B97" t="n">
         <v>2621.04</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4978,12 +4978,12 @@
         <v>2.62</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B98" t="n">
         <v>2575.208</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5025,12 +5025,12 @@
         <v>2.58</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="B99" t="n">
         <v>2563.107</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="100">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>2.54</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="101">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>2.54</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="102">
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>2.5</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="103">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5260,12 +5260,12 @@
         <v>2.48</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B104" t="n">
         <v>2458.319</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5307,12 +5307,12 @@
         <v>2.46</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B105" t="n">
         <v>2457.914</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5354,12 +5354,12 @@
         <v>2.46</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B106" t="n">
         <v>2450.365</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5401,12 +5401,12 @@
         <v>2.45</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B107" t="n">
         <v>2417.248</v>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5448,12 +5448,12 @@
         <v>2.42</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B108" t="n">
         <v>2413.223</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5495,12 +5495,12 @@
         <v>2.41</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B109" t="n">
         <v>2339.618</v>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5542,12 +5542,12 @@
         <v>2.34</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B110" t="n">
         <v>2326.922</v>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5589,12 +5589,12 @@
         <v>2.33</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="B111" t="n">
         <v>2281.543</v>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>2.28</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="112">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>2.28</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="113">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>2.26</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="114">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5777,12 +5777,12 @@
         <v>2.24</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B115" t="n">
         <v>2235.788</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5824,12 +5824,12 @@
         <v>2.24</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B116" t="n">
         <v>2214.878</v>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5871,12 +5871,12 @@
         <v>2.21</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B117" t="n">
         <v>2192.483</v>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5918,12 +5918,12 @@
         <v>2.19</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B118" t="n">
         <v>2180.293</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
         <v>2.18</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="B119" t="n">
         <v>2165.214</v>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6012,12 +6012,12 @@
         <v>2.17</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="B120" t="n">
         <v>2154.281</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6059,12 +6059,12 @@
         <v>2.15</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="B121" t="n">
         <v>2147.981</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6106,12 +6106,12 @@
         <v>2.15</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B122" t="n">
         <v>2104.643</v>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6153,12 +6153,12 @@
         <v>2.1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B123" t="n">
         <v>2101.794</v>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6200,12 +6200,12 @@
         <v>2.1</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B124" t="n">
         <v>2100.259</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6247,12 +6247,12 @@
         <v>2.1</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>2.1</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="126">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6341,12 +6341,12 @@
         <v>2.09</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B127" t="n">
         <v>2057</v>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6388,12 +6388,12 @@
         <v>2.06</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B128" t="n">
         <v>2047.984</v>
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6435,12 +6435,12 @@
         <v>2.05</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B129" t="n">
         <v>2016.514</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6482,12 +6482,12 @@
         <v>2.02</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="B130" t="n">
         <v>2010.821</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6529,12 +6529,12 @@
         <v>2.01</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="B131" t="n">
         <v>2008.814</v>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>2.01</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="132">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6623,12 +6623,12 @@
         <v>2</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="B133" t="n">
         <v>1963.898</v>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6670,12 +6670,12 @@
         <v>1.96</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="B134" t="n">
         <v>1948.176</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
         <v>1.95</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2153</v>
+        <v>2149</v>
       </c>
       <c r="B135" t="n">
         <v>1942.966</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6764,12 +6764,12 @@
         <v>1.94</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="B136" t="n">
         <v>1935.918</v>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>1.94</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="137">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6858,12 +6858,12 @@
         <v>1.9</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="B138" t="n">
         <v>1865.074</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6905,12 +6905,12 @@
         <v>1.87</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="B139" t="n">
         <v>1863.725</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>1.86</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="140">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.83</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="141">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>1.83</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="142">
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -7093,12 +7093,12 @@
         <v>1.81</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="B143" t="n">
         <v>1798.554</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>1.8</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="144">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>1.78</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="145">
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7234,12 +7234,12 @@
         <v>1.78</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="B146" t="n">
         <v>1760.988</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -7281,12 +7281,12 @@
         <v>1.76</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B147" t="n">
         <v>1753.479</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7328,12 +7328,12 @@
         <v>1.75</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="B148" t="n">
         <v>1716.6</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7375,12 +7375,12 @@
         <v>1.72</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B149" t="n">
         <v>1711.584</v>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>1.71</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="150">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>1.69</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="151">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>1.69</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="152">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>1.69</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="153">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>1.69</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="154">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>1.69</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="155">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7704,12 +7704,12 @@
         <v>1.68</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="B156" t="n">
         <v>1664.261</v>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>1.66</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="157">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7798,12 +7798,12 @@
         <v>1.65</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="B158" t="n">
         <v>1642.892</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7845,12 +7845,12 @@
         <v>1.64</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2468</v>
+        <v>2465</v>
       </c>
       <c r="B159" t="n">
         <v>1636.369</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7892,12 +7892,12 @@
         <v>1.64</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="B160" t="n">
         <v>1634.503</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7939,12 +7939,12 @@
         <v>1.63</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="B161" t="n">
         <v>1598.308</v>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7986,12 +7986,12 @@
         <v>1.6</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B162" t="n">
         <v>1585.722</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>1.59</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="163">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8080,12 +8080,12 @@
         <v>1.57</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="B164" t="n">
         <v>1555.265</v>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -8127,12 +8127,12 @@
         <v>1.56</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="B165" t="n">
         <v>1551.059</v>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8174,12 +8174,12 @@
         <v>1.55</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="B166" t="n">
         <v>1544.473</v>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
         <v>1.54</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="B167" t="n">
         <v>1535.967</v>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8268,12 +8268,12 @@
         <v>1.54</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="B168" t="n">
         <v>1533.654</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8315,12 +8315,12 @@
         <v>1.53</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="B169" t="n">
         <v>1527.065</v>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8362,12 +8362,12 @@
         <v>1.53</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="B170" t="n">
         <v>1500</v>
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8409,12 +8409,12 @@
         <v>1.5</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B171" t="n">
         <v>1496.758</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8456,12 +8456,12 @@
         <v>1.5</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B172" t="n">
         <v>1496.758</v>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8503,12 +8503,12 @@
         <v>1.5</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="B173" t="n">
         <v>1479.294</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>1.48</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="174">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>1.47</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="175">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8644,12 +8644,12 @@
         <v>1.45</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="B176" t="n">
         <v>1446.827</v>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8691,12 +8691,12 @@
         <v>1.45</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="B177" t="n">
         <v>1414.754</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8738,12 +8738,12 @@
         <v>1.41</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="B178" t="n">
         <v>1411.854</v>
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8785,12 +8785,12 @@
         <v>1.41</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="B179" t="n">
         <v>1409.878</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8832,12 +8832,12 @@
         <v>1.41</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B180" t="n">
         <v>1408.744</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8879,12 +8879,12 @@
         <v>1.41</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="B181" t="n">
         <v>1401.953</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8926,12 +8926,12 @@
         <v>1.4</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="B182" t="n">
         <v>1376.279</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8973,12 +8973,12 @@
         <v>1.38</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="B183" t="n">
         <v>1375.923</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -9020,12 +9020,12 @@
         <v>1.38</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="B184" t="n">
         <v>1375.254</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9067,12 +9067,12 @@
         <v>1.38</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="B185" t="n">
         <v>1373.237</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>1.37</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="186">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -9161,12 +9161,12 @@
         <v>1.36</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2842</v>
+        <v>2839</v>
       </c>
       <c r="B187" t="n">
         <v>1344.178</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9208,12 +9208,12 @@
         <v>1.34</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="B188" t="n">
         <v>1340.059</v>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>1.34</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="189">
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9302,12 +9302,12 @@
         <v>1.31</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2905</v>
+        <v>2901</v>
       </c>
       <c r="B190" t="n">
         <v>1306.807</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9349,12 +9349,12 @@
         <v>1.31</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="B191" t="n">
         <v>1294.918</v>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
         <v>1.29</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B192" t="n">
         <v>1294.904</v>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -9443,12 +9443,12 @@
         <v>1.29</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B193" t="n">
         <v>1294.904</v>
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9490,12 +9490,12 @@
         <v>1.29</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B194" t="n">
         <v>1292.64</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>1.29</v>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="195">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>1.28</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="196">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>1.27</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="197">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>1.26</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="198">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>1.26</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="199">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>1.25</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="200">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>1.25</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="201">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>1.25</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="202">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>1.21</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="203">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -9960,12 +9960,12 @@
         <v>1.21</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B204" t="n">
         <v>1185.412</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>1.19</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="205">
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -10054,12 +10054,12 @@
         <v>1.16</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="B206" t="n">
         <v>1155.838</v>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -10101,12 +10101,12 @@
         <v>1.16</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="B207" t="n">
         <v>1149.133</v>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>1.15</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="208">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>1.14</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="209">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -10242,12 +10242,12 @@
         <v>1.14</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B210" t="n">
         <v>1127.916</v>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>1779215402563</v>
+        <v>1779222002411</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
         <v>1.13</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>46162.00002966435</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="B211" t="n">
         <v>1105.436</v>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -10336,12 +10336,12 @@
         <v>1.11</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="B212" t="n">
         <v>1104.74</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -10383,12 +10383,12 @@
         <v>1.1</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="B213" t="n">
         <v>1104.361</v>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -10430,12 +10430,12 @@
         <v>1.1</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3253</v>
+        <v>3250</v>
       </c>
       <c r="B214" t="n">
         <v>1095.926</v>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -10477,12 +10477,12 @@
         <v>1.1</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3262</v>
+        <v>3259</v>
       </c>
       <c r="B215" t="n">
         <v>1090.188</v>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -10524,12 +10524,12 @@
         <v>1.09</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B216" t="n">
         <v>1081.852</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.08</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="217">
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>1.08</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="218">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -10665,12 +10665,12 @@
         <v>1.08</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="B219" t="n">
         <v>1061.292</v>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -10712,12 +10712,12 @@
         <v>1.06</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3334</v>
+        <v>3331</v>
       </c>
       <c r="B220" t="n">
         <v>1032.26</v>
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -10759,12 +10759,12 @@
         <v>1.03</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3337</v>
+        <v>3335</v>
       </c>
       <c r="B221" t="n">
         <v>1031.325</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -10806,12 +10806,12 @@
         <v>1.03</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3337</v>
+        <v>3335</v>
       </c>
       <c r="B222" t="n">
         <v>1031.325</v>
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -10853,12 +10853,12 @@
         <v>1.03</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="B223" t="n">
         <v>996.251</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>1779215402564</v>
+        <v>1779222002411</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>46162.00002967592</v>
+        <v>46162.07641679399</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         <v>89.25</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>80.67</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>37.61</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>28.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>26.26</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="7">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>26.25</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>25.82</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="9">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>21.31</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>16.19</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="11">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>13.96</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>12.75</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="13">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>12.5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="15">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>10.3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="16">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>10.21</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="17">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="18">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1779222002410</v>
+        <v>1779227402205</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.13891440972</v>
       </c>
     </row>
     <row r="19">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>8.58</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="20">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>8.25</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>7.89</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>7.72</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>7.72</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="24">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>7.61</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="25">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>7.29</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>6.35</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="27">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>6.07</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="28">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>5.86</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="29">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>5.6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="30">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>5.47</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="31">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>5.25</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="32">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>5.17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="33">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>5.15</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>5.15</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="35">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>5.03</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="36">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>5.03</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="37">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>5.03</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="38">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>4.99</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="39">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>4.95</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="40">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>4.95</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="41">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>4.92</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="42">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>4.68</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="43">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>4.64</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="44">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>4.58</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="45">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>4.38</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="46">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>4.33</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="47">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>4.27</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="48">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>4.26</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>4.06</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="50">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="51">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>3.94</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="52">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>3.86</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="53">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>3.77</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="54">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>3.73</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="55">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>3.72</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="56">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>3.72</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="57">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>3.72</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="58">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>3.68</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="59">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1779222002410</v>
+        <v>1779227402206</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>3.58</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46162.07641678241</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="60">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>3.52</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="61">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>3.5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="62">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>3.5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="63">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>3.48</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="64">
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>3.48</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="65">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>3.45</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="66">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>3.44</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="67">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>3.41</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="68">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.34</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="69">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>3.28</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="70">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>3.21</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="71">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>3.21</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="72">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>3.14</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="73">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>3.1</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="74">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>3.07</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="75">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>3.07</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="76">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>3.06</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="77">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>3.02</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="78">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>3.02</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="79">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="80">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>2.99</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="81">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>2.98</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="82">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>2.94</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="83">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>2.93</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="84">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>2.9</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="85">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="86">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>2.81</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="87">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>2.76</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="88">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>2.73</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="89">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>2.71</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="90">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>2.7</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="91">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>2.66</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="92">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>2.66</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="93">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>2.63</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="94">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>2.62</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="95">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>2.62</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="96">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>2.62</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="97">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>2.62</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="98">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>2.58</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="99">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="100">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>2.54</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="101">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>2.54</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="102">
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>2.5</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="103">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>2.48</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="104">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>2.46</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="105">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>2.46</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="106">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>2.45</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="107">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>2.42</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="108">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>2.41</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="109">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>2.34</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="110">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>2.33</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="111">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>2.28</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="112">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>2.28</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="113">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>2.26</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="114">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>2.24</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="115">
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>2.24</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="116">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>2.21</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="117">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>2.19</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="118">
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>2.18</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="119">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>2.17</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="120">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>2.15</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="121">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>2.15</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="122">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>2.1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="123">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>2.1</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="124">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>2.1</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="125">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>2.1</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="126">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>2.09</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="127">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>2.06</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="128">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>2.05</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="129">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>2.02</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="130">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>2.01</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="131">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>2.01</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="132">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>2</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="133">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>1.96</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="134">
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>1.95</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="135">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>1.94</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="136">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>1.94</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="137">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>1.9</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="138">
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>1.87</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="139">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>1.86</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="140">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.83</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="141">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>1.83</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="142">
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>1.81</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="143">
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>1.8</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="144">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>1.78</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="145">
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>1.78</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="146">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>1.76</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="147">
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>1.75</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="148">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>1.72</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="149">
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1779222002411</v>
+        <v>1779227402206</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>1.71</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.1389144213</v>
       </c>
     </row>
     <row r="150">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>1.69</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="151">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>1.69</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="152">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>1.69</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="153">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>1.69</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="154">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>1.69</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="155">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>1.68</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="156">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>1.66</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="157">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>1.65</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="158">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>1.64</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="159">
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>1.64</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="160">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>1.63</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="161">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>1.6</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="162">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>1.59</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="163">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>1.57</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="164">
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>1.56</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="165">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.55</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="166">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>1.54</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="167">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>1.54</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="168">
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>1.53</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="169">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>1.53</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="170">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>1.5</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="171">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>1.5</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="172">
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>1.5</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="173">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>1.48</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="174">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
         <v>1.47</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="B175" t="n">
         <v>1448.418</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8644,12 +8644,12 @@
         <v>1.45</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="B176" t="n">
         <v>1446.827</v>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>1.45</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="177">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>1.41</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="178">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>1.41</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="179">
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1.41</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="180">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8879,12 +8879,12 @@
         <v>1.41</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="B181" t="n">
         <v>1401.953</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>1.4</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="182">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>1.38</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="183">
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>1.38</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="184">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>1.38</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="185">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>1.37</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="186">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>1.36</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="187">
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>1.34</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="188">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>1.34</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="189">
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>1.31</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="190">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>1.31</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="191">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>1.29</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="192">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>1.29</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="193">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>1.29</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="194">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>1.29</v>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="195">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>1.28</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="196">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>1.27</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="197">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>1.26</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="198">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>1.26</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="199">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>1.25</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="200">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>1.25</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="201">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>1.25</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="202">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>1.21</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="203">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>1.21</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="204">
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>1.19</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="205">
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>1.16</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="206">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>1.16</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="207">
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>1.15</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="208">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>1.14</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="209">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>1.14</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="210">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
         <v>1.13</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="B211" t="n">
         <v>1105.436</v>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>1.11</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="212">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>1.1</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="213">
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>1.1</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="214">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -10477,12 +10477,12 @@
         <v>1.1</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="B215" t="n">
         <v>1090.188</v>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>1.09</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="216">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.08</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="217">
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>1.08</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="218">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>1.08</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="219">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>1.06</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="220">
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>1.03</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="221">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>1.03</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="222">
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>1.03</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
     <row r="223">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>1779222002411</v>
+        <v>1779227402207</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>46162.07641679399</v>
+        <v>46162.13891443287</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         <v>89.25</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>80.67</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>37.61</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>28.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>26.26</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="7">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>26.25</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>25.82</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="9">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>21.31</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>16.19</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="11">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>13.96</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>12.75</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="13">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>12.5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="15">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>10.3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="16">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>10.21</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="17">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="18">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1779227402205</v>
+        <v>1779231302092</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46162.13891440972</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="19">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>8.58</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="20">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>8.25</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>7.89</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>7.72</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>7.72</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="24">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>7.61</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="25">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>7.29</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>6.35</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="27">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>6.07</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="28">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>5.86</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="29">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>5.6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="30">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>5.47</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="31">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>5.25</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="32">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>5.17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="33">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>5.15</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>5.15</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="35">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>5.03</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="36">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>5.03</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="37">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>5.03</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="38">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>4.99</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="39">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>4.95</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="40">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>4.95</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="41">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>4.92</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="42">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>4.68</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="43">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>4.64</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="44">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>4.58</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="45">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>4.38</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="46">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>4.33</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="47">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>4.27</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="48">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>4.26</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>4.06</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="50">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="51">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>3.94</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="52">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
         <v>3.86</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B53" t="n">
         <v>3766.742</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>3.77</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="54">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>3.73</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="55">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>3.72</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="56">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>3.72</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="57">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>3.72</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="58">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>3.68</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="59">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>3.58</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="60">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>3.52</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="61">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>3.5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="62">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>3.5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="63">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>3.48</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="64">
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>3.48</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="65">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>3.45</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="66">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>3.44</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="67">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>3.41</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="68">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.34</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="69">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>3.28</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="70">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>3.21</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="71">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>3.21</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="72">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>3.14</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="73">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>3.1</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="74">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>3.07</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="75">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>3.07</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="76">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>3.06</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="77">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>3.02</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="78">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>3.02</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="79">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="80">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>2.99</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="81">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>2.98</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="82">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>2.94</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="83">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>2.93</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="84">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>2.9</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="85">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="86">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>2.81</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="87">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>2.76</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="88">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>2.73</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="89">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>2.71</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="90">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>2.7</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="91">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>2.66</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="92">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>2.66</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="93">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>2.63</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="94">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>2.62</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="95">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>2.62</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="96">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>2.62</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="97">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>2.62</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="98">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>2.58</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="99">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="100">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>2.54</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="101">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>2.54</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="102">
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>2.5</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="103">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>2.48</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="104">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>2.46</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="105">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>2.46</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="106">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>2.45</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="107">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>2.42</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="108">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>2.41</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="109">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>2.34</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="110">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>2.33</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="111">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>2.28</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="112">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>2.28</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="113">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>2.26</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="114">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>2.24</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="115">
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>2.24</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="116">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>2.21</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="117">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>2.19</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="118">
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>2.18</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="119">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>2.17</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="120">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>2.15</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="121">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>2.15</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="122">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>2.1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="123">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>2.1</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="124">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>2.1</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="125">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>2.1</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="126">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>2.09</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="127">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>2.06</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="128">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>2.05</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="129">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>2.02</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="130">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>2.01</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="131">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>2.01</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="132">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>2</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="133">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>1.96</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="134">
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>1.95</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="135">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>1.94</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="136">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>1.94</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="137">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>1.9</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="138">
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>1.87</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="139">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>1.86</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="140">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.83</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="141">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>1.83</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="142">
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>1.81</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="143">
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>1.8</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="144">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>1.78</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="145">
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>1.78</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="146">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>1.76</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="147">
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>1.75</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="148">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>1.72</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="149">
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1779227402206</v>
+        <v>1779231302092</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>1.71</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46162.1389144213</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="150">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>1.69</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="151">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>1.69</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="152">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>1.69</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="153">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>1.69</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="154">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>1.69</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="155">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>1.68</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="156">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>1.66</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="157">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>1.65</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="158">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>1.64</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="159">
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>1.64</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="160">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>1.63</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="161">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>1.6</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="162">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>1.59</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="163">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>1.57</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="164">
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>1.56</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="165">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.55</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="166">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>1.54</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="167">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>1.54</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="168">
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>1.53</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="169">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>1.53</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="170">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>1.5</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="171">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>1.5</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="172">
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>1.5</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="173">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>1.48</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="174">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>1.47</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="175">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>1.45</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="176">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>1.45</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="177">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>1.41</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="178">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>1.41</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="179">
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1.41</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="180">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>1.41</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="181">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>1.4</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="182">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>1.38</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="183">
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>1.38</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="184">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>1.38</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="185">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>1.37</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="186">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>1.36</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="187">
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>1.34</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="188">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>1.34</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="189">
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>1.31</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="190">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>1.31</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="191">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>1.29</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="192">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>1.29</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="193">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>1.29</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="194">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>1.29</v>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="195">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>1.28</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="196">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>1.27</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="197">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>1.26</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="198">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>1.26</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="199">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>1.25</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="200">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>1.25</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="201">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>1779227402207</v>
+        <v>1779231302092</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>1.25</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18405199074</v>
       </c>
     </row>
     <row r="202">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>1.21</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="203">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>1.21</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="204">
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>1.19</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="205">
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>1.16</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="206">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>1.16</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="207">
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>1.15</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="208">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>1.14</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="209">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>1.14</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="210">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>1.13</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="211">
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>1.11</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="212">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>1.1</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="213">
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>1.1</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="214">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>1.1</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="215">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>1.09</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="216">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.08</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="217">
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>1.08</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="218">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>1.08</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="219">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>1.06</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="220">
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>1.03</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="221">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>1.03</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="222">
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -10853,12 +10853,12 @@
         <v>1.03</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="B223" t="n">
         <v>996.251</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>1779227402207</v>
+        <v>1779231002133</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>46162.13891443287</v>
+        <v>46162.18058024305</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         <v>89.25</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>80.67</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>37.61</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>28.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>26.26</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="7">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>26.25</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>25.82</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="9">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>21.31</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>16.19</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="11">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>13.96</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>12.75</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="13">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>12.5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="15">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>10.3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="16">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>10.21</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="17">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="18">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="19">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>8.58</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="20">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>8.25</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>7.89</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>7.72</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>7.72</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="24">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>7.61</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="25">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>7.29</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>6.35</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="27">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>6.07</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="28">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>5.86</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="29">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>5.6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="30">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>5.47</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="31">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>5.25</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="32">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>5.17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="33">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>5.15</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>5.15</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="35">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>5.03</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="36">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>5.03</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="37">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>5.03</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="38">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>4.99</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="39">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>4.95</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="40">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>4.95</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="41">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>4.92</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="42">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>4.68</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="43">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>4.64</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="44">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>4.58</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="45">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>4.38</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="46">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2585,12 +2585,12 @@
         <v>4.33</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B47" t="n">
         <v>4271.58</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2632,12 +2632,12 @@
         <v>4.27</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B48" t="n">
         <v>4257.587</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>4.26</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>4.06</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="50">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="51">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>3.94</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="52">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>3.86</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="53">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>3.77</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="54">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>3.73</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="55">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>3.72</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="56">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>3.72</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="57">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>3.72</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="58">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>3.68</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="59">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>3.58</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="60">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>3.52</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="61">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>3.5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="62">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>3.5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="63">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>3.48</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="64">
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>3.48</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="65">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>3.45</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="66">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>3.44</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="67">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>3.41</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="68">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.34</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="69">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>3.28</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="70">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>3.21</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="71">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>3.21</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="72">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>3.14</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="73">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>3.1</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="74">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>3.07</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="75">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>3.07</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="76">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>3.06</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="77">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>3.02</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="78">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>3.02</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="79">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="80">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>2.99</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="81">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>2.98</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="82">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>2.94</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="83">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>2.93</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="84">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>2.9</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="85">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="86">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>2.81</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="87">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>2.76</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="88">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>2.73</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="89">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>2.71</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="90">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>2.7</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="91">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>2.66</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="92">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>2.66</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="93">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>2.63</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="94">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>2.62</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="95">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>2.62</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="96">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>2.62</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="97">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>2.62</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="98">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>2.58</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="99">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="100">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>2.54</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="101">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>2.54</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="102">
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>2.5</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="103">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>2.48</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="104">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>2.46</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="105">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>2.46</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="106">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>2.45</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="107">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>2.42</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="108">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>2.41</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="109">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>2.34</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="110">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>2.33</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="111">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>2.28</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="112">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>2.28</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="113">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>2.26</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="114">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>2.24</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="115">
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>2.24</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="116">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>2.21</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="117">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>2.19</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="118">
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>2.18</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="119">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>2.17</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="120">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>2.15</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="121">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>2.15</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="122">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>2.1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="123">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>2.1</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="124">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>2.1</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="125">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>2.1</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="126">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>2.09</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="127">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>2.06</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="128">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>2.05</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="129">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>2.02</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="130">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>2.01</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="131">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>2.01</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="132">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>2</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="133">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>1.96</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="134">
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>1.95</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="135">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>1.94</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="136">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>1.94</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="137">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>1.9</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="138">
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>1.87</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="139">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>1.86</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="140">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.83</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="141">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>1.83</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="142">
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>1.81</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="143">
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>1.8</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="144">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>1.78</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="145">
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>1.78</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="146">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>1.76</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="147">
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>1.75</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="148">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>1.72</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="149">
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>1.71</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="150">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>1.69</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="151">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>1.69</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="152">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>1.69</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="153">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>1.69</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="154">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>1.69</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="155">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>1.68</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="156">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>1.66</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="157">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>1.65</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="158">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>1.64</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="159">
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>1.64</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="160">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>1.63</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="161">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>1.6</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="162">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>1.59</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="163">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>1.57</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="164">
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>1.56</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="165">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.55</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="166">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>1.54</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="167">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>1.54</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="168">
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>1.53</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="169">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>1.53</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="170">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>1.5</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="171">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>1.5</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="172">
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>1.5</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="173">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>1.48</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="174">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>1.47</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="175">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>1.45</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="176">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>1.45</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="177">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>1.41</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="178">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>1.41</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="179">
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1.41</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="180">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>1.41</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="181">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>1.4</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="182">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>1.38</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="183">
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>1.38</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="184">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>1.38</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="185">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>1.37</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="186">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>1.36</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="187">
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>1.34</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="188">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>1.34</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="189">
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>1.31</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="190">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>1.31</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="191">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>1.29</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="192">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>1.29</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="193">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>1.29</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="194">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>1.29</v>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="195">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>1.28</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="196">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>1.27</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="197">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>1.26</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="198">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>1.26</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="199">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>1.25</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="200">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>1.25</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="201">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>1779231302092</v>
+        <v>1779234602085</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>1.25</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>46162.18405199074</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="202">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>1.21</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="203">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>1.21</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="204">
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>1.19</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="205">
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>1.16</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="206">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>1.16</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="207">
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>1.15</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="208">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>1.14</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="209">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>1.14</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="210">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>1.13</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="211">
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>1.11</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="212">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>1.1</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="213">
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>1.1</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="214">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>1.1</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="215">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>1.09</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="216">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.08</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="217">
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>1.08</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="218">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>1.08</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="219">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>1.06</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="220">
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>1.03</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="221">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>1.03</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="222">
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>1.03</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
     <row r="223">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>1779231002133</v>
+        <v>1779234602085</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>46162.18058024305</v>
+        <v>46162.22224635417</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         <v>89.25</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>80.67</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>37.61</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -658,12 +658,12 @@
         <v>28.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" t="n">
         <v>26257.331</v>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
         <v>26.26</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" t="n">
         <v>26250.423</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>26.25</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
         <v>25.82</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" t="n">
         <v>21309.892</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
         <v>21.31</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" t="n">
         <v>16189.48</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>16.19</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="11">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>13.96</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>12.75</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="13">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1034,12 +1034,12 @@
         <v>12.5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B14" t="n">
         <v>11476.259</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="15">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>10.3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="16">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1175,12 +1175,12 @@
         <v>10.21</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B17" t="n">
         <v>9136.491</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1222,12 +1222,12 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B18" t="n">
         <v>9113.49</v>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1269,12 +1269,12 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B19" t="n">
         <v>8575.26</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1316,12 +1316,12 @@
         <v>8.58</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B20" t="n">
         <v>8250.538</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>8.25</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>7.89</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>7.72</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>7.72</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="24">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,12 +1551,12 @@
         <v>7.61</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B25" t="n">
         <v>7290.358</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>7.29</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
         <v>6.35</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B27" t="n">
         <v>6073.892</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1692,12 +1692,12 @@
         <v>6.07</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B28" t="n">
         <v>5859.767</v>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1739,12 +1739,12 @@
         <v>5.86</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B29" t="n">
         <v>5600</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1786,12 +1786,12 @@
         <v>5.6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B30" t="n">
         <v>5469.746</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>5.47</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="31">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>5.25</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="32">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1927,12 +1927,12 @@
         <v>5.17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B33" t="n">
         <v>5145.149</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1974,12 +1974,12 @@
         <v>5.15</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B34" t="n">
         <v>5145.149</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2021,12 +2021,12 @@
         <v>5.15</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B35" t="n">
         <v>5032.575</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2068,12 +2068,12 @@
         <v>5.03</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B36" t="n">
         <v>5032.569</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2115,12 +2115,12 @@
         <v>5.03</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B37" t="n">
         <v>5026.415</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2162,12 +2162,12 @@
         <v>5.03</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B38" t="n">
         <v>4986.6</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
         <v>4.99</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B39" t="n">
         <v>4949.227</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2256,12 +2256,12 @@
         <v>4.95</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B40" t="n">
         <v>4945.018</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2303,12 +2303,12 @@
         <v>4.95</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B41" t="n">
         <v>4923.921</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>4.92</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="42">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>4.68</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="43">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>4.64</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="44">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>4.58</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="45">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2538,12 +2538,12 @@
         <v>4.38</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B46" t="n">
         <v>4333.934</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>4.33</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="47">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>4.27</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="48">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2679,12 +2679,12 @@
         <v>4.26</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B49" t="n">
         <v>4063.822</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2726,12 +2726,12 @@
         <v>4.06</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B50" t="n">
         <v>4000</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="51">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1779234602085</v>
+        <v>1779242402274</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2820,12 +2820,12 @@
         <v>3.94</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252631945</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B52" t="n">
         <v>3855.441</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>3.86</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="53">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2914,12 +2914,12 @@
         <v>3.77</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B54" t="n">
         <v>3728.89</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2961,12 +2961,12 @@
         <v>3.73</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B55" t="n">
         <v>3718.234</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3008,12 +3008,12 @@
         <v>3.72</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B56" t="n">
         <v>3718.198</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3055,12 +3055,12 @@
         <v>3.72</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B57" t="n">
         <v>3718.198</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
         <v>3.72</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="B58" t="n">
         <v>3679.75</v>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
         <v>3.68</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B59" t="n">
         <v>3582.255</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3192,15 +3192,15 @@
         <v>3.58</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B60" t="n">
-        <v>3520.169</v>
+        <v>3517.675</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3239,12 +3239,12 @@
         <v>3.52</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B61" t="n">
         <v>3504.698</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
         <v>3.5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B62" t="n">
         <v>3499.409</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
         <v>3.5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B63" t="n">
         <v>3481.809</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3380,12 +3380,12 @@
         <v>3.48</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B64" t="n">
         <v>3480.546</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
         <v>3.48</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B65" t="n">
         <v>3445.605</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3474,12 +3474,12 @@
         <v>3.45</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B66" t="n">
         <v>3440.07</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3521,12 +3521,12 @@
         <v>3.44</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B67" t="n">
         <v>3405.713</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3568,12 +3568,12 @@
         <v>3.41</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="B68" t="n">
         <v>3337.25</v>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3615,12 +3615,12 @@
         <v>3.34</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="B69" t="n">
         <v>3278.3</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3662,12 +3662,12 @@
         <v>3.28</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B70" t="n">
         <v>3208.067</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3709,12 +3709,12 @@
         <v>3.21</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="B71" t="n">
         <v>3206.88</v>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3756,12 +3756,12 @@
         <v>3.21</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B72" t="n">
         <v>3135.506</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3803,12 +3803,12 @@
         <v>3.14</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="B73" t="n">
         <v>3100.307</v>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3850,12 +3850,12 @@
         <v>3.1</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B74" t="n">
         <v>3072.649</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3897,12 +3897,12 @@
         <v>3.07</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="B75" t="n">
         <v>3068.071</v>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3944,12 +3944,12 @@
         <v>3.07</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="B76" t="n">
         <v>3063.21</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>3.06</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="77">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4038,12 +4038,12 @@
         <v>3.02</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B78" t="n">
         <v>3015.587</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4085,12 +4085,12 @@
         <v>3.02</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B79" t="n">
         <v>2998.849</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4132,12 +4132,12 @@
         <v>3</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B80" t="n">
         <v>2988.916</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4179,12 +4179,12 @@
         <v>2.99</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B81" t="n">
         <v>2979</v>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>2.98</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="82">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
         <v>2.94</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B83" t="n">
         <v>2926.106</v>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4320,12 +4320,12 @@
         <v>2.93</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B84" t="n">
         <v>2904.619</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>2.9</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="85">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4414,15 +4414,15 @@
         <v>2.9</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B86" t="n">
-        <v>2811.471</v>
+        <v>2804.854</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4458,15 +4458,15 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="B87" t="n">
         <v>2763.4</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4508,12 +4508,12 @@
         <v>2.76</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="B88" t="n">
         <v>2726.181</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4555,12 +4555,12 @@
         <v>2.73</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B89" t="n">
         <v>2706.174</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4602,12 +4602,12 @@
         <v>2.71</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B90" t="n">
         <v>2702.317</v>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4649,12 +4649,12 @@
         <v>2.7</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="B91" t="n">
         <v>2660.688</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4696,12 +4696,12 @@
         <v>2.66</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="B92" t="n">
         <v>2660.688</v>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4743,12 +4743,12 @@
         <v>2.66</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B93" t="n">
         <v>2631.963</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>2.63</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="94">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>2.62</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="95">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>2.62</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="96">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>2.62</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="97">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4978,12 +4978,12 @@
         <v>2.62</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="B98" t="n">
         <v>2575.208</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5025,12 +5025,12 @@
         <v>2.58</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="B99" t="n">
         <v>2563.107</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5072,12 +5072,12 @@
         <v>2.56</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B100" t="n">
         <v>2543.714</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5119,12 +5119,12 @@
         <v>2.54</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B101" t="n">
         <v>2540.764</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5166,12 +5166,12 @@
         <v>2.54</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1675</v>
+        <v>1668</v>
       </c>
       <c r="B102" t="n">
         <v>2499.861</v>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5213,12 +5213,12 @@
         <v>2.5</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="B103" t="n">
         <v>2478.664</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5260,12 +5260,12 @@
         <v>2.48</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="B104" t="n">
         <v>2458.319</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5307,12 +5307,12 @@
         <v>2.46</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="B105" t="n">
         <v>2457.914</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5354,12 +5354,12 @@
         <v>2.46</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1709</v>
+        <v>1705</v>
       </c>
       <c r="B106" t="n">
         <v>2450.365</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5401,12 +5401,12 @@
         <v>2.45</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="B107" t="n">
         <v>2417.248</v>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5448,12 +5448,12 @@
         <v>2.42</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="B108" t="n">
         <v>2413.223</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5495,12 +5495,12 @@
         <v>2.41</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="B109" t="n">
         <v>2339.618</v>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>2.34</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="110">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5589,12 +5589,12 @@
         <v>2.33</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B111" t="n">
         <v>2281.543</v>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5636,12 +5636,12 @@
         <v>2.28</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B112" t="n">
         <v>2278.214</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5683,12 +5683,12 @@
         <v>2.28</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="B113" t="n">
         <v>2261.775</v>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5730,12 +5730,12 @@
         <v>2.26</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B114" t="n">
         <v>2241.256</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5777,12 +5777,12 @@
         <v>2.24</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="B115" t="n">
         <v>2235.788</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5824,12 +5824,12 @@
         <v>2.24</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B116" t="n">
         <v>2214.878</v>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5871,12 +5871,12 @@
         <v>2.21</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="B117" t="n">
         <v>2192.483</v>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5918,12 +5918,12 @@
         <v>2.19</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B118" t="n">
         <v>2180.293</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
         <v>2.18</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="B119" t="n">
         <v>2165.214</v>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6012,12 +6012,12 @@
         <v>2.17</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="B120" t="n">
         <v>2154.281</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6059,12 +6059,12 @@
         <v>2.15</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="B121" t="n">
         <v>2147.981</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6106,12 +6106,12 @@
         <v>2.15</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="B122" t="n">
         <v>2104.643</v>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6153,12 +6153,12 @@
         <v>2.1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="B123" t="n">
         <v>2101.794</v>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6200,12 +6200,12 @@
         <v>2.1</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B124" t="n">
         <v>2100.259</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6247,12 +6247,12 @@
         <v>2.1</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B125" t="n">
         <v>2100</v>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6294,12 +6294,12 @@
         <v>2.1</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B126" t="n">
         <v>2092.411</v>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>2.09</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="127">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>2.06</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="128">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6435,12 +6435,12 @@
         <v>2.05</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="B129" t="n">
         <v>2016.514</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>2.02</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="130">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>2.01</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="131">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6576,12 +6576,12 @@
         <v>2.01</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="B132" t="n">
         <v>2004.739</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6623,12 +6623,12 @@
         <v>2</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B133" t="n">
         <v>1963.898</v>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6670,12 +6670,12 @@
         <v>1.96</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="B134" t="n">
         <v>1948.176</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
         <v>1.95</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="B135" t="n">
         <v>1942.966</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6764,12 +6764,12 @@
         <v>1.94</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2158</v>
+        <v>2151</v>
       </c>
       <c r="B136" t="n">
         <v>1935.918</v>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6811,12 +6811,12 @@
         <v>1.94</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B137" t="n">
         <v>1898.548</v>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6858,12 +6858,12 @@
         <v>1.9</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B138" t="n">
         <v>1865.074</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>1.87</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="139">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6952,12 +6952,12 @@
         <v>1.86</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B140" t="n">
         <v>1830.164</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6999,12 +6999,12 @@
         <v>1.83</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B141" t="n">
         <v>1829.683</v>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7046,12 +7046,12 @@
         <v>1.83</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="B142" t="n">
         <v>1806.507</v>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -7093,12 +7093,12 @@
         <v>1.81</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="B143" t="n">
         <v>1798.554</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -7140,12 +7140,12 @@
         <v>1.8</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="B144" t="n">
         <v>1782.941</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -7187,12 +7187,12 @@
         <v>1.78</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="B145" t="n">
         <v>1781.03</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7234,12 +7234,12 @@
         <v>1.78</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="B146" t="n">
         <v>1760.988</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -7281,12 +7281,12 @@
         <v>1.76</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="B147" t="n">
         <v>1753.479</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7328,12 +7328,12 @@
         <v>1.75</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="B148" t="n">
         <v>1716.6</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>1.72</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="149">
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7422,12 +7422,12 @@
         <v>1.71</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="B150" t="n">
         <v>1692.54</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7469,12 +7469,12 @@
         <v>1.69</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="B151" t="n">
         <v>1689.098</v>
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7516,12 +7516,12 @@
         <v>1.69</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="B152" t="n">
         <v>1688.326</v>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7563,12 +7563,12 @@
         <v>1.69</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="B153" t="n">
         <v>1686.861</v>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>1.69</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="154">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7657,12 +7657,12 @@
         <v>1.69</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="B155" t="n">
         <v>1682.312</v>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7704,12 +7704,12 @@
         <v>1.68</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="B156" t="n">
         <v>1664.261</v>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>1.66</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="157">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7798,12 +7798,12 @@
         <v>1.65</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="B158" t="n">
         <v>1642.892</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7845,12 +7845,12 @@
         <v>1.64</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="B159" t="n">
         <v>1636.369</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7892,12 +7892,12 @@
         <v>1.64</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B160" t="n">
         <v>1634.503</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>1.63</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="161">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1779234602085</v>
+        <v>1779242402275</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7986,12 +7986,12 @@
         <v>1.6</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.31252633102</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="B162" t="n">
         <v>1585.722</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8033,12 +8033,12 @@
         <v>1.59</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2543</v>
+        <v>2534</v>
       </c>
       <c r="B163" t="n">
         <v>1570.959</v>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8080,12 +8080,12 @@
         <v>1.57</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2565</v>
+        <v>2561</v>
       </c>
       <c r="B164" t="n">
         <v>1555.265</v>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -8127,12 +8127,12 @@
         <v>1.56</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2573</v>
+        <v>2569</v>
       </c>
       <c r="B165" t="n">
         <v>1551.059</v>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8174,12 +8174,12 @@
         <v>1.55</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="B166" t="n">
         <v>1544.473</v>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
         <v>1.54</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="B167" t="n">
         <v>1535.967</v>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8268,12 +8268,12 @@
         <v>1.54</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2596</v>
+        <v>2590</v>
       </c>
       <c r="B168" t="n">
         <v>1533.654</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8315,12 +8315,12 @@
         <v>1.53</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2604</v>
+        <v>2600</v>
       </c>
       <c r="B169" t="n">
         <v>1527.065</v>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -8362,12 +8362,12 @@
         <v>1.53</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="B170" t="n">
         <v>1500</v>
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -8409,12 +8409,12 @@
         <v>1.5</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="B171" t="n">
         <v>1496.758</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8456,12 +8456,12 @@
         <v>1.5</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="B172" t="n">
         <v>1496.758</v>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8503,12 +8503,12 @@
         <v>1.5</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="B173" t="n">
         <v>1479.294</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8550,12 +8550,12 @@
         <v>1.48</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2676</v>
+        <v>2679</v>
       </c>
       <c r="B174" t="n">
         <v>1469.34</v>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
         <v>1.47</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="B175" t="n">
         <v>1448.418</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8644,12 +8644,12 @@
         <v>1.45</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="B176" t="n">
         <v>1446.827</v>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8691,12 +8691,12 @@
         <v>1.45</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="B177" t="n">
         <v>1414.754</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8738,12 +8738,12 @@
         <v>1.41</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="B178" t="n">
         <v>1411.854</v>
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8785,12 +8785,12 @@
         <v>1.41</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="B179" t="n">
         <v>1409.878</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1.41</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="180">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8879,12 +8879,12 @@
         <v>1.41</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2752</v>
+        <v>2747</v>
       </c>
       <c r="B181" t="n">
         <v>1401.953</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8926,12 +8926,12 @@
         <v>1.4</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="B182" t="n">
         <v>1376.279</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8973,12 +8973,12 @@
         <v>1.38</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2798</v>
+        <v>2795</v>
       </c>
       <c r="B183" t="n">
         <v>1375.923</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -9020,12 +9020,12 @@
         <v>1.38</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2800</v>
+        <v>2797</v>
       </c>
       <c r="B184" t="n">
         <v>1375.254</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9067,12 +9067,12 @@
         <v>1.38</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="B185" t="n">
         <v>1373.237</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9114,12 +9114,12 @@
         <v>1.37</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="B186" t="n">
         <v>1356.362</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -9161,12 +9161,12 @@
         <v>1.36</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="B187" t="n">
         <v>1344.178</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9208,12 +9208,12 @@
         <v>1.34</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="B188" t="n">
         <v>1340.059</v>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9255,12 +9255,12 @@
         <v>1.34</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="B189" t="n">
         <v>1314.935</v>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9302,12 +9302,12 @@
         <v>1.31</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2901</v>
+        <v>2895</v>
       </c>
       <c r="B190" t="n">
         <v>1306.807</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>1.31</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="191">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>1.29</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46162.22224635417</v>
+        <v>46162.30905008102</v>
       </c>
     </row>
     <row r="192">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1779234602085</v>
+        <v>1779242101927<